--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I616"/>
+  <dimension ref="A1:I638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26987,6 +26987,952 @@
       </c>
       <c r="I616" s="4" t="inlineStr"/>
     </row>
+    <row r="617">
+      <c r="A617" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B617" s="6" t="inlineStr">
+        <is>
+          <t>05:45:05</t>
+        </is>
+      </c>
+      <c r="C617" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D617" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E617" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F617" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G617" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260911054505548341.gif</t>
+        </is>
+      </c>
+      <c r="H617" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I617" s="7" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B618" s="3" t="inlineStr">
+        <is>
+          <t>05:45:05</t>
+        </is>
+      </c>
+      <c r="C618" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D618" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E618" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F618" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G618" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260911054505678643.xlsx</t>
+        </is>
+      </c>
+      <c r="H618" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I618" s="4" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B619" s="6" t="inlineStr">
+        <is>
+          <t>05:45:05</t>
+        </is>
+      </c>
+      <c r="C619" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D619" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E619" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F619" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G619" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260911054505817150.csv</t>
+        </is>
+      </c>
+      <c r="H619" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I619" s="7" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>05:45:05</t>
+        </is>
+      </c>
+      <c r="C620" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D620" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E620" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F620" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G620" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260911054505949324.pdf</t>
+        </is>
+      </c>
+      <c r="H620" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I620" s="4" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B621" s="6" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C621" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D621" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E621" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F621" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G621" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260911054506077756.docx</t>
+        </is>
+      </c>
+      <c r="H621" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I621" s="7" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B622" s="3" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C622" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D622" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E622" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F622" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G622" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260911054506206307.pptx</t>
+        </is>
+      </c>
+      <c r="H622" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I622" s="4" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B623" s="6" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C623" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D623" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E623" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F623" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G623" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260911054506358907.jpg</t>
+        </is>
+      </c>
+      <c r="H623" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I623" s="7" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B624" s="3" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C624" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D624" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E624" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F624" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G624" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260911054506488029.doc</t>
+        </is>
+      </c>
+      <c r="H624" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I624" s="4" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B625" s="6" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C625" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D625" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E625" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F625" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G625" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260911054506617438.txt</t>
+        </is>
+      </c>
+      <c r="H625" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I625" s="7" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B626" s="3" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C626" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D626" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E626" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F626" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G626" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260911054506745722.xls</t>
+        </is>
+      </c>
+      <c r="H626" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I626" s="4" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B627" s="6" t="inlineStr">
+        <is>
+          <t>05:45:06</t>
+        </is>
+      </c>
+      <c r="C627" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D627" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E627" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F627" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G627" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260911054506901881.png</t>
+        </is>
+      </c>
+      <c r="H627" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I627" s="7" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>05:45:07</t>
+        </is>
+      </c>
+      <c r="C628" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D628" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E628" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F628" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G628" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260911054507032670.dat</t>
+        </is>
+      </c>
+      <c r="H628" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I628" s="4" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B629" s="6" t="inlineStr">
+        <is>
+          <t>05:45:09</t>
+        </is>
+      </c>
+      <c r="C629" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D629" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E629" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F629" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G629" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260911054509134428.docx</t>
+        </is>
+      </c>
+      <c r="H629" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I629" s="7" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>05:45:09</t>
+        </is>
+      </c>
+      <c r="C630" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D630" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E630" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F630" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G630" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260911054509262438.pdf</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I630" s="4" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B631" s="6" t="inlineStr">
+        <is>
+          <t>05:45:09</t>
+        </is>
+      </c>
+      <c r="C631" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D631" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E631" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F631" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G631" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260911054509422658.jpeg</t>
+        </is>
+      </c>
+      <c r="H631" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I631" s="7" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>05:45:09</t>
+        </is>
+      </c>
+      <c r="C632" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D632" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E632" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F632" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G632" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260911054509554271.xlsx</t>
+        </is>
+      </c>
+      <c r="H632" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I632" s="4" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B633" s="6" t="inlineStr">
+        <is>
+          <t>05:45:10</t>
+        </is>
+      </c>
+      <c r="C633" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D633" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E633" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F633" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G633" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260911054510054989.txt</t>
+        </is>
+      </c>
+      <c r="H633" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I633" s="7" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>05:45:10</t>
+        </is>
+      </c>
+      <c r="C634" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D634" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E634" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F634" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G634" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260911054510185991.xlsx</t>
+        </is>
+      </c>
+      <c r="H634" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I634" s="4" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B635" s="6" t="inlineStr">
+        <is>
+          <t>05:45:10</t>
+        </is>
+      </c>
+      <c r="C635" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D635" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E635" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F635" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G635" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H635" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I635" s="7" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>05:45:11</t>
+        </is>
+      </c>
+      <c r="C636" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D636" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E636" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F636" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G636" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260911054511028838.pdf</t>
+        </is>
+      </c>
+      <c r="H636" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I636" s="4" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B637" s="6" t="inlineStr">
+        <is>
+          <t>05:45:11</t>
+        </is>
+      </c>
+      <c r="C637" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D637" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E637" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F637" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G637" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260911054511160913.jpeg</t>
+        </is>
+      </c>
+      <c r="H637" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I637" s="7" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B638" s="3" t="inlineStr">
+        <is>
+          <t>05:45:11</t>
+        </is>
+      </c>
+      <c r="C638" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D638" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E638" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F638" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G638" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260911054511317141.pages</t>
+        </is>
+      </c>
+      <c r="H638" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I638" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I638"/>
+  <dimension ref="A1:I660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27933,6 +27933,952 @@
       </c>
       <c r="I638" s="4" t="inlineStr"/>
     </row>
+    <row r="639">
+      <c r="A639" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B639" s="6" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C639" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D639" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E639" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F639" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G639" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260912032526541861.gif</t>
+        </is>
+      </c>
+      <c r="H639" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I639" s="7" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C640" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D640" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E640" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F640" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G640" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260912032526615271.xlsx</t>
+        </is>
+      </c>
+      <c r="H640" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I640" s="4" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B641" s="6" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C641" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D641" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E641" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F641" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G641" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260912032526688831.csv</t>
+        </is>
+      </c>
+      <c r="H641" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I641" s="7" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B642" s="3" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C642" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D642" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E642" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F642" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G642" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260912032526757015.pdf</t>
+        </is>
+      </c>
+      <c r="H642" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I642" s="4" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B643" s="6" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C643" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D643" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E643" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F643" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G643" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260912032526826081.docx</t>
+        </is>
+      </c>
+      <c r="H643" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I643" s="7" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B644" s="3" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C644" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D644" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E644" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F644" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G644" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260912032526906348.pptx</t>
+        </is>
+      </c>
+      <c r="H644" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I644" s="4" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B645" s="6" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C645" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D645" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E645" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F645" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G645" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260912032526973905.jpg</t>
+        </is>
+      </c>
+      <c r="H645" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I645" s="7" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>03:25:27</t>
+        </is>
+      </c>
+      <c r="C646" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D646" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E646" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F646" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G646" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260912032527041739.doc</t>
+        </is>
+      </c>
+      <c r="H646" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I646" s="4" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B647" s="6" t="inlineStr">
+        <is>
+          <t>03:25:27</t>
+        </is>
+      </c>
+      <c r="C647" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D647" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E647" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F647" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G647" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260912032527113549.txt</t>
+        </is>
+      </c>
+      <c r="H647" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I647" s="7" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>03:25:27</t>
+        </is>
+      </c>
+      <c r="C648" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D648" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E648" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F648" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G648" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260912032527202587.xls</t>
+        </is>
+      </c>
+      <c r="H648" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I648" s="4" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B649" s="6" t="inlineStr">
+        <is>
+          <t>03:25:27</t>
+        </is>
+      </c>
+      <c r="C649" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D649" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E649" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F649" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G649" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260912032527278808.png</t>
+        </is>
+      </c>
+      <c r="H649" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I649" s="7" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>03:25:27</t>
+        </is>
+      </c>
+      <c r="C650" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D650" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E650" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F650" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G650" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260912032527348396.dat</t>
+        </is>
+      </c>
+      <c r="H650" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I650" s="4" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B651" s="6" t="inlineStr">
+        <is>
+          <t>03:25:28</t>
+        </is>
+      </c>
+      <c r="C651" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D651" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E651" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F651" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G651" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260912032528371728.docx</t>
+        </is>
+      </c>
+      <c r="H651" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I651" s="7" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>03:25:28</t>
+        </is>
+      </c>
+      <c r="C652" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D652" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E652" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F652" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G652" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260912032528459342.pdf</t>
+        </is>
+      </c>
+      <c r="H652" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I652" s="4" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B653" s="6" t="inlineStr">
+        <is>
+          <t>03:25:28</t>
+        </is>
+      </c>
+      <c r="C653" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D653" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E653" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F653" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G653" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260912032528665790.jpeg</t>
+        </is>
+      </c>
+      <c r="H653" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I653" s="7" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>03:25:28</t>
+        </is>
+      </c>
+      <c r="C654" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D654" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E654" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F654" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G654" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260912032528734600.xlsx</t>
+        </is>
+      </c>
+      <c r="H654" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I654" s="4" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B655" s="6" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C655" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D655" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E655" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F655" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G655" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260912032529066260.txt</t>
+        </is>
+      </c>
+      <c r="H655" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I655" s="7" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C656" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D656" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E656" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F656" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G656" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260912032529214445.xlsx</t>
+        </is>
+      </c>
+      <c r="H656" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I656" s="4" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B657" s="6" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C657" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D657" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E657" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F657" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G657" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H657" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I657" s="7" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C658" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D658" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E658" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F658" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G658" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260912032529521521.pdf</t>
+        </is>
+      </c>
+      <c r="H658" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I658" s="4" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B659" s="6" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C659" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D659" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E659" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F659" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G659" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260912032529590924.jpeg</t>
+        </is>
+      </c>
+      <c r="H659" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I659" s="7" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B660" s="3" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C660" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D660" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E660" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F660" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G660" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260912032529675031.pages</t>
+        </is>
+      </c>
+      <c r="H660" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I660" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I660"/>
+  <dimension ref="A1:I682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28879,6 +28879,952 @@
       </c>
       <c r="I660" s="4" t="inlineStr"/>
     </row>
+    <row r="661">
+      <c r="A661" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B661" s="6" t="inlineStr">
+        <is>
+          <t>03:31:21</t>
+        </is>
+      </c>
+      <c r="C661" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D661" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E661" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F661" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G661" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260913033121216445.gif</t>
+        </is>
+      </c>
+      <c r="H661" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I661" s="7" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>03:31:21</t>
+        </is>
+      </c>
+      <c r="C662" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D662" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E662" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F662" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G662" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260913033121333797.xlsx</t>
+        </is>
+      </c>
+      <c r="H662" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I662" s="4" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B663" s="6" t="inlineStr">
+        <is>
+          <t>03:31:21</t>
+        </is>
+      </c>
+      <c r="C663" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D663" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E663" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F663" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G663" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260913033121439243.csv</t>
+        </is>
+      </c>
+      <c r="H663" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I663" s="7" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>03:31:21</t>
+        </is>
+      </c>
+      <c r="C664" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D664" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E664" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F664" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G664" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260913033121553718.pdf</t>
+        </is>
+      </c>
+      <c r="H664" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I664" s="4" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B665" s="6" t="inlineStr">
+        <is>
+          <t>03:31:21</t>
+        </is>
+      </c>
+      <c r="C665" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D665" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E665" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F665" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G665" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260913033121794491.docx</t>
+        </is>
+      </c>
+      <c r="H665" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I665" s="7" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B666" s="3" t="inlineStr">
+        <is>
+          <t>03:31:21</t>
+        </is>
+      </c>
+      <c r="C666" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D666" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E666" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F666" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G666" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260913033121931947.pptx</t>
+        </is>
+      </c>
+      <c r="H666" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I666" s="4" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B667" s="6" t="inlineStr">
+        <is>
+          <t>03:31:22</t>
+        </is>
+      </c>
+      <c r="C667" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D667" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E667" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F667" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G667" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260913033122180879.jpg</t>
+        </is>
+      </c>
+      <c r="H667" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I667" s="7" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B668" s="3" t="inlineStr">
+        <is>
+          <t>03:31:22</t>
+        </is>
+      </c>
+      <c r="C668" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D668" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E668" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F668" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G668" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260913033122310715.doc</t>
+        </is>
+      </c>
+      <c r="H668" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I668" s="4" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B669" s="6" t="inlineStr">
+        <is>
+          <t>03:31:22</t>
+        </is>
+      </c>
+      <c r="C669" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D669" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E669" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F669" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G669" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260913033122450340.txt</t>
+        </is>
+      </c>
+      <c r="H669" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I669" s="7" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B670" s="3" t="inlineStr">
+        <is>
+          <t>03:31:22</t>
+        </is>
+      </c>
+      <c r="C670" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D670" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E670" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F670" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G670" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260913033122591149.xls</t>
+        </is>
+      </c>
+      <c r="H670" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I670" s="4" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B671" s="6" t="inlineStr">
+        <is>
+          <t>03:31:22</t>
+        </is>
+      </c>
+      <c r="C671" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D671" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E671" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F671" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G671" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260913033122821221.png</t>
+        </is>
+      </c>
+      <c r="H671" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I671" s="7" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>03:31:22</t>
+        </is>
+      </c>
+      <c r="C672" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D672" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E672" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F672" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G672" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260913033122937497.dat</t>
+        </is>
+      </c>
+      <c r="H672" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I672" s="4" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B673" s="6" t="inlineStr">
+        <is>
+          <t>03:31:25</t>
+        </is>
+      </c>
+      <c r="C673" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D673" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E673" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F673" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G673" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260913033125134452.docx</t>
+        </is>
+      </c>
+      <c r="H673" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I673" s="7" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>03:31:25</t>
+        </is>
+      </c>
+      <c r="C674" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D674" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E674" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F674" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G674" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260913033125427822.pdf</t>
+        </is>
+      </c>
+      <c r="H674" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I674" s="4" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B675" s="6" t="inlineStr">
+        <is>
+          <t>03:31:25</t>
+        </is>
+      </c>
+      <c r="C675" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D675" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E675" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F675" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G675" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260913033125676422.jpeg</t>
+        </is>
+      </c>
+      <c r="H675" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I675" s="7" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>03:31:25</t>
+        </is>
+      </c>
+      <c r="C676" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D676" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E676" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F676" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G676" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260913033125807000.xlsx</t>
+        </is>
+      </c>
+      <c r="H676" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I676" s="4" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B677" s="6" t="inlineStr">
+        <is>
+          <t>03:31:26</t>
+        </is>
+      </c>
+      <c r="C677" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D677" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E677" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F677" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G677" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260913033126458013.txt</t>
+        </is>
+      </c>
+      <c r="H677" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I677" s="7" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>03:31:26</t>
+        </is>
+      </c>
+      <c r="C678" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D678" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E678" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F678" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G678" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260913033126565270.xlsx</t>
+        </is>
+      </c>
+      <c r="H678" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I678" s="4" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B679" s="6" t="inlineStr">
+        <is>
+          <t>03:31:26</t>
+        </is>
+      </c>
+      <c r="C679" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D679" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E679" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F679" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G679" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H679" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I679" s="7" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>03:31:27</t>
+        </is>
+      </c>
+      <c r="C680" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D680" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E680" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F680" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G680" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260913033127311819.pdf</t>
+        </is>
+      </c>
+      <c r="H680" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I680" s="4" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B681" s="6" t="inlineStr">
+        <is>
+          <t>03:31:27</t>
+        </is>
+      </c>
+      <c r="C681" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D681" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E681" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F681" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G681" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260913033127439259.jpeg</t>
+        </is>
+      </c>
+      <c r="H681" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I681" s="7" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B682" s="3" t="inlineStr">
+        <is>
+          <t>03:31:27</t>
+        </is>
+      </c>
+      <c r="C682" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D682" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E682" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F682" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G682" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260913033127552232.pages</t>
+        </is>
+      </c>
+      <c r="H682" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I682" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I682"/>
+  <dimension ref="A1:I704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29825,6 +29825,952 @@
       </c>
       <c r="I682" s="4" t="inlineStr"/>
     </row>
+    <row r="683">
+      <c r="A683" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B683" s="6" t="inlineStr">
+        <is>
+          <t>03:41:36</t>
+        </is>
+      </c>
+      <c r="C683" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D683" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E683" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F683" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G683" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260914034136831194.gif</t>
+        </is>
+      </c>
+      <c r="H683" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I683" s="7" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B684" s="3" t="inlineStr">
+        <is>
+          <t>03:41:36</t>
+        </is>
+      </c>
+      <c r="C684" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D684" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E684" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F684" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G684" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260914034136992615.xlsx</t>
+        </is>
+      </c>
+      <c r="H684" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I684" s="4" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B685" s="6" t="inlineStr">
+        <is>
+          <t>03:41:37</t>
+        </is>
+      </c>
+      <c r="C685" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D685" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E685" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F685" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G685" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260914034137146380.csv</t>
+        </is>
+      </c>
+      <c r="H685" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I685" s="7" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B686" s="3" t="inlineStr">
+        <is>
+          <t>03:41:37</t>
+        </is>
+      </c>
+      <c r="C686" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D686" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E686" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F686" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G686" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260914034137298896.pdf</t>
+        </is>
+      </c>
+      <c r="H686" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I686" s="4" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B687" s="6" t="inlineStr">
+        <is>
+          <t>03:41:37</t>
+        </is>
+      </c>
+      <c r="C687" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D687" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E687" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F687" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G687" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260914034137450551.docx</t>
+        </is>
+      </c>
+      <c r="H687" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I687" s="7" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B688" s="3" t="inlineStr">
+        <is>
+          <t>03:41:37</t>
+        </is>
+      </c>
+      <c r="C688" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D688" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E688" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F688" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G688" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260914034137624609.pptx</t>
+        </is>
+      </c>
+      <c r="H688" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I688" s="4" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B689" s="6" t="inlineStr">
+        <is>
+          <t>03:41:37</t>
+        </is>
+      </c>
+      <c r="C689" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D689" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E689" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F689" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G689" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260914034137778027.jpg</t>
+        </is>
+      </c>
+      <c r="H689" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I689" s="7" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B690" s="3" t="inlineStr">
+        <is>
+          <t>03:41:37</t>
+        </is>
+      </c>
+      <c r="C690" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D690" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E690" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F690" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G690" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260914034137930917.doc</t>
+        </is>
+      </c>
+      <c r="H690" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I690" s="4" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B691" s="6" t="inlineStr">
+        <is>
+          <t>03:41:38</t>
+        </is>
+      </c>
+      <c r="C691" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D691" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E691" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F691" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G691" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260914034138082376.txt</t>
+        </is>
+      </c>
+      <c r="H691" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I691" s="7" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B692" s="3" t="inlineStr">
+        <is>
+          <t>03:41:38</t>
+        </is>
+      </c>
+      <c r="C692" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D692" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E692" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F692" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G692" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260914034138252787.xls</t>
+        </is>
+      </c>
+      <c r="H692" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I692" s="4" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B693" s="6" t="inlineStr">
+        <is>
+          <t>03:41:38</t>
+        </is>
+      </c>
+      <c r="C693" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D693" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E693" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F693" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G693" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260914034138405074.png</t>
+        </is>
+      </c>
+      <c r="H693" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I693" s="7" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B694" s="3" t="inlineStr">
+        <is>
+          <t>03:41:38</t>
+        </is>
+      </c>
+      <c r="C694" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D694" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E694" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F694" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G694" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260914034138558942.dat</t>
+        </is>
+      </c>
+      <c r="H694" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I694" s="4" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B695" s="6" t="inlineStr">
+        <is>
+          <t>03:41:39</t>
+        </is>
+      </c>
+      <c r="C695" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D695" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E695" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F695" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G695" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260914034139785508.docx</t>
+        </is>
+      </c>
+      <c r="H695" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I695" s="7" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B696" s="3" t="inlineStr">
+        <is>
+          <t>03:41:39</t>
+        </is>
+      </c>
+      <c r="C696" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D696" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E696" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F696" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G696" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260914034139939566.pdf</t>
+        </is>
+      </c>
+      <c r="H696" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I696" s="4" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B697" s="6" t="inlineStr">
+        <is>
+          <t>03:41:40</t>
+        </is>
+      </c>
+      <c r="C697" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D697" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E697" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F697" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G697" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260914034140096837.jpeg</t>
+        </is>
+      </c>
+      <c r="H697" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I697" s="7" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B698" s="3" t="inlineStr">
+        <is>
+          <t>03:41:40</t>
+        </is>
+      </c>
+      <c r="C698" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D698" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E698" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F698" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G698" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260914034140248985.xlsx</t>
+        </is>
+      </c>
+      <c r="H698" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I698" s="4" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B699" s="6" t="inlineStr">
+        <is>
+          <t>03:41:40</t>
+        </is>
+      </c>
+      <c r="C699" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D699" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E699" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F699" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G699" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260914034140918790.txt</t>
+        </is>
+      </c>
+      <c r="H699" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I699" s="7" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B700" s="3" t="inlineStr">
+        <is>
+          <t>03:41:41</t>
+        </is>
+      </c>
+      <c r="C700" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D700" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E700" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F700" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G700" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260914034141071796.xlsx</t>
+        </is>
+      </c>
+      <c r="H700" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I700" s="4" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B701" s="6" t="inlineStr">
+        <is>
+          <t>03:41:41</t>
+        </is>
+      </c>
+      <c r="C701" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D701" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E701" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F701" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G701" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H701" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I701" s="7" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B702" s="3" t="inlineStr">
+        <is>
+          <t>03:41:41</t>
+        </is>
+      </c>
+      <c r="C702" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D702" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E702" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F702" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G702" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260914034141639752.pdf</t>
+        </is>
+      </c>
+      <c r="H702" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I702" s="4" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B703" s="6" t="inlineStr">
+        <is>
+          <t>03:41:41</t>
+        </is>
+      </c>
+      <c r="C703" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D703" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E703" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F703" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G703" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260914034141795433.jpeg</t>
+        </is>
+      </c>
+      <c r="H703" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I703" s="7" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B704" s="3" t="inlineStr">
+        <is>
+          <t>03:41:41</t>
+        </is>
+      </c>
+      <c r="C704" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D704" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E704" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F704" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G704" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260914034141950967.pages</t>
+        </is>
+      </c>
+      <c r="H704" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I704" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I704"/>
+  <dimension ref="A1:I726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30771,6 +30771,952 @@
       </c>
       <c r="I704" s="4" t="inlineStr"/>
     </row>
+    <row r="705">
+      <c r="A705" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B705" s="6" t="inlineStr">
+        <is>
+          <t>03:42:24</t>
+        </is>
+      </c>
+      <c r="C705" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D705" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E705" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F705" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G705" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260915034224648154.gif</t>
+        </is>
+      </c>
+      <c r="H705" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I705" s="7" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
+        <is>
+          <t>03:42:24</t>
+        </is>
+      </c>
+      <c r="C706" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D706" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E706" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F706" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G706" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260915034224794568.xlsx</t>
+        </is>
+      </c>
+      <c r="H706" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I706" s="4" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B707" s="6" t="inlineStr">
+        <is>
+          <t>03:42:24</t>
+        </is>
+      </c>
+      <c r="C707" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D707" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E707" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F707" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G707" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260915034224931435.csv</t>
+        </is>
+      </c>
+      <c r="H707" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I707" s="7" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B708" s="3" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C708" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D708" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E708" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F708" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G708" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260915034225066798.pdf</t>
+        </is>
+      </c>
+      <c r="H708" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I708" s="4" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B709" s="6" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C709" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D709" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E709" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F709" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G709" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260915034225202229.docx</t>
+        </is>
+      </c>
+      <c r="H709" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I709" s="7" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B710" s="3" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C710" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D710" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E710" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F710" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G710" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260915034225356940.pptx</t>
+        </is>
+      </c>
+      <c r="H710" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I710" s="4" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B711" s="6" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C711" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D711" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E711" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F711" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G711" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260915034225493109.jpg</t>
+        </is>
+      </c>
+      <c r="H711" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I711" s="7" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B712" s="3" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C712" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D712" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E712" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F712" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G712" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260915034225629622.doc</t>
+        </is>
+      </c>
+      <c r="H712" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I712" s="4" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B713" s="6" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C713" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D713" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E713" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F713" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G713" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260915034225784561.txt</t>
+        </is>
+      </c>
+      <c r="H713" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I713" s="7" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B714" s="3" t="inlineStr">
+        <is>
+          <t>03:42:25</t>
+        </is>
+      </c>
+      <c r="C714" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D714" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E714" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F714" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G714" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260915034225920303.xls</t>
+        </is>
+      </c>
+      <c r="H714" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I714" s="4" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B715" s="6" t="inlineStr">
+        <is>
+          <t>03:42:26</t>
+        </is>
+      </c>
+      <c r="C715" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D715" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E715" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F715" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G715" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260915034226056729.png</t>
+        </is>
+      </c>
+      <c r="H715" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I715" s="7" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B716" s="3" t="inlineStr">
+        <is>
+          <t>03:42:26</t>
+        </is>
+      </c>
+      <c r="C716" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D716" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E716" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F716" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G716" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260915034226192808.dat</t>
+        </is>
+      </c>
+      <c r="H716" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I716" s="4" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B717" s="6" t="inlineStr">
+        <is>
+          <t>03:42:29</t>
+        </is>
+      </c>
+      <c r="C717" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D717" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E717" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F717" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G717" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260915034229259533.docx</t>
+        </is>
+      </c>
+      <c r="H717" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I717" s="7" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B718" s="3" t="inlineStr">
+        <is>
+          <t>03:42:29</t>
+        </is>
+      </c>
+      <c r="C718" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D718" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E718" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F718" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G718" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260915034229397806.pdf</t>
+        </is>
+      </c>
+      <c r="H718" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I718" s="4" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B719" s="6" t="inlineStr">
+        <is>
+          <t>03:42:29</t>
+        </is>
+      </c>
+      <c r="C719" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D719" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E719" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F719" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G719" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260915034229537506.jpeg</t>
+        </is>
+      </c>
+      <c r="H719" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I719" s="7" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B720" s="3" t="inlineStr">
+        <is>
+          <t>03:42:29</t>
+        </is>
+      </c>
+      <c r="C720" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D720" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E720" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F720" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G720" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260915034229691789.xlsx</t>
+        </is>
+      </c>
+      <c r="H720" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I720" s="4" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B721" s="6" t="inlineStr">
+        <is>
+          <t>03:42:30</t>
+        </is>
+      </c>
+      <c r="C721" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D721" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E721" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F721" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G721" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260915034230309894.txt</t>
+        </is>
+      </c>
+      <c r="H721" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I721" s="7" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B722" s="3" t="inlineStr">
+        <is>
+          <t>03:42:30</t>
+        </is>
+      </c>
+      <c r="C722" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D722" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E722" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F722" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G722" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260915034230449874.xlsx</t>
+        </is>
+      </c>
+      <c r="H722" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I722" s="4" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B723" s="6" t="inlineStr">
+        <is>
+          <t>03:42:30</t>
+        </is>
+      </c>
+      <c r="C723" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D723" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E723" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F723" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G723" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H723" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I723" s="7" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
+        <is>
+          <t>03:42:31</t>
+        </is>
+      </c>
+      <c r="C724" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D724" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E724" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F724" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G724" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260915034231062022.pdf</t>
+        </is>
+      </c>
+      <c r="H724" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I724" s="4" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B725" s="6" t="inlineStr">
+        <is>
+          <t>03:42:31</t>
+        </is>
+      </c>
+      <c r="C725" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D725" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E725" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F725" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G725" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260915034231201847.jpeg</t>
+        </is>
+      </c>
+      <c r="H725" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I725" s="7" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B726" s="3" t="inlineStr">
+        <is>
+          <t>03:42:31</t>
+        </is>
+      </c>
+      <c r="C726" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D726" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E726" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F726" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G726" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260915034231342564.pages</t>
+        </is>
+      </c>
+      <c r="H726" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I726" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I726"/>
+  <dimension ref="A1:I748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31717,6 +31717,952 @@
       </c>
       <c r="I726" s="4" t="inlineStr"/>
     </row>
+    <row r="727">
+      <c r="A727" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B727" s="6" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C727" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D727" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E727" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F727" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G727" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260916033855085486.gif</t>
+        </is>
+      </c>
+      <c r="H727" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I727" s="7" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B728" s="3" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C728" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D728" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E728" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F728" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G728" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260916033855255231.xlsx</t>
+        </is>
+      </c>
+      <c r="H728" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I728" s="4" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B729" s="6" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C729" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D729" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E729" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F729" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G729" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260916033855405197.csv</t>
+        </is>
+      </c>
+      <c r="H729" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I729" s="7" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B730" s="3" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C730" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D730" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E730" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F730" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G730" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260916033855555152.pdf</t>
+        </is>
+      </c>
+      <c r="H730" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I730" s="4" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B731" s="6" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C731" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D731" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E731" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F731" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G731" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260916033855703702.docx</t>
+        </is>
+      </c>
+      <c r="H731" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I731" s="7" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B732" s="3" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C732" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D732" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E732" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F732" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G732" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260916033855883353.pptx</t>
+        </is>
+      </c>
+      <c r="H732" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I732" s="4" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B733" s="6" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C733" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D733" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E733" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F733" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G733" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260916033856032141.jpg</t>
+        </is>
+      </c>
+      <c r="H733" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I733" s="7" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B734" s="3" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C734" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D734" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E734" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F734" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G734" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260916033856181318.doc</t>
+        </is>
+      </c>
+      <c r="H734" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I734" s="4" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B735" s="6" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C735" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D735" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E735" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F735" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G735" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260916033856355077.txt</t>
+        </is>
+      </c>
+      <c r="H735" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I735" s="7" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B736" s="3" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C736" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D736" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E736" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F736" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G736" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260916033856505725.xls</t>
+        </is>
+      </c>
+      <c r="H736" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I736" s="4" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B737" s="6" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C737" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D737" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E737" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F737" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G737" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260916033856655522.png</t>
+        </is>
+      </c>
+      <c r="H737" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I737" s="7" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B738" s="3" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C738" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D738" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E738" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F738" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G738" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260916033856831646.dat</t>
+        </is>
+      </c>
+      <c r="H738" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I738" s="4" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B739" s="6" t="inlineStr">
+        <is>
+          <t>03:38:59</t>
+        </is>
+      </c>
+      <c r="C739" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D739" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E739" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F739" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G739" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260916033859216175.docx</t>
+        </is>
+      </c>
+      <c r="H739" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I739" s="7" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B740" s="3" t="inlineStr">
+        <is>
+          <t>03:38:59</t>
+        </is>
+      </c>
+      <c r="C740" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D740" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E740" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F740" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G740" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260916033859366077.pdf</t>
+        </is>
+      </c>
+      <c r="H740" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I740" s="4" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B741" s="6" t="inlineStr">
+        <is>
+          <t>03:38:59</t>
+        </is>
+      </c>
+      <c r="C741" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D741" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E741" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F741" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G741" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260916033859518461.jpeg</t>
+        </is>
+      </c>
+      <c r="H741" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I741" s="7" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B742" s="3" t="inlineStr">
+        <is>
+          <t>03:38:59</t>
+        </is>
+      </c>
+      <c r="C742" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D742" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E742" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F742" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G742" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260916033859701383.xlsx</t>
+        </is>
+      </c>
+      <c r="H742" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I742" s="4" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B743" s="6" t="inlineStr">
+        <is>
+          <t>03:39:00</t>
+        </is>
+      </c>
+      <c r="C743" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D743" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E743" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F743" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G743" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260916033900223875.txt</t>
+        </is>
+      </c>
+      <c r="H743" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I743" s="7" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B744" s="3" t="inlineStr">
+        <is>
+          <t>03:39:00</t>
+        </is>
+      </c>
+      <c r="C744" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D744" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E744" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F744" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G744" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260916033900376157.xlsx</t>
+        </is>
+      </c>
+      <c r="H744" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I744" s="4" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B745" s="6" t="inlineStr">
+        <is>
+          <t>03:39:00</t>
+        </is>
+      </c>
+      <c r="C745" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D745" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E745" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F745" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G745" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H745" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I745" s="7" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B746" s="3" t="inlineStr">
+        <is>
+          <t>03:39:01</t>
+        </is>
+      </c>
+      <c r="C746" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D746" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E746" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F746" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G746" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260916033901352890.pdf</t>
+        </is>
+      </c>
+      <c r="H746" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I746" s="4" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B747" s="6" t="inlineStr">
+        <is>
+          <t>03:39:01</t>
+        </is>
+      </c>
+      <c r="C747" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D747" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E747" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F747" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G747" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260916033901505419.jpeg</t>
+        </is>
+      </c>
+      <c r="H747" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I747" s="7" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B748" s="3" t="inlineStr">
+        <is>
+          <t>03:39:01</t>
+        </is>
+      </c>
+      <c r="C748" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D748" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E748" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F748" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G748" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260916033901686561.pages</t>
+        </is>
+      </c>
+      <c r="H748" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I748" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I748"/>
+  <dimension ref="A1:I771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32663,6 +32663,995 @@
       </c>
       <c r="I748" s="4" t="inlineStr"/>
     </row>
+    <row r="749">
+      <c r="A749" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B749" s="6" t="inlineStr">
+        <is>
+          <t>04:25:33</t>
+        </is>
+      </c>
+      <c r="C749" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D749" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E749" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F749" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G749" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260916042533972487.gif</t>
+        </is>
+      </c>
+      <c r="H749" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I749" s="7" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B750" s="3" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C750" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D750" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E750" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F750" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G750" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260916042534099523.xlsx</t>
+        </is>
+      </c>
+      <c r="H750" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I750" s="4" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B751" s="6" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C751" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D751" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E751" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F751" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G751" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260916042534217072.csv</t>
+        </is>
+      </c>
+      <c r="H751" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I751" s="7" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B752" s="3" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C752" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D752" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E752" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F752" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G752" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260916042534334981.pdf</t>
+        </is>
+      </c>
+      <c r="H752" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I752" s="4" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B753" s="6" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C753" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D753" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E753" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F753" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G753" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260916042534451930.docx</t>
+        </is>
+      </c>
+      <c r="H753" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I753" s="7" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B754" s="3" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C754" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D754" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E754" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F754" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G754" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260916042534584442.pptx</t>
+        </is>
+      </c>
+      <c r="H754" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I754" s="4" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B755" s="6" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C755" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D755" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E755" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F755" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G755" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260916042534701834.jpg</t>
+        </is>
+      </c>
+      <c r="H755" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I755" s="7" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B756" s="3" t="inlineStr">
+        <is>
+          <t>04:25:34</t>
+        </is>
+      </c>
+      <c r="C756" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D756" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E756" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F756" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G756" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260916042534865361.doc</t>
+        </is>
+      </c>
+      <c r="H756" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I756" s="4" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B757" s="6" t="inlineStr">
+        <is>
+          <t>04:25:35</t>
+        </is>
+      </c>
+      <c r="C757" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D757" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E757" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F757" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G757" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260916042535140787.txt</t>
+        </is>
+      </c>
+      <c r="H757" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I757" s="7" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B758" s="3" t="inlineStr">
+        <is>
+          <t>04:25:35</t>
+        </is>
+      </c>
+      <c r="C758" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D758" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E758" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F758" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G758" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260916042535292512.xls</t>
+        </is>
+      </c>
+      <c r="H758" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I758" s="4" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B759" s="6" t="inlineStr">
+        <is>
+          <t>04:25:35</t>
+        </is>
+      </c>
+      <c r="C759" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D759" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E759" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F759" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G759" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260916042535480597.png</t>
+        </is>
+      </c>
+      <c r="H759" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I759" s="7" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B760" s="3" t="inlineStr">
+        <is>
+          <t>04:25:35</t>
+        </is>
+      </c>
+      <c r="C760" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D760" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E760" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F760" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G760" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260916042535652775.dat</t>
+        </is>
+      </c>
+      <c r="H760" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I760" s="4" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B761" s="6" t="inlineStr">
+        <is>
+          <t>04:25:37</t>
+        </is>
+      </c>
+      <c r="C761" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D761" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E761" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F761" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G761" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260916042537743273.docx</t>
+        </is>
+      </c>
+      <c r="H761" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I761" s="7" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B762" s="3" t="inlineStr">
+        <is>
+          <t>04:25:37</t>
+        </is>
+      </c>
+      <c r="C762" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D762" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E762" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F762" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G762" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260916042537863262.pdf</t>
+        </is>
+      </c>
+      <c r="H762" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I762" s="4" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B763" s="6" t="inlineStr">
+        <is>
+          <t>04:25:38</t>
+        </is>
+      </c>
+      <c r="C763" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D763" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E763" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F763" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G763" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260916042538000662.jpeg</t>
+        </is>
+      </c>
+      <c r="H763" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I763" s="7" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B764" s="3" t="inlineStr">
+        <is>
+          <t>04:25:38</t>
+        </is>
+      </c>
+      <c r="C764" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D764" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E764" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F764" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G764" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260916042538119374.xlsx</t>
+        </is>
+      </c>
+      <c r="H764" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I764" s="4" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B765" s="6" t="inlineStr">
+        <is>
+          <t>04:25:38</t>
+        </is>
+      </c>
+      <c r="C765" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D765" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E765" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F765" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G765" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260916042538415617.txt</t>
+        </is>
+      </c>
+      <c r="H765" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I765" s="7" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B766" s="3" t="inlineStr">
+        <is>
+          <t>04:25:38</t>
+        </is>
+      </c>
+      <c r="C766" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D766" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E766" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F766" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G766" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260916042538663048.xlsx</t>
+        </is>
+      </c>
+      <c r="H766" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I766" s="4" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B767" s="6" t="inlineStr">
+        <is>
+          <t>04:25:38</t>
+        </is>
+      </c>
+      <c r="C767" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D767" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E767" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F767" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G767" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H767" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I767" s="7" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B768" s="3" t="inlineStr">
+        <is>
+          <t>04:25:39</t>
+        </is>
+      </c>
+      <c r="C768" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D768" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E768" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F768" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G768" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260916042539457961.pdf</t>
+        </is>
+      </c>
+      <c r="H768" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I768" s="4" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B769" s="6" t="inlineStr">
+        <is>
+          <t>04:25:39</t>
+        </is>
+      </c>
+      <c r="C769" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D769" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E769" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F769" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G769" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260916042539578505.jpeg</t>
+        </is>
+      </c>
+      <c r="H769" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I769" s="7" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B770" s="3" t="inlineStr">
+        <is>
+          <t>04:25:39</t>
+        </is>
+      </c>
+      <c r="C770" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D770" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E770" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F770" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G770" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260916042539715184.pages</t>
+        </is>
+      </c>
+      <c r="H770" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I770" s="4" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B771" s="6" t="inlineStr">
+        <is>
+          <t>04:25:40</t>
+        </is>
+      </c>
+      <c r="C771" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D771" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E771" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F771" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G771" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1.pdf</t>
+        </is>
+      </c>
+      <c r="H771" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I771" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I771"/>
+  <dimension ref="A1:I794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33652,6 +33652,995 @@
       </c>
       <c r="I771" s="7" t="inlineStr"/>
     </row>
+    <row r="772">
+      <c r="A772" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B772" s="3" t="inlineStr">
+        <is>
+          <t>03:44:04</t>
+        </is>
+      </c>
+      <c r="C772" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D772" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E772" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F772" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G772" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260917034404528474.gif</t>
+        </is>
+      </c>
+      <c r="H772" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I772" s="4" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B773" s="6" t="inlineStr">
+        <is>
+          <t>03:44:04</t>
+        </is>
+      </c>
+      <c r="C773" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D773" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E773" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F773" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G773" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260917034404696652.xlsx</t>
+        </is>
+      </c>
+      <c r="H773" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I773" s="7" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B774" s="3" t="inlineStr">
+        <is>
+          <t>03:44:04</t>
+        </is>
+      </c>
+      <c r="C774" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D774" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E774" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F774" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G774" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260917034404847706.csv</t>
+        </is>
+      </c>
+      <c r="H774" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I774" s="4" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B775" s="6" t="inlineStr">
+        <is>
+          <t>03:44:04</t>
+        </is>
+      </c>
+      <c r="C775" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D775" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E775" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F775" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G775" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260917034404995715.pdf</t>
+        </is>
+      </c>
+      <c r="H775" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I775" s="7" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B776" s="3" t="inlineStr">
+        <is>
+          <t>03:44:05</t>
+        </is>
+      </c>
+      <c r="C776" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D776" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E776" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F776" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G776" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260917034405142854.docx</t>
+        </is>
+      </c>
+      <c r="H776" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I776" s="4" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B777" s="6" t="inlineStr">
+        <is>
+          <t>03:44:05</t>
+        </is>
+      </c>
+      <c r="C777" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D777" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E777" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F777" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G777" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260917034405322442.pptx</t>
+        </is>
+      </c>
+      <c r="H777" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I777" s="7" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B778" s="3" t="inlineStr">
+        <is>
+          <t>03:44:05</t>
+        </is>
+      </c>
+      <c r="C778" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D778" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E778" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F778" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G778" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260917034405485923.jpg</t>
+        </is>
+      </c>
+      <c r="H778" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I778" s="4" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B779" s="6" t="inlineStr">
+        <is>
+          <t>03:44:05</t>
+        </is>
+      </c>
+      <c r="C779" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D779" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E779" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F779" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G779" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260917034405800226.doc</t>
+        </is>
+      </c>
+      <c r="H779" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I779" s="7" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B780" s="3" t="inlineStr">
+        <is>
+          <t>03:44:05</t>
+        </is>
+      </c>
+      <c r="C780" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D780" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E780" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F780" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G780" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260917034405968157.txt</t>
+        </is>
+      </c>
+      <c r="H780" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I780" s="4" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B781" s="6" t="inlineStr">
+        <is>
+          <t>03:44:06</t>
+        </is>
+      </c>
+      <c r="C781" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D781" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E781" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F781" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G781" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260917034406117094.xls</t>
+        </is>
+      </c>
+      <c r="H781" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I781" s="7" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B782" s="3" t="inlineStr">
+        <is>
+          <t>03:44:06</t>
+        </is>
+      </c>
+      <c r="C782" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D782" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E782" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F782" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G782" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260917034406279853.png</t>
+        </is>
+      </c>
+      <c r="H782" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I782" s="4" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B783" s="6" t="inlineStr">
+        <is>
+          <t>03:44:06</t>
+        </is>
+      </c>
+      <c r="C783" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D783" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E783" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F783" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G783" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260917034406461206.dat</t>
+        </is>
+      </c>
+      <c r="H783" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I783" s="7" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B784" s="3" t="inlineStr">
+        <is>
+          <t>03:44:08</t>
+        </is>
+      </c>
+      <c r="C784" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D784" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E784" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F784" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G784" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260917034408374604.docx</t>
+        </is>
+      </c>
+      <c r="H784" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I784" s="4" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B785" s="6" t="inlineStr">
+        <is>
+          <t>03:44:08</t>
+        </is>
+      </c>
+      <c r="C785" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D785" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E785" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F785" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G785" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260917034408558334.pdf</t>
+        </is>
+      </c>
+      <c r="H785" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I785" s="7" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B786" s="3" t="inlineStr">
+        <is>
+          <t>03:44:09</t>
+        </is>
+      </c>
+      <c r="C786" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D786" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E786" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F786" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G786" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260917034409096509.jpeg</t>
+        </is>
+      </c>
+      <c r="H786" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I786" s="4" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B787" s="6" t="inlineStr">
+        <is>
+          <t>03:44:09</t>
+        </is>
+      </c>
+      <c r="C787" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D787" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E787" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F787" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G787" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260917034409262062.xlsx</t>
+        </is>
+      </c>
+      <c r="H787" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I787" s="7" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B788" s="3" t="inlineStr">
+        <is>
+          <t>03:44:10</t>
+        </is>
+      </c>
+      <c r="C788" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D788" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E788" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F788" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G788" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260917034410067736.txt</t>
+        </is>
+      </c>
+      <c r="H788" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I788" s="4" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B789" s="6" t="inlineStr">
+        <is>
+          <t>03:44:10</t>
+        </is>
+      </c>
+      <c r="C789" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D789" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E789" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F789" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G789" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260917034410252938.xlsx</t>
+        </is>
+      </c>
+      <c r="H789" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I789" s="7" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B790" s="3" t="inlineStr">
+        <is>
+          <t>03:44:10</t>
+        </is>
+      </c>
+      <c r="C790" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D790" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E790" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F790" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G790" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H790" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I790" s="4" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B791" s="6" t="inlineStr">
+        <is>
+          <t>03:44:11</t>
+        </is>
+      </c>
+      <c r="C791" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D791" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E791" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F791" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G791" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260917034411186039.pdf</t>
+        </is>
+      </c>
+      <c r="H791" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I791" s="7" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B792" s="3" t="inlineStr">
+        <is>
+          <t>03:44:11</t>
+        </is>
+      </c>
+      <c r="C792" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D792" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E792" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F792" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G792" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260917034411334824.jpeg</t>
+        </is>
+      </c>
+      <c r="H792" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I792" s="4" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B793" s="6" t="inlineStr">
+        <is>
+          <t>03:44:11</t>
+        </is>
+      </c>
+      <c r="C793" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D793" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E793" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F793" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G793" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260917034411520673.pages</t>
+        </is>
+      </c>
+      <c r="H793" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I793" s="7" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B794" s="3" t="inlineStr">
+        <is>
+          <t>03:44:12</t>
+        </is>
+      </c>
+      <c r="C794" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D794" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E794" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F794" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G794" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260917034412311111.pdf</t>
+        </is>
+      </c>
+      <c r="H794" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I794" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I794"/>
+  <dimension ref="A1:I817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34641,6 +34641,995 @@
       </c>
       <c r="I794" s="4" t="inlineStr"/>
     </row>
+    <row r="795">
+      <c r="A795" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B795" s="6" t="inlineStr">
+        <is>
+          <t>03:30:15</t>
+        </is>
+      </c>
+      <c r="C795" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D795" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E795" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F795" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G795" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260918033015193794.gif</t>
+        </is>
+      </c>
+      <c r="H795" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I795" s="7" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B796" s="3" t="inlineStr">
+        <is>
+          <t>03:30:15</t>
+        </is>
+      </c>
+      <c r="C796" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D796" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E796" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F796" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G796" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260918033015384175.xlsx</t>
+        </is>
+      </c>
+      <c r="H796" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I796" s="4" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B797" s="6" t="inlineStr">
+        <is>
+          <t>03:30:15</t>
+        </is>
+      </c>
+      <c r="C797" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D797" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E797" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F797" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G797" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260918033015562027.csv</t>
+        </is>
+      </c>
+      <c r="H797" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I797" s="7" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B798" s="3" t="inlineStr">
+        <is>
+          <t>03:30:15</t>
+        </is>
+      </c>
+      <c r="C798" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D798" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E798" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F798" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G798" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260918033015739708.pdf</t>
+        </is>
+      </c>
+      <c r="H798" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I798" s="4" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B799" s="6" t="inlineStr">
+        <is>
+          <t>03:30:15</t>
+        </is>
+      </c>
+      <c r="C799" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D799" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E799" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F799" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G799" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260918033015934229.docx</t>
+        </is>
+      </c>
+      <c r="H799" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I799" s="7" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B800" s="3" t="inlineStr">
+        <is>
+          <t>03:30:16</t>
+        </is>
+      </c>
+      <c r="C800" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D800" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E800" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F800" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G800" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260918033016113758.pptx</t>
+        </is>
+      </c>
+      <c r="H800" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I800" s="4" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B801" s="6" t="inlineStr">
+        <is>
+          <t>03:30:16</t>
+        </is>
+      </c>
+      <c r="C801" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D801" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E801" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F801" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G801" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260918033016294055.jpg</t>
+        </is>
+      </c>
+      <c r="H801" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I801" s="7" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B802" s="3" t="inlineStr">
+        <is>
+          <t>03:30:16</t>
+        </is>
+      </c>
+      <c r="C802" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D802" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E802" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F802" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G802" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260918033016471259.doc</t>
+        </is>
+      </c>
+      <c r="H802" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I802" s="4" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B803" s="6" t="inlineStr">
+        <is>
+          <t>03:30:16</t>
+        </is>
+      </c>
+      <c r="C803" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D803" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E803" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F803" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G803" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260918033016674049.txt</t>
+        </is>
+      </c>
+      <c r="H803" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I803" s="7" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B804" s="3" t="inlineStr">
+        <is>
+          <t>03:30:16</t>
+        </is>
+      </c>
+      <c r="C804" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D804" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E804" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F804" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G804" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260918033016851005.xls</t>
+        </is>
+      </c>
+      <c r="H804" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I804" s="4" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B805" s="6" t="inlineStr">
+        <is>
+          <t>03:30:17</t>
+        </is>
+      </c>
+      <c r="C805" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D805" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E805" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F805" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G805" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260918033017027309.png</t>
+        </is>
+      </c>
+      <c r="H805" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I805" s="7" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
+        <is>
+          <t>03:30:17</t>
+        </is>
+      </c>
+      <c r="C806" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D806" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E806" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F806" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G806" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260918033017220898.dat</t>
+        </is>
+      </c>
+      <c r="H806" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I806" s="4" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B807" s="6" t="inlineStr">
+        <is>
+          <t>03:30:18</t>
+        </is>
+      </c>
+      <c r="C807" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D807" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E807" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F807" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G807" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260918033018864953.docx</t>
+        </is>
+      </c>
+      <c r="H807" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I807" s="7" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
+        <is>
+          <t>03:30:19</t>
+        </is>
+      </c>
+      <c r="C808" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D808" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E808" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F808" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G808" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260918033019041605.pdf</t>
+        </is>
+      </c>
+      <c r="H808" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I808" s="4" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B809" s="6" t="inlineStr">
+        <is>
+          <t>03:30:19</t>
+        </is>
+      </c>
+      <c r="C809" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D809" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E809" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F809" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G809" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260918033019239405.jpeg</t>
+        </is>
+      </c>
+      <c r="H809" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I809" s="7" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>03:30:19</t>
+        </is>
+      </c>
+      <c r="C810" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D810" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E810" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F810" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G810" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260918033019417269.xlsx</t>
+        </is>
+      </c>
+      <c r="H810" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I810" s="4" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B811" s="6" t="inlineStr">
+        <is>
+          <t>03:30:19</t>
+        </is>
+      </c>
+      <c r="C811" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D811" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E811" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F811" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G811" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260918033019901180.txt</t>
+        </is>
+      </c>
+      <c r="H811" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I811" s="7" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>03:30:20</t>
+        </is>
+      </c>
+      <c r="C812" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D812" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E812" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F812" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G812" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260918033020095719.xlsx</t>
+        </is>
+      </c>
+      <c r="H812" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I812" s="4" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B813" s="6" t="inlineStr">
+        <is>
+          <t>03:30:20</t>
+        </is>
+      </c>
+      <c r="C813" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D813" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E813" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F813" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G813" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H813" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I813" s="7" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>03:30:20</t>
+        </is>
+      </c>
+      <c r="C814" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D814" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E814" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G814" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260918033020673170.pdf</t>
+        </is>
+      </c>
+      <c r="H814" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I814" s="4" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B815" s="6" t="inlineStr">
+        <is>
+          <t>03:30:20</t>
+        </is>
+      </c>
+      <c r="C815" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D815" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E815" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F815" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G815" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260918033020867911.jpeg</t>
+        </is>
+      </c>
+      <c r="H815" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I815" s="7" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
+        <is>
+          <t>03:30:21</t>
+        </is>
+      </c>
+      <c r="C816" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D816" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E816" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F816" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G816" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260918033021048034.pages</t>
+        </is>
+      </c>
+      <c r="H816" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I816" s="4" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B817" s="6" t="inlineStr">
+        <is>
+          <t>03:30:21</t>
+        </is>
+      </c>
+      <c r="C817" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D817" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E817" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F817" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G817" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260918033021665224.pdf</t>
+        </is>
+      </c>
+      <c r="H817" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I817" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I817"/>
+  <dimension ref="A1:I840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35630,6 +35630,995 @@
       </c>
       <c r="I817" s="7" t="inlineStr"/>
     </row>
+    <row r="818">
+      <c r="A818" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
+        <is>
+          <t>03:27:04</t>
+        </is>
+      </c>
+      <c r="C818" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D818" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E818" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F818" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G818" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260919032704093156.gif</t>
+        </is>
+      </c>
+      <c r="H818" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I818" s="4" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B819" s="6" t="inlineStr">
+        <is>
+          <t>03:27:04</t>
+        </is>
+      </c>
+      <c r="C819" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D819" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E819" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F819" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G819" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260919032704260867.xlsx</t>
+        </is>
+      </c>
+      <c r="H819" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I819" s="7" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>03:27:04</t>
+        </is>
+      </c>
+      <c r="C820" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D820" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E820" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F820" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G820" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260919032704420519.csv</t>
+        </is>
+      </c>
+      <c r="H820" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I820" s="4" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B821" s="6" t="inlineStr">
+        <is>
+          <t>03:27:04</t>
+        </is>
+      </c>
+      <c r="C821" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D821" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E821" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F821" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G821" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260919032704581091.pdf</t>
+        </is>
+      </c>
+      <c r="H821" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I821" s="7" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>03:27:04</t>
+        </is>
+      </c>
+      <c r="C822" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D822" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E822" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F822" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G822" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260919032704760931.docx</t>
+        </is>
+      </c>
+      <c r="H822" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I822" s="4" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B823" s="6" t="inlineStr">
+        <is>
+          <t>03:27:04</t>
+        </is>
+      </c>
+      <c r="C823" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D823" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E823" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F823" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G823" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260919032704919446.pptx</t>
+        </is>
+      </c>
+      <c r="H823" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I823" s="7" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>03:27:05</t>
+        </is>
+      </c>
+      <c r="C824" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D824" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E824" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G824" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260919032705077858.jpg</t>
+        </is>
+      </c>
+      <c r="H824" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I824" s="4" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B825" s="6" t="inlineStr">
+        <is>
+          <t>03:27:05</t>
+        </is>
+      </c>
+      <c r="C825" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D825" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E825" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F825" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G825" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260919032705257379.doc</t>
+        </is>
+      </c>
+      <c r="H825" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I825" s="7" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
+        <is>
+          <t>03:27:05</t>
+        </is>
+      </c>
+      <c r="C826" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D826" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E826" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G826" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260919032705416489.txt</t>
+        </is>
+      </c>
+      <c r="H826" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I826" s="4" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B827" s="6" t="inlineStr">
+        <is>
+          <t>03:27:05</t>
+        </is>
+      </c>
+      <c r="C827" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D827" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E827" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F827" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G827" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260919032705575875.xls</t>
+        </is>
+      </c>
+      <c r="H827" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I827" s="7" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>03:27:05</t>
+        </is>
+      </c>
+      <c r="C828" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D828" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E828" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F828" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G828" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260919032705755825.png</t>
+        </is>
+      </c>
+      <c r="H828" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I828" s="4" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B829" s="6" t="inlineStr">
+        <is>
+          <t>03:27:05</t>
+        </is>
+      </c>
+      <c r="C829" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D829" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E829" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F829" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G829" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260919032705914631.dat</t>
+        </is>
+      </c>
+      <c r="H829" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I829" s="7" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>03:27:07</t>
+        </is>
+      </c>
+      <c r="C830" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D830" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E830" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G830" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260919032707586569.docx</t>
+        </is>
+      </c>
+      <c r="H830" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I830" s="4" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B831" s="6" t="inlineStr">
+        <is>
+          <t>03:27:07</t>
+        </is>
+      </c>
+      <c r="C831" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D831" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E831" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F831" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G831" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260919032707769525.pdf</t>
+        </is>
+      </c>
+      <c r="H831" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I831" s="7" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>03:27:07</t>
+        </is>
+      </c>
+      <c r="C832" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D832" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E832" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G832" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260919032707931766.jpeg</t>
+        </is>
+      </c>
+      <c r="H832" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I832" s="4" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B833" s="6" t="inlineStr">
+        <is>
+          <t>03:27:08</t>
+        </is>
+      </c>
+      <c r="C833" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D833" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E833" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F833" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G833" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260919032708092844.xlsx</t>
+        </is>
+      </c>
+      <c r="H833" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I833" s="7" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>03:27:08</t>
+        </is>
+      </c>
+      <c r="C834" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D834" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E834" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G834" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260919032708591419.txt</t>
+        </is>
+      </c>
+      <c r="H834" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I834" s="4" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B835" s="6" t="inlineStr">
+        <is>
+          <t>03:27:08</t>
+        </is>
+      </c>
+      <c r="C835" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D835" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E835" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F835" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G835" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260919032708752607.xlsx</t>
+        </is>
+      </c>
+      <c r="H835" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I835" s="7" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>03:27:08</t>
+        </is>
+      </c>
+      <c r="C836" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D836" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E836" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G836" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H836" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I836" s="4" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B837" s="6" t="inlineStr">
+        <is>
+          <t>03:27:09</t>
+        </is>
+      </c>
+      <c r="C837" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D837" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E837" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F837" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G837" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260919032709377384.pdf</t>
+        </is>
+      </c>
+      <c r="H837" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I837" s="7" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
+        <is>
+          <t>03:27:09</t>
+        </is>
+      </c>
+      <c r="C838" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D838" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E838" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F838" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G838" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260919032709539126.jpeg</t>
+        </is>
+      </c>
+      <c r="H838" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I838" s="4" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B839" s="6" t="inlineStr">
+        <is>
+          <t>03:27:09</t>
+        </is>
+      </c>
+      <c r="C839" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D839" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E839" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F839" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G839" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260919032709701879.pages</t>
+        </is>
+      </c>
+      <c r="H839" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I839" s="7" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>03:27:10</t>
+        </is>
+      </c>
+      <c r="C840" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D840" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E840" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F840" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G840" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260919032710434682.pdf</t>
+        </is>
+      </c>
+      <c r="H840" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I840" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I840"/>
+  <dimension ref="A1:I863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36619,6 +36619,995 @@
       </c>
       <c r="I840" s="4" t="inlineStr"/>
     </row>
+    <row r="841">
+      <c r="A841" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B841" s="6" t="inlineStr">
+        <is>
+          <t>03:43:41</t>
+        </is>
+      </c>
+      <c r="C841" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D841" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E841" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F841" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G841" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260920034341278720.gif</t>
+        </is>
+      </c>
+      <c r="H841" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I841" s="7" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
+        <is>
+          <t>03:43:41</t>
+        </is>
+      </c>
+      <c r="C842" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D842" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E842" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G842" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260920034341475346.xlsx</t>
+        </is>
+      </c>
+      <c r="H842" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I842" s="4" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B843" s="6" t="inlineStr">
+        <is>
+          <t>03:43:41</t>
+        </is>
+      </c>
+      <c r="C843" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D843" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E843" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F843" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G843" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260920034341660093.csv</t>
+        </is>
+      </c>
+      <c r="H843" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I843" s="7" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>03:43:41</t>
+        </is>
+      </c>
+      <c r="C844" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D844" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E844" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G844" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260920034341848698.pdf</t>
+        </is>
+      </c>
+      <c r="H844" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I844" s="4" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B845" s="6" t="inlineStr">
+        <is>
+          <t>03:43:42</t>
+        </is>
+      </c>
+      <c r="C845" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D845" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E845" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F845" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G845" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260920034342061099.docx</t>
+        </is>
+      </c>
+      <c r="H845" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I845" s="7" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
+        <is>
+          <t>03:43:42</t>
+        </is>
+      </c>
+      <c r="C846" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D846" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E846" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G846" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260920034342249168.pptx</t>
+        </is>
+      </c>
+      <c r="H846" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I846" s="4" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B847" s="6" t="inlineStr">
+        <is>
+          <t>03:43:42</t>
+        </is>
+      </c>
+      <c r="C847" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D847" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E847" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F847" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G847" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260920034342436596.jpg</t>
+        </is>
+      </c>
+      <c r="H847" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I847" s="7" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
+        <is>
+          <t>03:43:42</t>
+        </is>
+      </c>
+      <c r="C848" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D848" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E848" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G848" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260920034342642856.doc</t>
+        </is>
+      </c>
+      <c r="H848" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I848" s="4" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B849" s="6" t="inlineStr">
+        <is>
+          <t>03:43:42</t>
+        </is>
+      </c>
+      <c r="C849" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D849" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E849" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F849" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G849" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260920034342825287.txt</t>
+        </is>
+      </c>
+      <c r="H849" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I849" s="7" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>03:43:43</t>
+        </is>
+      </c>
+      <c r="C850" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D850" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E850" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G850" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260920034343009186.xls</t>
+        </is>
+      </c>
+      <c r="H850" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I850" s="4" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B851" s="6" t="inlineStr">
+        <is>
+          <t>03:43:43</t>
+        </is>
+      </c>
+      <c r="C851" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D851" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E851" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F851" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G851" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260920034343218675.png</t>
+        </is>
+      </c>
+      <c r="H851" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I851" s="7" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>03:43:43</t>
+        </is>
+      </c>
+      <c r="C852" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D852" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E852" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F852" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G852" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260920034343409014.dat</t>
+        </is>
+      </c>
+      <c r="H852" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I852" s="4" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B853" s="6" t="inlineStr">
+        <is>
+          <t>03:43:44</t>
+        </is>
+      </c>
+      <c r="C853" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D853" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E853" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F853" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G853" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260920034344461617.docx</t>
+        </is>
+      </c>
+      <c r="H853" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I853" s="7" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>03:43:44</t>
+        </is>
+      </c>
+      <c r="C854" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D854" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E854" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G854" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260920034344670447.pdf</t>
+        </is>
+      </c>
+      <c r="H854" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I854" s="4" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B855" s="6" t="inlineStr">
+        <is>
+          <t>03:43:44</t>
+        </is>
+      </c>
+      <c r="C855" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D855" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E855" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F855" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G855" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260920034344862552.jpeg</t>
+        </is>
+      </c>
+      <c r="H855" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I855" s="7" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
+        <is>
+          <t>03:43:45</t>
+        </is>
+      </c>
+      <c r="C856" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D856" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E856" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G856" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260920034345050698.xlsx</t>
+        </is>
+      </c>
+      <c r="H856" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I856" s="4" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B857" s="6" t="inlineStr">
+        <is>
+          <t>03:43:45</t>
+        </is>
+      </c>
+      <c r="C857" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D857" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E857" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F857" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G857" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260920034345520138.txt</t>
+        </is>
+      </c>
+      <c r="H857" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I857" s="7" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>03:43:45</t>
+        </is>
+      </c>
+      <c r="C858" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D858" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E858" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G858" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260920034345706144.xlsx</t>
+        </is>
+      </c>
+      <c r="H858" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I858" s="4" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B859" s="6" t="inlineStr">
+        <is>
+          <t>03:43:45</t>
+        </is>
+      </c>
+      <c r="C859" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D859" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E859" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F859" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G859" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H859" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I859" s="7" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
+        <is>
+          <t>03:43:46</t>
+        </is>
+      </c>
+      <c r="C860" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D860" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E860" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F860" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G860" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260920034346287357.pdf</t>
+        </is>
+      </c>
+      <c r="H860" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I860" s="4" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B861" s="6" t="inlineStr">
+        <is>
+          <t>03:43:46</t>
+        </is>
+      </c>
+      <c r="C861" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D861" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E861" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F861" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G861" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260920034346476723.jpeg</t>
+        </is>
+      </c>
+      <c r="H861" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I861" s="7" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>03:43:46</t>
+        </is>
+      </c>
+      <c r="C862" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D862" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E862" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G862" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260920034346665075.pages</t>
+        </is>
+      </c>
+      <c r="H862" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I862" s="4" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B863" s="6" t="inlineStr">
+        <is>
+          <t>03:43:47</t>
+        </is>
+      </c>
+      <c r="C863" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D863" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E863" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F863" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G863" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260920034347122081.pdf</t>
+        </is>
+      </c>
+      <c r="H863" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I863" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I863"/>
+  <dimension ref="A1:I886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37608,6 +37608,995 @@
       </c>
       <c r="I863" s="7" t="inlineStr"/>
     </row>
+    <row r="864">
+      <c r="A864" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C864" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D864" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E864" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F864" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G864" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260921033918141274.gif</t>
+        </is>
+      </c>
+      <c r="H864" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I864" s="4" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B865" s="6" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C865" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D865" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E865" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F865" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G865" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260921033918361773.xlsx</t>
+        </is>
+      </c>
+      <c r="H865" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I865" s="7" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C866" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D866" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E866" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F866" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G866" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260921033918553944.csv</t>
+        </is>
+      </c>
+      <c r="H866" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I866" s="4" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B867" s="6" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C867" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D867" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E867" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F867" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G867" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260921033918746094.pdf</t>
+        </is>
+      </c>
+      <c r="H867" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I867" s="7" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C868" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D868" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E868" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G868" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260921033918959183.docx</t>
+        </is>
+      </c>
+      <c r="H868" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I868" s="4" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B869" s="6" t="inlineStr">
+        <is>
+          <t>03:39:19</t>
+        </is>
+      </c>
+      <c r="C869" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D869" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E869" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F869" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G869" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260921033919149451.pptx</t>
+        </is>
+      </c>
+      <c r="H869" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I869" s="7" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>03:39:19</t>
+        </is>
+      </c>
+      <c r="C870" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D870" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E870" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F870" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G870" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260921033919340195.jpg</t>
+        </is>
+      </c>
+      <c r="H870" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I870" s="4" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B871" s="6" t="inlineStr">
+        <is>
+          <t>03:39:19</t>
+        </is>
+      </c>
+      <c r="C871" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D871" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E871" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F871" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G871" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260921033919555814.doc</t>
+        </is>
+      </c>
+      <c r="H871" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I871" s="7" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>03:39:19</t>
+        </is>
+      </c>
+      <c r="C872" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D872" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E872" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G872" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260921033919748235.txt</t>
+        </is>
+      </c>
+      <c r="H872" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I872" s="4" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B873" s="6" t="inlineStr">
+        <is>
+          <t>03:39:19</t>
+        </is>
+      </c>
+      <c r="C873" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D873" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E873" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F873" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G873" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260921033919938172.xls</t>
+        </is>
+      </c>
+      <c r="H873" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I873" s="7" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>03:39:20</t>
+        </is>
+      </c>
+      <c r="C874" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D874" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E874" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F874" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G874" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260921033920146148.png</t>
+        </is>
+      </c>
+      <c r="H874" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I874" s="4" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B875" s="6" t="inlineStr">
+        <is>
+          <t>03:39:20</t>
+        </is>
+      </c>
+      <c r="C875" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D875" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E875" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F875" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G875" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260921033920335316.dat</t>
+        </is>
+      </c>
+      <c r="H875" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I875" s="7" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>03:39:21</t>
+        </is>
+      </c>
+      <c r="C876" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D876" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E876" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G876" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260921033921777814.docx</t>
+        </is>
+      </c>
+      <c r="H876" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I876" s="4" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B877" s="6" t="inlineStr">
+        <is>
+          <t>03:39:21</t>
+        </is>
+      </c>
+      <c r="C877" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D877" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E877" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F877" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G877" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260921033921994153.pdf</t>
+        </is>
+      </c>
+      <c r="H877" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I877" s="7" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>03:39:22</t>
+        </is>
+      </c>
+      <c r="C878" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D878" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E878" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F878" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G878" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260921033922192029.jpeg</t>
+        </is>
+      </c>
+      <c r="H878" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I878" s="4" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B879" s="6" t="inlineStr">
+        <is>
+          <t>03:39:22</t>
+        </is>
+      </c>
+      <c r="C879" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D879" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E879" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F879" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G879" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260921033922399770.xlsx</t>
+        </is>
+      </c>
+      <c r="H879" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I879" s="7" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>03:39:22</t>
+        </is>
+      </c>
+      <c r="C880" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D880" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E880" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G880" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260921033922883811.txt</t>
+        </is>
+      </c>
+      <c r="H880" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I880" s="4" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B881" s="6" t="inlineStr">
+        <is>
+          <t>03:39:23</t>
+        </is>
+      </c>
+      <c r="C881" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D881" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E881" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F881" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G881" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260921033923077851.xlsx</t>
+        </is>
+      </c>
+      <c r="H881" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I881" s="7" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>03:39:23</t>
+        </is>
+      </c>
+      <c r="C882" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D882" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E882" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G882" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H882" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I882" s="4" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B883" s="6" t="inlineStr">
+        <is>
+          <t>03:39:23</t>
+        </is>
+      </c>
+      <c r="C883" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D883" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E883" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F883" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G883" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260921033923771600.pdf</t>
+        </is>
+      </c>
+      <c r="H883" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I883" s="7" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>03:39:23</t>
+        </is>
+      </c>
+      <c r="C884" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D884" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E884" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F884" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G884" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260921033923966923.jpeg</t>
+        </is>
+      </c>
+      <c r="H884" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I884" s="4" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B885" s="6" t="inlineStr">
+        <is>
+          <t>03:39:24</t>
+        </is>
+      </c>
+      <c r="C885" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D885" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E885" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F885" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G885" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260921033924188197.pages</t>
+        </is>
+      </c>
+      <c r="H885" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I885" s="7" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>03:39:24</t>
+        </is>
+      </c>
+      <c r="C886" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D886" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E886" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F886" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G886" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260921033924797138.pdf</t>
+        </is>
+      </c>
+      <c r="H886" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I886" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I886"/>
+  <dimension ref="A1:I909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38597,6 +38597,995 @@
       </c>
       <c r="I886" s="4" t="inlineStr"/>
     </row>
+    <row r="887">
+      <c r="A887" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B887" s="6" t="inlineStr">
+        <is>
+          <t>03:37:29</t>
+        </is>
+      </c>
+      <c r="C887" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D887" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E887" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F887" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G887" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260922033729599803.gif</t>
+        </is>
+      </c>
+      <c r="H887" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I887" s="7" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>03:37:29</t>
+        </is>
+      </c>
+      <c r="C888" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D888" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E888" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F888" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G888" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260922033729729035.xlsx</t>
+        </is>
+      </c>
+      <c r="H888" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I888" s="4" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B889" s="6" t="inlineStr">
+        <is>
+          <t>03:37:29</t>
+        </is>
+      </c>
+      <c r="C889" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D889" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E889" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F889" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G889" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260922033729831420.csv</t>
+        </is>
+      </c>
+      <c r="H889" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I889" s="7" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>03:37:29</t>
+        </is>
+      </c>
+      <c r="C890" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D890" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E890" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F890" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G890" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260922033729937474.pdf</t>
+        </is>
+      </c>
+      <c r="H890" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I890" s="4" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B891" s="6" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C891" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D891" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E891" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F891" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G891" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260922033730065280.docx</t>
+        </is>
+      </c>
+      <c r="H891" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I891" s="7" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B892" s="3" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C892" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D892" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E892" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F892" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G892" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260922033730169784.pptx</t>
+        </is>
+      </c>
+      <c r="H892" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I892" s="4" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B893" s="6" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C893" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D893" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E893" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F893" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G893" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260922033730273885.jpg</t>
+        </is>
+      </c>
+      <c r="H893" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I893" s="7" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C894" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D894" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E894" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F894" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G894" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260922033730420552.doc</t>
+        </is>
+      </c>
+      <c r="H894" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I894" s="4" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B895" s="6" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C895" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D895" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E895" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F895" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G895" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260922033730527907.txt</t>
+        </is>
+      </c>
+      <c r="H895" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I895" s="7" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C896" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D896" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E896" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F896" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G896" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260922033730632198.xls</t>
+        </is>
+      </c>
+      <c r="H896" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I896" s="4" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B897" s="6" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C897" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D897" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E897" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F897" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G897" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260922033730766723.png</t>
+        </is>
+      </c>
+      <c r="H897" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I897" s="7" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>03:37:30</t>
+        </is>
+      </c>
+      <c r="C898" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D898" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E898" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F898" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G898" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260922033730874263.dat</t>
+        </is>
+      </c>
+      <c r="H898" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I898" s="4" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B899" s="6" t="inlineStr">
+        <is>
+          <t>03:37:32</t>
+        </is>
+      </c>
+      <c r="C899" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D899" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E899" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F899" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G899" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260922033732193390.docx</t>
+        </is>
+      </c>
+      <c r="H899" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I899" s="7" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>03:37:32</t>
+        </is>
+      </c>
+      <c r="C900" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D900" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E900" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F900" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G900" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260922033732303009.pdf</t>
+        </is>
+      </c>
+      <c r="H900" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I900" s="4" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B901" s="6" t="inlineStr">
+        <is>
+          <t>03:37:32</t>
+        </is>
+      </c>
+      <c r="C901" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D901" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E901" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F901" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G901" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260922033732441074.jpeg</t>
+        </is>
+      </c>
+      <c r="H901" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I901" s="7" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B902" s="3" t="inlineStr">
+        <is>
+          <t>03:37:32</t>
+        </is>
+      </c>
+      <c r="C902" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D902" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E902" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F902" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G902" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260922033732584022.xlsx</t>
+        </is>
+      </c>
+      <c r="H902" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I902" s="4" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B903" s="6" t="inlineStr">
+        <is>
+          <t>03:37:32</t>
+        </is>
+      </c>
+      <c r="C903" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D903" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E903" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F903" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G903" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260922033732964454.txt</t>
+        </is>
+      </c>
+      <c r="H903" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I903" s="7" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
+        <is>
+          <t>03:37:33</t>
+        </is>
+      </c>
+      <c r="C904" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D904" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E904" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F904" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G904" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260922033733076897.xlsx</t>
+        </is>
+      </c>
+      <c r="H904" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I904" s="4" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B905" s="6" t="inlineStr">
+        <is>
+          <t>03:37:33</t>
+        </is>
+      </c>
+      <c r="C905" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D905" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E905" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F905" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G905" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H905" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I905" s="7" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B906" s="3" t="inlineStr">
+        <is>
+          <t>03:37:33</t>
+        </is>
+      </c>
+      <c r="C906" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D906" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E906" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F906" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G906" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260922033733765969.pdf</t>
+        </is>
+      </c>
+      <c r="H906" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I906" s="4" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B907" s="6" t="inlineStr">
+        <is>
+          <t>03:37:34</t>
+        </is>
+      </c>
+      <c r="C907" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D907" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E907" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F907" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G907" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260922033734037066.jpeg</t>
+        </is>
+      </c>
+      <c r="H907" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I907" s="7" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>03:37:34</t>
+        </is>
+      </c>
+      <c r="C908" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E908" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F908" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G908" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260922033734394334.pages</t>
+        </is>
+      </c>
+      <c r="H908" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I908" s="4" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B909" s="6" t="inlineStr">
+        <is>
+          <t>03:37:35</t>
+        </is>
+      </c>
+      <c r="C909" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D909" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E909" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F909" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G909" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260922033735058004.pdf</t>
+        </is>
+      </c>
+      <c r="H909" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I909" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I909"/>
+  <dimension ref="A1:I932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39586,6 +39586,995 @@
       </c>
       <c r="I909" s="7" t="inlineStr"/>
     </row>
+    <row r="910">
+      <c r="A910" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B910" s="3" t="inlineStr">
+        <is>
+          <t>03:37:12</t>
+        </is>
+      </c>
+      <c r="C910" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D910" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E910" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F910" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G910" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260923033712016288.gif</t>
+        </is>
+      </c>
+      <c r="H910" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I910" s="4" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B911" s="6" t="inlineStr">
+        <is>
+          <t>03:37:12</t>
+        </is>
+      </c>
+      <c r="C911" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D911" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E911" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F911" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G911" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260923033712214792.xlsx</t>
+        </is>
+      </c>
+      <c r="H911" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I911" s="7" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B912" s="3" t="inlineStr">
+        <is>
+          <t>03:37:12</t>
+        </is>
+      </c>
+      <c r="C912" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D912" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E912" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F912" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G912" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260923033712398879.csv</t>
+        </is>
+      </c>
+      <c r="H912" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I912" s="4" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B913" s="6" t="inlineStr">
+        <is>
+          <t>03:37:12</t>
+        </is>
+      </c>
+      <c r="C913" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D913" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E913" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F913" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G913" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260923033712583201.pdf</t>
+        </is>
+      </c>
+      <c r="H913" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I913" s="7" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>03:37:12</t>
+        </is>
+      </c>
+      <c r="C914" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D914" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E914" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F914" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G914" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260923033712795455.docx</t>
+        </is>
+      </c>
+      <c r="H914" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I914" s="4" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B915" s="6" t="inlineStr">
+        <is>
+          <t>03:37:12</t>
+        </is>
+      </c>
+      <c r="C915" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D915" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E915" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F915" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G915" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260923033712979426.pptx</t>
+        </is>
+      </c>
+      <c r="H915" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I915" s="7" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>03:37:13</t>
+        </is>
+      </c>
+      <c r="C916" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D916" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E916" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F916" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G916" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260923033713162425.jpg</t>
+        </is>
+      </c>
+      <c r="H916" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I916" s="4" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B917" s="6" t="inlineStr">
+        <is>
+          <t>03:37:13</t>
+        </is>
+      </c>
+      <c r="C917" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D917" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E917" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F917" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G917" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260923033713374699.doc</t>
+        </is>
+      </c>
+      <c r="H917" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I917" s="7" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
+        <is>
+          <t>03:37:13</t>
+        </is>
+      </c>
+      <c r="C918" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D918" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E918" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F918" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G918" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260923033713559294.txt</t>
+        </is>
+      </c>
+      <c r="H918" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I918" s="4" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B919" s="6" t="inlineStr">
+        <is>
+          <t>03:37:13</t>
+        </is>
+      </c>
+      <c r="C919" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D919" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E919" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F919" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G919" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260923033713775787.xls</t>
+        </is>
+      </c>
+      <c r="H919" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I919" s="7" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B920" s="3" t="inlineStr">
+        <is>
+          <t>03:37:13</t>
+        </is>
+      </c>
+      <c r="C920" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D920" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E920" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F920" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G920" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260923033713969130.png</t>
+        </is>
+      </c>
+      <c r="H920" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I920" s="4" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B921" s="6" t="inlineStr">
+        <is>
+          <t>03:37:14</t>
+        </is>
+      </c>
+      <c r="C921" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D921" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E921" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F921" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G921" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260923033714152653.dat</t>
+        </is>
+      </c>
+      <c r="H921" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I921" s="7" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B922" s="3" t="inlineStr">
+        <is>
+          <t>03:37:15</t>
+        </is>
+      </c>
+      <c r="C922" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D922" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E922" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F922" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G922" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260923033715821586.docx</t>
+        </is>
+      </c>
+      <c r="H922" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I922" s="4" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B923" s="6" t="inlineStr">
+        <is>
+          <t>03:37:16</t>
+        </is>
+      </c>
+      <c r="C923" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D923" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E923" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F923" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G923" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260923033716006709.pdf</t>
+        </is>
+      </c>
+      <c r="H923" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I923" s="7" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B924" s="3" t="inlineStr">
+        <is>
+          <t>03:37:16</t>
+        </is>
+      </c>
+      <c r="C924" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D924" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E924" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F924" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G924" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260923033716192022.jpeg</t>
+        </is>
+      </c>
+      <c r="H924" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I924" s="4" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B925" s="6" t="inlineStr">
+        <is>
+          <t>03:37:16</t>
+        </is>
+      </c>
+      <c r="C925" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D925" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E925" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F925" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G925" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260923033716412108.xlsx</t>
+        </is>
+      </c>
+      <c r="H925" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I925" s="7" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
+        <is>
+          <t>03:37:16</t>
+        </is>
+      </c>
+      <c r="C926" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D926" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E926" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F926" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G926" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260923033716887112.txt</t>
+        </is>
+      </c>
+      <c r="H926" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I926" s="4" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B927" s="6" t="inlineStr">
+        <is>
+          <t>03:37:17</t>
+        </is>
+      </c>
+      <c r="C927" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D927" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E927" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F927" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G927" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260923033717097214.xlsx</t>
+        </is>
+      </c>
+      <c r="H927" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I927" s="7" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B928" s="3" t="inlineStr">
+        <is>
+          <t>03:37:17</t>
+        </is>
+      </c>
+      <c r="C928" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D928" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E928" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F928" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G928" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H928" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I928" s="4" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B929" s="6" t="inlineStr">
+        <is>
+          <t>03:37:17</t>
+        </is>
+      </c>
+      <c r="C929" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D929" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E929" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F929" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G929" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260923033717728075.pdf</t>
+        </is>
+      </c>
+      <c r="H929" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I929" s="7" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B930" s="3" t="inlineStr">
+        <is>
+          <t>03:37:17</t>
+        </is>
+      </c>
+      <c r="C930" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D930" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E930" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F930" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G930" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260923033717945529.jpeg</t>
+        </is>
+      </c>
+      <c r="H930" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I930" s="4" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B931" s="6" t="inlineStr">
+        <is>
+          <t>03:37:18</t>
+        </is>
+      </c>
+      <c r="C931" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D931" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E931" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F931" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G931" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260923033718131256.pages</t>
+        </is>
+      </c>
+      <c r="H931" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I931" s="7" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B932" s="3" t="inlineStr">
+        <is>
+          <t>03:37:18</t>
+        </is>
+      </c>
+      <c r="C932" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D932" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E932" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F932" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G932" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260923033718736945.pdf</t>
+        </is>
+      </c>
+      <c r="H932" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I932" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I932"/>
+  <dimension ref="A1:I955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40575,6 +40575,995 @@
       </c>
       <c r="I932" s="4" t="inlineStr"/>
     </row>
+    <row r="933">
+      <c r="A933" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B933" s="6" t="inlineStr">
+        <is>
+          <t>03:27:45</t>
+        </is>
+      </c>
+      <c r="C933" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D933" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E933" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F933" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G933" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260924032745586104.gif</t>
+        </is>
+      </c>
+      <c r="H933" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I933" s="7" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B934" s="3" t="inlineStr">
+        <is>
+          <t>03:27:45</t>
+        </is>
+      </c>
+      <c r="C934" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D934" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E934" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F934" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G934" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260924032745740372.xlsx</t>
+        </is>
+      </c>
+      <c r="H934" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I934" s="4" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B935" s="6" t="inlineStr">
+        <is>
+          <t>03:27:45</t>
+        </is>
+      </c>
+      <c r="C935" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D935" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E935" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F935" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G935" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260924032745885583.csv</t>
+        </is>
+      </c>
+      <c r="H935" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I935" s="7" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B936" s="3" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C936" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D936" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E936" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F936" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G936" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260924032746056377.pdf</t>
+        </is>
+      </c>
+      <c r="H936" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I936" s="4" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B937" s="6" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C937" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D937" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E937" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F937" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G937" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260924032746216767.docx</t>
+        </is>
+      </c>
+      <c r="H937" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I937" s="7" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C938" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D938" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E938" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F938" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G938" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260924032746361705.pptx</t>
+        </is>
+      </c>
+      <c r="H938" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I938" s="4" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B939" s="6" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C939" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D939" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E939" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F939" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G939" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260924032746522710.jpg</t>
+        </is>
+      </c>
+      <c r="H939" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I939" s="7" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C940" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D940" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E940" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F940" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G940" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260924032746669372.doc</t>
+        </is>
+      </c>
+      <c r="H940" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I940" s="4" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B941" s="6" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C941" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D941" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E941" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F941" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G941" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260924032746814594.txt</t>
+        </is>
+      </c>
+      <c r="H941" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I941" s="7" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>03:27:46</t>
+        </is>
+      </c>
+      <c r="C942" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D942" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E942" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F942" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G942" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260924032746992635.xls</t>
+        </is>
+      </c>
+      <c r="H942" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I942" s="4" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B943" s="6" t="inlineStr">
+        <is>
+          <t>03:27:47</t>
+        </is>
+      </c>
+      <c r="C943" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D943" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E943" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F943" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G943" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260924032747138875.png</t>
+        </is>
+      </c>
+      <c r="H943" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I943" s="7" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>03:27:47</t>
+        </is>
+      </c>
+      <c r="C944" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D944" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E944" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F944" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G944" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260924032747285189.dat</t>
+        </is>
+      </c>
+      <c r="H944" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I944" s="4" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B945" s="6" t="inlineStr">
+        <is>
+          <t>03:27:48</t>
+        </is>
+      </c>
+      <c r="C945" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D945" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E945" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F945" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G945" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260924032748609087.docx</t>
+        </is>
+      </c>
+      <c r="H945" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I945" s="7" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>03:27:48</t>
+        </is>
+      </c>
+      <c r="C946" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D946" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E946" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F946" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G946" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260924032748755380.pdf</t>
+        </is>
+      </c>
+      <c r="H946" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I946" s="4" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B947" s="6" t="inlineStr">
+        <is>
+          <t>03:27:48</t>
+        </is>
+      </c>
+      <c r="C947" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D947" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E947" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F947" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G947" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260924032748918656.jpeg</t>
+        </is>
+      </c>
+      <c r="H947" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I947" s="7" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>03:27:49</t>
+        </is>
+      </c>
+      <c r="C948" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D948" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E948" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F948" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G948" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260924032749070399.xlsx</t>
+        </is>
+      </c>
+      <c r="H948" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I948" s="4" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B949" s="6" t="inlineStr">
+        <is>
+          <t>03:27:49</t>
+        </is>
+      </c>
+      <c r="C949" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D949" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E949" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F949" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G949" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260924032749495865.txt</t>
+        </is>
+      </c>
+      <c r="H949" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I949" s="7" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>03:27:49</t>
+        </is>
+      </c>
+      <c r="C950" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D950" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E950" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F950" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G950" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260924032749801128.xlsx</t>
+        </is>
+      </c>
+      <c r="H950" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I950" s="4" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B951" s="6" t="inlineStr">
+        <is>
+          <t>03:27:50</t>
+        </is>
+      </c>
+      <c r="C951" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D951" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E951" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F951" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G951" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H951" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I951" s="7" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>03:27:50</t>
+        </is>
+      </c>
+      <c r="C952" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D952" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E952" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F952" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G952" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260924032750711482.pdf</t>
+        </is>
+      </c>
+      <c r="H952" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I952" s="4" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B953" s="6" t="inlineStr">
+        <is>
+          <t>03:27:50</t>
+        </is>
+      </c>
+      <c r="C953" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D953" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E953" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F953" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G953" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260924032750902626.jpeg</t>
+        </is>
+      </c>
+      <c r="H953" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I953" s="7" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>03:27:51</t>
+        </is>
+      </c>
+      <c r="C954" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D954" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E954" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F954" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G954" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260924032751221171.pages</t>
+        </is>
+      </c>
+      <c r="H954" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I954" s="4" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B955" s="6" t="inlineStr">
+        <is>
+          <t>03:27:51</t>
+        </is>
+      </c>
+      <c r="C955" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D955" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E955" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F955" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G955" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260924032751816211.pdf</t>
+        </is>
+      </c>
+      <c r="H955" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I955" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I955"/>
+  <dimension ref="A1:I978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41564,6 +41564,995 @@
       </c>
       <c r="I955" s="7" t="inlineStr"/>
     </row>
+    <row r="956">
+      <c r="A956" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>03:45:03</t>
+        </is>
+      </c>
+      <c r="C956" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D956" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E956" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F956" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G956" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260925034503791770.gif</t>
+        </is>
+      </c>
+      <c r="H956" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I956" s="4" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B957" s="6" t="inlineStr">
+        <is>
+          <t>03:45:04</t>
+        </is>
+      </c>
+      <c r="C957" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D957" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E957" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F957" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G957" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260925034504016720.xlsx</t>
+        </is>
+      </c>
+      <c r="H957" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I957" s="7" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>03:45:04</t>
+        </is>
+      </c>
+      <c r="C958" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D958" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E958" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F958" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G958" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260925034504231114.csv</t>
+        </is>
+      </c>
+      <c r="H958" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I958" s="4" t="inlineStr"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B959" s="6" t="inlineStr">
+        <is>
+          <t>03:45:04</t>
+        </is>
+      </c>
+      <c r="C959" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D959" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E959" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F959" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G959" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260925034504443434.pdf</t>
+        </is>
+      </c>
+      <c r="H959" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I959" s="7" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>03:45:04</t>
+        </is>
+      </c>
+      <c r="C960" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D960" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E960" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F960" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G960" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260925034504676218.docx</t>
+        </is>
+      </c>
+      <c r="H960" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I960" s="4" t="inlineStr"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B961" s="6" t="inlineStr">
+        <is>
+          <t>03:45:04</t>
+        </is>
+      </c>
+      <c r="C961" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D961" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E961" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F961" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G961" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260925034504889589.pptx</t>
+        </is>
+      </c>
+      <c r="H961" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I961" s="7" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>03:45:05</t>
+        </is>
+      </c>
+      <c r="C962" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D962" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E962" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F962" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G962" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260925034505124767.jpg</t>
+        </is>
+      </c>
+      <c r="H962" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I962" s="4" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B963" s="6" t="inlineStr">
+        <is>
+          <t>03:45:05</t>
+        </is>
+      </c>
+      <c r="C963" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D963" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E963" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F963" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G963" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260925034505341081.doc</t>
+        </is>
+      </c>
+      <c r="H963" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I963" s="7" t="inlineStr"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>03:45:05</t>
+        </is>
+      </c>
+      <c r="C964" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D964" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E964" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F964" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G964" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260925034505553779.txt</t>
+        </is>
+      </c>
+      <c r="H964" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I964" s="4" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B965" s="6" t="inlineStr">
+        <is>
+          <t>03:45:05</t>
+        </is>
+      </c>
+      <c r="C965" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D965" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E965" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F965" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G965" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260925034505791547.xls</t>
+        </is>
+      </c>
+      <c r="H965" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I965" s="7" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>03:45:06</t>
+        </is>
+      </c>
+      <c r="C966" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D966" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E966" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F966" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G966" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260925034506005629.png</t>
+        </is>
+      </c>
+      <c r="H966" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I966" s="4" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B967" s="6" t="inlineStr">
+        <is>
+          <t>03:45:06</t>
+        </is>
+      </c>
+      <c r="C967" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D967" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E967" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F967" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G967" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260925034506237022.dat</t>
+        </is>
+      </c>
+      <c r="H967" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I967" s="7" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>03:45:08</t>
+        </is>
+      </c>
+      <c r="C968" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D968" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E968" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F968" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G968" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260925034508250587.docx</t>
+        </is>
+      </c>
+      <c r="H968" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I968" s="4" t="inlineStr"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B969" s="6" t="inlineStr">
+        <is>
+          <t>03:45:08</t>
+        </is>
+      </c>
+      <c r="C969" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D969" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E969" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F969" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G969" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260925034508462187.pdf</t>
+        </is>
+      </c>
+      <c r="H969" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I969" s="7" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>03:45:08</t>
+        </is>
+      </c>
+      <c r="C970" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D970" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E970" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F970" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G970" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260925034508705771.jpeg</t>
+        </is>
+      </c>
+      <c r="H970" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I970" s="4" t="inlineStr"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B971" s="6" t="inlineStr">
+        <is>
+          <t>03:45:08</t>
+        </is>
+      </c>
+      <c r="C971" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D971" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E971" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F971" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G971" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260925034508919151.xlsx</t>
+        </is>
+      </c>
+      <c r="H971" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I971" s="7" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>03:45:09</t>
+        </is>
+      </c>
+      <c r="C972" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D972" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E972" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F972" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G972" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260925034509449113.txt</t>
+        </is>
+      </c>
+      <c r="H972" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I972" s="4" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B973" s="6" t="inlineStr">
+        <is>
+          <t>03:45:09</t>
+        </is>
+      </c>
+      <c r="C973" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D973" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E973" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F973" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G973" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260925034509696475.xlsx</t>
+        </is>
+      </c>
+      <c r="H973" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I973" s="7" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>03:45:09</t>
+        </is>
+      </c>
+      <c r="C974" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D974" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E974" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F974" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G974" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H974" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I974" s="4" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B975" s="6" t="inlineStr">
+        <is>
+          <t>03:45:10</t>
+        </is>
+      </c>
+      <c r="C975" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D975" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E975" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F975" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G975" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260925034510644444.pdf</t>
+        </is>
+      </c>
+      <c r="H975" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I975" s="7" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>03:45:10</t>
+        </is>
+      </c>
+      <c r="C976" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D976" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E976" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F976" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G976" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260925034510859467.jpeg</t>
+        </is>
+      </c>
+      <c r="H976" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I976" s="4" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B977" s="6" t="inlineStr">
+        <is>
+          <t>03:45:11</t>
+        </is>
+      </c>
+      <c r="C977" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D977" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E977" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F977" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G977" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260925034511074220.pages</t>
+        </is>
+      </c>
+      <c r="H977" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I977" s="7" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
+          <t>03:45:12</t>
+        </is>
+      </c>
+      <c r="C978" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D978" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E978" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F978" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G978" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260925034512016855.pdf</t>
+        </is>
+      </c>
+      <c r="H978" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I978" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I978"/>
+  <dimension ref="A1:I1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42553,6 +42553,995 @@
       </c>
       <c r="I978" s="4" t="inlineStr"/>
     </row>
+    <row r="979">
+      <c r="A979" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B979" s="6" t="inlineStr">
+        <is>
+          <t>03:51:14</t>
+        </is>
+      </c>
+      <c r="C979" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D979" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E979" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F979" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G979" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260926035114297249.gif</t>
+        </is>
+      </c>
+      <c r="H979" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I979" s="7" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>03:51:14</t>
+        </is>
+      </c>
+      <c r="C980" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D980" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E980" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F980" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G980" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260926035114462503.xlsx</t>
+        </is>
+      </c>
+      <c r="H980" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I980" s="4" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B981" s="6" t="inlineStr">
+        <is>
+          <t>03:51:14</t>
+        </is>
+      </c>
+      <c r="C981" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D981" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E981" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F981" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G981" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260926035114614468.csv</t>
+        </is>
+      </c>
+      <c r="H981" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I981" s="7" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>03:51:14</t>
+        </is>
+      </c>
+      <c r="C982" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D982" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E982" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F982" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G982" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260926035114777462.pdf</t>
+        </is>
+      </c>
+      <c r="H982" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I982" s="4" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B983" s="6" t="inlineStr">
+        <is>
+          <t>03:51:14</t>
+        </is>
+      </c>
+      <c r="C983" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D983" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E983" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F983" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G983" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260926035114952550.docx</t>
+        </is>
+      </c>
+      <c r="H983" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I983" s="7" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>03:51:15</t>
+        </is>
+      </c>
+      <c r="C984" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D984" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E984" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F984" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G984" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260926035115107425.pptx</t>
+        </is>
+      </c>
+      <c r="H984" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I984" s="4" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B985" s="6" t="inlineStr">
+        <is>
+          <t>03:51:15</t>
+        </is>
+      </c>
+      <c r="C985" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D985" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E985" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F985" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G985" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260926035115286653.jpg</t>
+        </is>
+      </c>
+      <c r="H985" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I985" s="7" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>03:51:15</t>
+        </is>
+      </c>
+      <c r="C986" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D986" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E986" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F986" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G986" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260926035115441631.doc</t>
+        </is>
+      </c>
+      <c r="H986" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I986" s="4" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B987" s="6" t="inlineStr">
+        <is>
+          <t>03:51:15</t>
+        </is>
+      </c>
+      <c r="C987" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D987" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E987" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F987" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G987" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260926035115596522.txt</t>
+        </is>
+      </c>
+      <c r="H987" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I987" s="7" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>03:51:16</t>
+        </is>
+      </c>
+      <c r="C988" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D988" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E988" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F988" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G988" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260926035116013785.xls</t>
+        </is>
+      </c>
+      <c r="H988" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I988" s="4" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B989" s="6" t="inlineStr">
+        <is>
+          <t>03:51:16</t>
+        </is>
+      </c>
+      <c r="C989" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D989" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E989" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F989" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G989" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260926035116169819.png</t>
+        </is>
+      </c>
+      <c r="H989" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I989" s="7" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>03:51:16</t>
+        </is>
+      </c>
+      <c r="C990" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D990" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E990" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F990" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G990" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260926035116353383.dat</t>
+        </is>
+      </c>
+      <c r="H990" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I990" s="4" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B991" s="6" t="inlineStr">
+        <is>
+          <t>03:51:17</t>
+        </is>
+      </c>
+      <c r="C991" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D991" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E991" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F991" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G991" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260926035117849949.docx</t>
+        </is>
+      </c>
+      <c r="H991" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I991" s="7" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>03:51:18</t>
+        </is>
+      </c>
+      <c r="C992" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D992" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E992" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F992" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G992" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260926035118005225.pdf</t>
+        </is>
+      </c>
+      <c r="H992" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I992" s="4" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B993" s="6" t="inlineStr">
+        <is>
+          <t>03:51:18</t>
+        </is>
+      </c>
+      <c r="C993" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D993" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E993" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F993" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G993" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260926035118188808.jpeg</t>
+        </is>
+      </c>
+      <c r="H993" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I993" s="7" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>03:51:18</t>
+        </is>
+      </c>
+      <c r="C994" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D994" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E994" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F994" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G994" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260926035118346134.xlsx</t>
+        </is>
+      </c>
+      <c r="H994" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I994" s="4" t="inlineStr"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B995" s="6" t="inlineStr">
+        <is>
+          <t>03:51:18</t>
+        </is>
+      </c>
+      <c r="C995" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D995" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E995" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F995" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G995" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260926035118801427.txt</t>
+        </is>
+      </c>
+      <c r="H995" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I995" s="7" t="inlineStr"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>03:51:18</t>
+        </is>
+      </c>
+      <c r="C996" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D996" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E996" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F996" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G996" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260926035118957511.xlsx</t>
+        </is>
+      </c>
+      <c r="H996" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I996" s="4" t="inlineStr"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B997" s="6" t="inlineStr">
+        <is>
+          <t>03:51:19</t>
+        </is>
+      </c>
+      <c r="C997" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D997" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E997" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F997" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G997" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H997" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I997" s="7" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>03:51:19</t>
+        </is>
+      </c>
+      <c r="C998" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D998" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E998" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F998" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G998" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260926035119498903.pdf</t>
+        </is>
+      </c>
+      <c r="H998" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I998" s="4" t="inlineStr"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B999" s="6" t="inlineStr">
+        <is>
+          <t>03:51:19</t>
+        </is>
+      </c>
+      <c r="C999" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D999" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E999" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F999" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G999" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260926035119654990.jpeg</t>
+        </is>
+      </c>
+      <c r="H999" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I999" s="7" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>03:51:19</t>
+        </is>
+      </c>
+      <c r="C1000" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1000" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1000" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1000" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1000" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260926035119830494.pages</t>
+        </is>
+      </c>
+      <c r="H1000" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1000" s="4" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1001" s="6" t="inlineStr">
+        <is>
+          <t>03:51:20</t>
+        </is>
+      </c>
+      <c r="C1001" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1001" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1001" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1001" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1001" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260926035120294979.pdf</t>
+        </is>
+      </c>
+      <c r="H1001" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1001" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43542,6 +43542,995 @@
       </c>
       <c r="I1001" s="7" t="inlineStr"/>
     </row>
+    <row r="1002">
+      <c r="A1002" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>04:00:09</t>
+        </is>
+      </c>
+      <c r="C1002" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1002" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1002" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1002" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1002" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260927040009752559.gif</t>
+        </is>
+      </c>
+      <c r="H1002" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1002" s="4" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1003" s="6" t="inlineStr">
+        <is>
+          <t>04:00:09</t>
+        </is>
+      </c>
+      <c r="C1003" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1003" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1003" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1003" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1003" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260927040009985199.xlsx</t>
+        </is>
+      </c>
+      <c r="H1003" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1003" s="7" t="inlineStr"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>04:00:10</t>
+        </is>
+      </c>
+      <c r="C1004" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1004" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1004" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1004" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1004" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260927040010205641.csv</t>
+        </is>
+      </c>
+      <c r="H1004" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1004" s="4" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1005" s="6" t="inlineStr">
+        <is>
+          <t>04:00:10</t>
+        </is>
+      </c>
+      <c r="C1005" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1005" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1005" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1005" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1005" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260927040010427363.pdf</t>
+        </is>
+      </c>
+      <c r="H1005" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1005" s="7" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>04:00:10</t>
+        </is>
+      </c>
+      <c r="C1006" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1006" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1006" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1006" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1006" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260927040010671801.docx</t>
+        </is>
+      </c>
+      <c r="H1006" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1006" s="4" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1007" s="6" t="inlineStr">
+        <is>
+          <t>04:00:10</t>
+        </is>
+      </c>
+      <c r="C1007" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1007" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1007" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1007" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1007" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260927040010891073.pptx</t>
+        </is>
+      </c>
+      <c r="H1007" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1007" s="7" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>04:00:11</t>
+        </is>
+      </c>
+      <c r="C1008" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1008" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1008" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1008" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1008" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260927040011129930.jpg</t>
+        </is>
+      </c>
+      <c r="H1008" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1008" s="4" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1009" s="6" t="inlineStr">
+        <is>
+          <t>04:00:11</t>
+        </is>
+      </c>
+      <c r="C1009" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1009" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1009" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1009" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1009" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260927040011351059.doc</t>
+        </is>
+      </c>
+      <c r="H1009" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1009" s="7" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>04:00:11</t>
+        </is>
+      </c>
+      <c r="C1010" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1010" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1010" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1010" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1010" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260927040011588692.txt</t>
+        </is>
+      </c>
+      <c r="H1010" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1010" s="4" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1011" s="6" t="inlineStr">
+        <is>
+          <t>04:00:11</t>
+        </is>
+      </c>
+      <c r="C1011" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1011" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1011" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1011" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1011" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260927040011811018.xls</t>
+        </is>
+      </c>
+      <c r="H1011" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1011" s="7" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>04:00:12</t>
+        </is>
+      </c>
+      <c r="C1012" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1012" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1012" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1012" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1012" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260927040012031085.png</t>
+        </is>
+      </c>
+      <c r="H1012" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1012" s="4" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1013" s="6" t="inlineStr">
+        <is>
+          <t>04:00:12</t>
+        </is>
+      </c>
+      <c r="C1013" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1013" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1013" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1013" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1013" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260927040012277807.dat</t>
+        </is>
+      </c>
+      <c r="H1013" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1013" s="7" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>04:00:14</t>
+        </is>
+      </c>
+      <c r="C1014" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1014" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1014" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1014" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1014" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260927040014377314.docx</t>
+        </is>
+      </c>
+      <c r="H1014" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1014" s="4" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1015" s="6" t="inlineStr">
+        <is>
+          <t>04:00:14</t>
+        </is>
+      </c>
+      <c r="C1015" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1015" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1015" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1015" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1015" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260927040014619655.pdf</t>
+        </is>
+      </c>
+      <c r="H1015" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1015" s="7" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>04:00:14</t>
+        </is>
+      </c>
+      <c r="C1016" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1016" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1016" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1016" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1016" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260927040014843026.jpeg</t>
+        </is>
+      </c>
+      <c r="H1016" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1016" s="4" t="inlineStr"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1017" s="6" t="inlineStr">
+        <is>
+          <t>04:00:15</t>
+        </is>
+      </c>
+      <c r="C1017" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1017" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1017" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1017" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1017" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260927040015062208.xlsx</t>
+        </is>
+      </c>
+      <c r="H1017" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1017" s="7" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>04:00:15</t>
+        </is>
+      </c>
+      <c r="C1018" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1018" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1018" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1018" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1018" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260927040015636433.txt</t>
+        </is>
+      </c>
+      <c r="H1018" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1018" s="4" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1019" s="6" t="inlineStr">
+        <is>
+          <t>04:00:15</t>
+        </is>
+      </c>
+      <c r="C1019" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1019" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1019" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1019" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1019" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260927040015862328.xlsx</t>
+        </is>
+      </c>
+      <c r="H1019" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1019" s="7" t="inlineStr"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>04:00:16</t>
+        </is>
+      </c>
+      <c r="C1020" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1020" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1020" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1020" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1020" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1020" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1020" s="4" t="inlineStr"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1021" s="6" t="inlineStr">
+        <is>
+          <t>04:00:16</t>
+        </is>
+      </c>
+      <c r="C1021" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1021" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1021" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1021" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1021" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260927040016662222.pdf</t>
+        </is>
+      </c>
+      <c r="H1021" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1021" s="7" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>04:00:16</t>
+        </is>
+      </c>
+      <c r="C1022" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1022" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1022" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1022" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1022" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260927040016884661.jpeg</t>
+        </is>
+      </c>
+      <c r="H1022" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1022" s="4" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1023" s="6" t="inlineStr">
+        <is>
+          <t>04:00:17</t>
+        </is>
+      </c>
+      <c r="C1023" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1023" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1023" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1023" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1023" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260927040017133350.pages</t>
+        </is>
+      </c>
+      <c r="H1023" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1023" s="7" t="inlineStr"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>04:00:17</t>
+        </is>
+      </c>
+      <c r="C1024" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1024" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1024" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1024" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1024" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260927040017708175.pdf</t>
+        </is>
+      </c>
+      <c r="H1024" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1024" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1024"/>
+  <dimension ref="A1:I1047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44531,6 +44531,995 @@
       </c>
       <c r="I1024" s="4" t="inlineStr"/>
     </row>
+    <row r="1025">
+      <c r="A1025" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1025" s="6" t="inlineStr">
+        <is>
+          <t>04:01:11</t>
+        </is>
+      </c>
+      <c r="C1025" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1025" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1025" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1025" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1025" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260928040111650489.gif</t>
+        </is>
+      </c>
+      <c r="H1025" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1025" s="7" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>04:01:11</t>
+        </is>
+      </c>
+      <c r="C1026" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1026" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1026" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1026" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1026" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260928040111842358.xlsx</t>
+        </is>
+      </c>
+      <c r="H1026" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1026" s="4" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1027" s="6" t="inlineStr">
+        <is>
+          <t>04:01:12</t>
+        </is>
+      </c>
+      <c r="C1027" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1027" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1027" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1027" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1027" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260928040112021338.csv</t>
+        </is>
+      </c>
+      <c r="H1027" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1027" s="7" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>04:01:12</t>
+        </is>
+      </c>
+      <c r="C1028" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1028" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1028" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1028" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1028" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260928040112202847.pdf</t>
+        </is>
+      </c>
+      <c r="H1028" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1028" s="4" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1029" s="6" t="inlineStr">
+        <is>
+          <t>04:01:12</t>
+        </is>
+      </c>
+      <c r="C1029" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1029" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1029" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1029" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1029" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260928040112550347.docx</t>
+        </is>
+      </c>
+      <c r="H1029" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1029" s="7" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>04:01:12</t>
+        </is>
+      </c>
+      <c r="C1030" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1030" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1030" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1030" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1030" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260928040112852691.pptx</t>
+        </is>
+      </c>
+      <c r="H1030" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1030" s="4" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1031" s="6" t="inlineStr">
+        <is>
+          <t>04:01:13</t>
+        </is>
+      </c>
+      <c r="C1031" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1031" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1031" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1031" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1031" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260928040113154606.jpg</t>
+        </is>
+      </c>
+      <c r="H1031" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1031" s="7" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>04:01:13</t>
+        </is>
+      </c>
+      <c r="C1032" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1032" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1032" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1032" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1032" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260928040113516517.doc</t>
+        </is>
+      </c>
+      <c r="H1032" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1032" s="4" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1033" s="6" t="inlineStr">
+        <is>
+          <t>04:01:13</t>
+        </is>
+      </c>
+      <c r="C1033" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1033" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1033" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1033" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1033" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260928040113868660.txt</t>
+        </is>
+      </c>
+      <c r="H1033" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1033" s="7" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>04:01:14</t>
+        </is>
+      </c>
+      <c r="C1034" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1034" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1034" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1034" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1034" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260928040114229475.xls</t>
+        </is>
+      </c>
+      <c r="H1034" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1034" s="4" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1035" s="6" t="inlineStr">
+        <is>
+          <t>04:01:14</t>
+        </is>
+      </c>
+      <c r="C1035" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1035" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1035" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1035" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1035" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260928040114582662.png</t>
+        </is>
+      </c>
+      <c r="H1035" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1035" s="7" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1036" s="3" t="inlineStr">
+        <is>
+          <t>04:01:14</t>
+        </is>
+      </c>
+      <c r="C1036" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1036" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1036" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1036" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1036" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260928040114895046.dat</t>
+        </is>
+      </c>
+      <c r="H1036" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1036" s="4" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1037" s="6" t="inlineStr">
+        <is>
+          <t>04:01:17</t>
+        </is>
+      </c>
+      <c r="C1037" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1037" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1037" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1037" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1037" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260928040117182076.docx</t>
+        </is>
+      </c>
+      <c r="H1037" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1037" s="7" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1038" s="3" t="inlineStr">
+        <is>
+          <t>04:01:17</t>
+        </is>
+      </c>
+      <c r="C1038" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1038" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1038" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1038" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1038" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260928040117357156.pdf</t>
+        </is>
+      </c>
+      <c r="H1038" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1038" s="4" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1039" s="6" t="inlineStr">
+        <is>
+          <t>04:01:17</t>
+        </is>
+      </c>
+      <c r="C1039" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1039" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1039" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1039" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1039" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260928040117520180.jpeg</t>
+        </is>
+      </c>
+      <c r="H1039" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1039" s="7" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1040" s="3" t="inlineStr">
+        <is>
+          <t>04:01:17</t>
+        </is>
+      </c>
+      <c r="C1040" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1040" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1040" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1040" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1040" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260928040117771314.xlsx</t>
+        </is>
+      </c>
+      <c r="H1040" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1040" s="4" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1041" s="6" t="inlineStr">
+        <is>
+          <t>04:01:18</t>
+        </is>
+      </c>
+      <c r="C1041" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1041" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1041" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1041" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1041" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260928040118575350.txt</t>
+        </is>
+      </c>
+      <c r="H1041" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1041" s="7" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1042" s="3" t="inlineStr">
+        <is>
+          <t>04:01:18</t>
+        </is>
+      </c>
+      <c r="C1042" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1042" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1042" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1042" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1042" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260928040118847454.xlsx</t>
+        </is>
+      </c>
+      <c r="H1042" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1042" s="4" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1043" s="6" t="inlineStr">
+        <is>
+          <t>04:01:19</t>
+        </is>
+      </c>
+      <c r="C1043" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1043" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1043" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1043" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1043" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1043" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1043" s="7" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1044" s="3" t="inlineStr">
+        <is>
+          <t>04:01:19</t>
+        </is>
+      </c>
+      <c r="C1044" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1044" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1044" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1044" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1044" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260928040119841036.pdf</t>
+        </is>
+      </c>
+      <c r="H1044" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1044" s="4" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1045" s="6" t="inlineStr">
+        <is>
+          <t>04:01:20</t>
+        </is>
+      </c>
+      <c r="C1045" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1045" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1045" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1045" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1045" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260928040120191882.jpeg</t>
+        </is>
+      </c>
+      <c r="H1045" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1045" s="7" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1046" s="3" t="inlineStr">
+        <is>
+          <t>04:01:20</t>
+        </is>
+      </c>
+      <c r="C1046" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1046" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1046" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1046" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1046" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260928040120361864.pages</t>
+        </is>
+      </c>
+      <c r="H1046" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1046" s="4" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1047" s="6" t="inlineStr">
+        <is>
+          <t>04:01:21</t>
+        </is>
+      </c>
+      <c r="C1047" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1047" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1047" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1047" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1047" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260928040121328044.pdf</t>
+        </is>
+      </c>
+      <c r="H1047" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1047" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1047"/>
+  <dimension ref="A1:I1070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45520,6 +45520,995 @@
       </c>
       <c r="I1047" s="7" t="inlineStr"/>
     </row>
+    <row r="1048">
+      <c r="A1048" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1048" s="3" t="inlineStr">
+        <is>
+          <t>04:34:49</t>
+        </is>
+      </c>
+      <c r="C1048" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1048" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1048" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1048" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1048" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260929043449705233.gif</t>
+        </is>
+      </c>
+      <c r="H1048" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1048" s="4" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1049" s="6" t="inlineStr">
+        <is>
+          <t>04:34:49</t>
+        </is>
+      </c>
+      <c r="C1049" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1049" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1049" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1049" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1049" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260929043449942034.xlsx</t>
+        </is>
+      </c>
+      <c r="H1049" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1049" s="7" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
+        <is>
+          <t>04:34:50</t>
+        </is>
+      </c>
+      <c r="C1050" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1050" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1050" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1050" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1050" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260929043450165645.csv</t>
+        </is>
+      </c>
+      <c r="H1050" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1050" s="4" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1051" s="6" t="inlineStr">
+        <is>
+          <t>04:34:50</t>
+        </is>
+      </c>
+      <c r="C1051" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1051" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1051" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1051" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1051" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260929043450389594.pdf</t>
+        </is>
+      </c>
+      <c r="H1051" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1051" s="7" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1052" s="3" t="inlineStr">
+        <is>
+          <t>04:34:50</t>
+        </is>
+      </c>
+      <c r="C1052" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1052" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1052" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1052" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1052" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260929043450631632.docx</t>
+        </is>
+      </c>
+      <c r="H1052" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1052" s="4" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1053" s="6" t="inlineStr">
+        <is>
+          <t>04:34:50</t>
+        </is>
+      </c>
+      <c r="C1053" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1053" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1053" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1053" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1053" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260929043450854506.pptx</t>
+        </is>
+      </c>
+      <c r="H1053" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1053" s="7" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1054" s="3" t="inlineStr">
+        <is>
+          <t>04:34:51</t>
+        </is>
+      </c>
+      <c r="C1054" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1054" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1054" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1054" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1054" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260929043451097386.jpg</t>
+        </is>
+      </c>
+      <c r="H1054" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1054" s="4" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1055" s="6" t="inlineStr">
+        <is>
+          <t>04:34:51</t>
+        </is>
+      </c>
+      <c r="C1055" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1055" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1055" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1055" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1055" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260929043451321338.doc</t>
+        </is>
+      </c>
+      <c r="H1055" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1055" s="7" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1056" s="3" t="inlineStr">
+        <is>
+          <t>04:34:51</t>
+        </is>
+      </c>
+      <c r="C1056" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1056" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1056" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1056" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1056" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260929043451564943.txt</t>
+        </is>
+      </c>
+      <c r="H1056" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1056" s="4" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1057" s="6" t="inlineStr">
+        <is>
+          <t>04:34:51</t>
+        </is>
+      </c>
+      <c r="C1057" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1057" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1057" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1057" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1057" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260929043451787895.xls</t>
+        </is>
+      </c>
+      <c r="H1057" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1057" s="7" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1058" s="3" t="inlineStr">
+        <is>
+          <t>04:34:52</t>
+        </is>
+      </c>
+      <c r="C1058" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1058" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1058" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1058" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1058" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260929043452009585.png</t>
+        </is>
+      </c>
+      <c r="H1058" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1058" s="4" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1059" s="6" t="inlineStr">
+        <is>
+          <t>04:34:52</t>
+        </is>
+      </c>
+      <c r="C1059" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1059" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1059" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1059" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1059" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260929043452254275.dat</t>
+        </is>
+      </c>
+      <c r="H1059" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1059" s="7" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1060" s="3" t="inlineStr">
+        <is>
+          <t>04:34:54</t>
+        </is>
+      </c>
+      <c r="C1060" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1060" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1060" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1060" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1060" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260929043454638404.docx</t>
+        </is>
+      </c>
+      <c r="H1060" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1060" s="4" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1061" s="6" t="inlineStr">
+        <is>
+          <t>04:34:54</t>
+        </is>
+      </c>
+      <c r="C1061" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1061" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1061" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1061" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1061" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260929043454881354.pdf</t>
+        </is>
+      </c>
+      <c r="H1061" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1061" s="7" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1062" s="3" t="inlineStr">
+        <is>
+          <t>04:34:55</t>
+        </is>
+      </c>
+      <c r="C1062" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1062" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1062" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1062" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1062" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260929043455106104.jpeg</t>
+        </is>
+      </c>
+      <c r="H1062" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1062" s="4" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1063" s="6" t="inlineStr">
+        <is>
+          <t>04:34:55</t>
+        </is>
+      </c>
+      <c r="C1063" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1063" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1063" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1063" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1063" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260929043455351565.xlsx</t>
+        </is>
+      </c>
+      <c r="H1063" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1063" s="7" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1064" s="3" t="inlineStr">
+        <is>
+          <t>04:34:56</t>
+        </is>
+      </c>
+      <c r="C1064" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1064" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1064" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1064" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1064" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260929043456180821.txt</t>
+        </is>
+      </c>
+      <c r="H1064" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1064" s="4" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1065" s="6" t="inlineStr">
+        <is>
+          <t>04:34:56</t>
+        </is>
+      </c>
+      <c r="C1065" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1065" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1065" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1065" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1065" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260929043456406282.xlsx</t>
+        </is>
+      </c>
+      <c r="H1065" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1065" s="7" t="inlineStr"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
+        <is>
+          <t>04:34:56</t>
+        </is>
+      </c>
+      <c r="C1066" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1066" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1066" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1066" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1066" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1066" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1066" s="4" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1067" s="6" t="inlineStr">
+        <is>
+          <t>04:34:57</t>
+        </is>
+      </c>
+      <c r="C1067" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1067" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1067" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1067" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1067" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260929043457493239.pdf</t>
+        </is>
+      </c>
+      <c r="H1067" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1067" s="7" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1068" s="3" t="inlineStr">
+        <is>
+          <t>04:34:57</t>
+        </is>
+      </c>
+      <c r="C1068" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1068" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1068" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1068" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1068" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260929043457736116.jpeg</t>
+        </is>
+      </c>
+      <c r="H1068" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1068" s="4" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1069" s="6" t="inlineStr">
+        <is>
+          <t>04:34:57</t>
+        </is>
+      </c>
+      <c r="C1069" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1069" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1069" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1069" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1069" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260929043457962683.pages</t>
+        </is>
+      </c>
+      <c r="H1069" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1069" s="7" t="inlineStr"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1070" s="3" t="inlineStr">
+        <is>
+          <t>04:34:59</t>
+        </is>
+      </c>
+      <c r="C1070" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1070" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1070" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1070" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1070" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260929043459030743.pdf</t>
+        </is>
+      </c>
+      <c r="H1070" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1070" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1070"/>
+  <dimension ref="A1:I1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46509,6 +46509,995 @@
       </c>
       <c r="I1070" s="4" t="inlineStr"/>
     </row>
+    <row r="1071">
+      <c r="A1071" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1071" s="6" t="inlineStr">
+        <is>
+          <t>04:18:09</t>
+        </is>
+      </c>
+      <c r="C1071" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1071" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1071" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1071" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1071" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20260930041809700360.gif</t>
+        </is>
+      </c>
+      <c r="H1071" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1071" s="7" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1072" s="3" t="inlineStr">
+        <is>
+          <t>04:18:09</t>
+        </is>
+      </c>
+      <c r="C1072" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1072" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1072" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1072" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1072" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20260930041809930565.xlsx</t>
+        </is>
+      </c>
+      <c r="H1072" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1072" s="4" t="inlineStr"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1073" s="6" t="inlineStr">
+        <is>
+          <t>04:18:10</t>
+        </is>
+      </c>
+      <c r="C1073" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1073" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1073" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1073" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1073" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20260930041810142916.csv</t>
+        </is>
+      </c>
+      <c r="H1073" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1073" s="7" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1074" s="3" t="inlineStr">
+        <is>
+          <t>04:18:10</t>
+        </is>
+      </c>
+      <c r="C1074" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1074" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1074" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1074" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1074" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20260930041810372739.pdf</t>
+        </is>
+      </c>
+      <c r="H1074" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1074" s="4" t="inlineStr"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1075" s="6" t="inlineStr">
+        <is>
+          <t>04:18:10</t>
+        </is>
+      </c>
+      <c r="C1075" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1075" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1075" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1075" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1075" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20260930041810590270.docx</t>
+        </is>
+      </c>
+      <c r="H1075" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1075" s="7" t="inlineStr"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1076" s="3" t="inlineStr">
+        <is>
+          <t>04:18:10</t>
+        </is>
+      </c>
+      <c r="C1076" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1076" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1076" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1076" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1076" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20260930041810803402.pptx</t>
+        </is>
+      </c>
+      <c r="H1076" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1076" s="4" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1077" s="6" t="inlineStr">
+        <is>
+          <t>04:18:11</t>
+        </is>
+      </c>
+      <c r="C1077" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1077" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1077" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1077" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1077" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20260930041811038167.jpg</t>
+        </is>
+      </c>
+      <c r="H1077" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1077" s="7" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1078" s="3" t="inlineStr">
+        <is>
+          <t>04:18:11</t>
+        </is>
+      </c>
+      <c r="C1078" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1078" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1078" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1078" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1078" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20260930041811251776.doc</t>
+        </is>
+      </c>
+      <c r="H1078" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1078" s="4" t="inlineStr"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1079" s="6" t="inlineStr">
+        <is>
+          <t>04:18:11</t>
+        </is>
+      </c>
+      <c r="C1079" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1079" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1079" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1079" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1079" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20260930041811484557.txt</t>
+        </is>
+      </c>
+      <c r="H1079" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1079" s="7" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1080" s="3" t="inlineStr">
+        <is>
+          <t>04:18:11</t>
+        </is>
+      </c>
+      <c r="C1080" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1080" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1080" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1080" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1080" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20260930041811699674.xls</t>
+        </is>
+      </c>
+      <c r="H1080" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1080" s="4" t="inlineStr"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1081" s="6" t="inlineStr">
+        <is>
+          <t>04:18:11</t>
+        </is>
+      </c>
+      <c r="C1081" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1081" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1081" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1081" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1081" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20260930041811933606.png</t>
+        </is>
+      </c>
+      <c r="H1081" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1081" s="7" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1082" s="3" t="inlineStr">
+        <is>
+          <t>04:18:12</t>
+        </is>
+      </c>
+      <c r="C1082" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1082" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1082" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1082" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1082" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20260930041812149430.dat</t>
+        </is>
+      </c>
+      <c r="H1082" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1082" s="4" t="inlineStr"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1083" s="6" t="inlineStr">
+        <is>
+          <t>04:18:13</t>
+        </is>
+      </c>
+      <c r="C1083" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1083" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1083" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1083" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1083" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20260930041813664267.docx</t>
+        </is>
+      </c>
+      <c r="H1083" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1083" s="7" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1084" s="3" t="inlineStr">
+        <is>
+          <t>04:18:13</t>
+        </is>
+      </c>
+      <c r="C1084" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1084" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1084" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1084" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1084" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20260930041813904919.pdf</t>
+        </is>
+      </c>
+      <c r="H1084" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1084" s="4" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1085" s="6" t="inlineStr">
+        <is>
+          <t>04:18:14</t>
+        </is>
+      </c>
+      <c r="C1085" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1085" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1085" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1085" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1085" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20260930041814122265.jpeg</t>
+        </is>
+      </c>
+      <c r="H1085" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1085" s="7" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1086" s="3" t="inlineStr">
+        <is>
+          <t>04:18:14</t>
+        </is>
+      </c>
+      <c r="C1086" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1086" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1086" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1086" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1086" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20260930041814355556.xlsx</t>
+        </is>
+      </c>
+      <c r="H1086" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1086" s="4" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1087" s="6" t="inlineStr">
+        <is>
+          <t>04:18:14</t>
+        </is>
+      </c>
+      <c r="C1087" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1087" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1087" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1087" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1087" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20260930041814940040.txt</t>
+        </is>
+      </c>
+      <c r="H1087" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1087" s="7" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1088" s="3" t="inlineStr">
+        <is>
+          <t>04:18:15</t>
+        </is>
+      </c>
+      <c r="C1088" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1088" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1088" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1088" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1088" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20260930041815174916.xlsx</t>
+        </is>
+      </c>
+      <c r="H1088" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1088" s="4" t="inlineStr"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1089" s="6" t="inlineStr">
+        <is>
+          <t>04:18:15</t>
+        </is>
+      </c>
+      <c r="C1089" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1089" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1089" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1089" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1089" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1089" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1089" s="7" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1090" s="3" t="inlineStr">
+        <is>
+          <t>04:18:15</t>
+        </is>
+      </c>
+      <c r="C1090" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1090" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1090" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1090" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1090" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20260930041815866928.pdf</t>
+        </is>
+      </c>
+      <c r="H1090" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1090" s="4" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1091" s="6" t="inlineStr">
+        <is>
+          <t>04:18:16</t>
+        </is>
+      </c>
+      <c r="C1091" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1091" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1091" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1091" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1091" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20260930041816092970.jpeg</t>
+        </is>
+      </c>
+      <c r="H1091" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1091" s="7" t="inlineStr"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1092" s="3" t="inlineStr">
+        <is>
+          <t>04:18:16</t>
+        </is>
+      </c>
+      <c r="C1092" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1092" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1092" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1092" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1092" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20260930041816334310.pages</t>
+        </is>
+      </c>
+      <c r="H1092" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1092" s="4" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1093" s="6" t="inlineStr">
+        <is>
+          <t>04:18:17</t>
+        </is>
+      </c>
+      <c r="C1093" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1093" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1093" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1093" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1093" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20260930041817045849.pdf</t>
+        </is>
+      </c>
+      <c r="H1093" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1093" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1093"/>
+  <dimension ref="A1:I1116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47498,6 +47498,995 @@
       </c>
       <c r="I1093" s="7" t="inlineStr"/>
     </row>
+    <row r="1094">
+      <c r="A1094" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1094" s="3" t="inlineStr">
+        <is>
+          <t>04:30:17</t>
+        </is>
+      </c>
+      <c r="C1094" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1094" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1094" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1094" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1094" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261001043017089786.gif</t>
+        </is>
+      </c>
+      <c r="H1094" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1094" s="4" t="inlineStr"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1095" s="6" t="inlineStr">
+        <is>
+          <t>04:30:17</t>
+        </is>
+      </c>
+      <c r="C1095" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1095" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1095" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1095" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1095" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261001043017339241.xlsx</t>
+        </is>
+      </c>
+      <c r="H1095" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1095" s="7" t="inlineStr"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1096" s="3" t="inlineStr">
+        <is>
+          <t>04:30:17</t>
+        </is>
+      </c>
+      <c r="C1096" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1096" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1096" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1096" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1096" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261001043017574335.csv</t>
+        </is>
+      </c>
+      <c r="H1096" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1096" s="4" t="inlineStr"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1097" s="6" t="inlineStr">
+        <is>
+          <t>04:30:17</t>
+        </is>
+      </c>
+      <c r="C1097" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1097" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1097" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1097" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1097" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261001043017829095.pdf</t>
+        </is>
+      </c>
+      <c r="H1097" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1097" s="7" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1098" s="3" t="inlineStr">
+        <is>
+          <t>04:30:18</t>
+        </is>
+      </c>
+      <c r="C1098" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1098" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1098" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1098" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1098" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261001043018062497.docx</t>
+        </is>
+      </c>
+      <c r="H1098" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1098" s="4" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1099" s="6" t="inlineStr">
+        <is>
+          <t>04:30:18</t>
+        </is>
+      </c>
+      <c r="C1099" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1099" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1099" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1099" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1099" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261001043018294794.pptx</t>
+        </is>
+      </c>
+      <c r="H1099" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1099" s="7" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1100" s="3" t="inlineStr">
+        <is>
+          <t>04:30:18</t>
+        </is>
+      </c>
+      <c r="C1100" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1100" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1100" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1100" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1100" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261001043018548932.jpg</t>
+        </is>
+      </c>
+      <c r="H1100" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1100" s="4" t="inlineStr"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1101" s="6" t="inlineStr">
+        <is>
+          <t>04:30:18</t>
+        </is>
+      </c>
+      <c r="C1101" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1101" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1101" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1101" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1101" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261001043018785266.doc</t>
+        </is>
+      </c>
+      <c r="H1101" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1101" s="7" t="inlineStr"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1102" s="3" t="inlineStr">
+        <is>
+          <t>04:30:19</t>
+        </is>
+      </c>
+      <c r="C1102" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1102" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1102" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1102" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261001043019036255.txt</t>
+        </is>
+      </c>
+      <c r="H1102" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1102" s="4" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1103" s="6" t="inlineStr">
+        <is>
+          <t>04:30:19</t>
+        </is>
+      </c>
+      <c r="C1103" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1103" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1103" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1103" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1103" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261001043019271961.xls</t>
+        </is>
+      </c>
+      <c r="H1103" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1103" s="7" t="inlineStr"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1104" s="3" t="inlineStr">
+        <is>
+          <t>04:30:19</t>
+        </is>
+      </c>
+      <c r="C1104" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1104" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1104" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1104" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261001043019523175.png</t>
+        </is>
+      </c>
+      <c r="H1104" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1104" s="4" t="inlineStr"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1105" s="6" t="inlineStr">
+        <is>
+          <t>04:30:19</t>
+        </is>
+      </c>
+      <c r="C1105" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1105" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1105" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1105" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1105" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261001043019761390.dat</t>
+        </is>
+      </c>
+      <c r="H1105" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1105" s="7" t="inlineStr"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1106" s="3" t="inlineStr">
+        <is>
+          <t>04:30:21</t>
+        </is>
+      </c>
+      <c r="C1106" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1106" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1106" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1106" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1106" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261001043021190545.docx</t>
+        </is>
+      </c>
+      <c r="H1106" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1106" s="4" t="inlineStr"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1107" s="6" t="inlineStr">
+        <is>
+          <t>04:30:21</t>
+        </is>
+      </c>
+      <c r="C1107" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1107" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1107" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1107" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1107" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261001043021427354.pdf</t>
+        </is>
+      </c>
+      <c r="H1107" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1107" s="7" t="inlineStr"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1108" s="3" t="inlineStr">
+        <is>
+          <t>04:30:21</t>
+        </is>
+      </c>
+      <c r="C1108" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1108" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1108" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1108" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1108" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261001043021664354.jpeg</t>
+        </is>
+      </c>
+      <c r="H1108" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1108" s="4" t="inlineStr"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1109" s="6" t="inlineStr">
+        <is>
+          <t>04:30:21</t>
+        </is>
+      </c>
+      <c r="C1109" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1109" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1109" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1109" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1109" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261001043021923037.xlsx</t>
+        </is>
+      </c>
+      <c r="H1109" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1109" s="7" t="inlineStr"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1110" s="3" t="inlineStr">
+        <is>
+          <t>04:30:22</t>
+        </is>
+      </c>
+      <c r="C1110" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1110" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1110" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1110" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1110" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261001043022467239.txt</t>
+        </is>
+      </c>
+      <c r="H1110" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1110" s="4" t="inlineStr"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1111" s="6" t="inlineStr">
+        <is>
+          <t>04:30:22</t>
+        </is>
+      </c>
+      <c r="C1111" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1111" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1111" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1111" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1111" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261001043022721344.xlsx</t>
+        </is>
+      </c>
+      <c r="H1111" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1111" s="7" t="inlineStr"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1112" s="3" t="inlineStr">
+        <is>
+          <t>04:30:22</t>
+        </is>
+      </c>
+      <c r="C1112" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1112" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1112" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1112" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1112" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1112" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1112" s="4" t="inlineStr"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1113" s="6" t="inlineStr">
+        <is>
+          <t>04:30:23</t>
+        </is>
+      </c>
+      <c r="C1113" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1113" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1113" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1113" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1113" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261001043023455065.pdf</t>
+        </is>
+      </c>
+      <c r="H1113" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1113" s="7" t="inlineStr"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1114" s="3" t="inlineStr">
+        <is>
+          <t>04:30:23</t>
+        </is>
+      </c>
+      <c r="C1114" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1114" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1114" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1114" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1114" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261001043023694229.jpeg</t>
+        </is>
+      </c>
+      <c r="H1114" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1114" s="4" t="inlineStr"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1115" s="6" t="inlineStr">
+        <is>
+          <t>04:30:23</t>
+        </is>
+      </c>
+      <c r="C1115" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1115" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1115" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1115" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1115" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261001043023954770.pages</t>
+        </is>
+      </c>
+      <c r="H1115" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1115" s="7" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1116" s="3" t="inlineStr">
+        <is>
+          <t>04:30:26</t>
+        </is>
+      </c>
+      <c r="C1116" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1116" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1116" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1116" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1116" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261001043026714271.pdf</t>
+        </is>
+      </c>
+      <c r="H1116" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1116" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1116"/>
+  <dimension ref="A1:I1139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48487,6 +48487,995 @@
       </c>
       <c r="I1116" s="4" t="inlineStr"/>
     </row>
+    <row r="1117">
+      <c r="A1117" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1117" s="6" t="inlineStr">
+        <is>
+          <t>04:22:47</t>
+        </is>
+      </c>
+      <c r="C1117" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1117" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1117" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1117" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1117" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261002042247669567.gif</t>
+        </is>
+      </c>
+      <c r="H1117" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1117" s="7" t="inlineStr"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1118" s="3" t="inlineStr">
+        <is>
+          <t>04:22:47</t>
+        </is>
+      </c>
+      <c r="C1118" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1118" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1118" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1118" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1118" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261002042247933591.xlsx</t>
+        </is>
+      </c>
+      <c r="H1118" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1118" s="4" t="inlineStr"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1119" s="6" t="inlineStr">
+        <is>
+          <t>04:22:48</t>
+        </is>
+      </c>
+      <c r="C1119" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1119" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1119" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1119" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1119" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261002042248182556.csv</t>
+        </is>
+      </c>
+      <c r="H1119" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1119" s="7" t="inlineStr"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1120" s="3" t="inlineStr">
+        <is>
+          <t>04:22:48</t>
+        </is>
+      </c>
+      <c r="C1120" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1120" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1120" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1120" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1120" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261002042248460138.pdf</t>
+        </is>
+      </c>
+      <c r="H1120" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1120" s="4" t="inlineStr"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1121" s="6" t="inlineStr">
+        <is>
+          <t>04:22:48</t>
+        </is>
+      </c>
+      <c r="C1121" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1121" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1121" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1121" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1121" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261002042248710434.docx</t>
+        </is>
+      </c>
+      <c r="H1121" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1121" s="7" t="inlineStr"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1122" s="3" t="inlineStr">
+        <is>
+          <t>04:22:48</t>
+        </is>
+      </c>
+      <c r="C1122" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1122" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1122" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1122" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1122" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261002042248954929.pptx</t>
+        </is>
+      </c>
+      <c r="H1122" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1122" s="4" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1123" s="6" t="inlineStr">
+        <is>
+          <t>04:22:49</t>
+        </is>
+      </c>
+      <c r="C1123" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1123" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1123" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1123" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1123" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261002042249231939.jpg</t>
+        </is>
+      </c>
+      <c r="H1123" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1123" s="7" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1124" s="3" t="inlineStr">
+        <is>
+          <t>04:22:49</t>
+        </is>
+      </c>
+      <c r="C1124" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1124" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1124" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1124" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1124" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261002042249478850.doc</t>
+        </is>
+      </c>
+      <c r="H1124" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1124" s="4" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1125" s="6" t="inlineStr">
+        <is>
+          <t>04:22:49</t>
+        </is>
+      </c>
+      <c r="C1125" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1125" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1125" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1125" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1125" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261002042249749874.txt</t>
+        </is>
+      </c>
+      <c r="H1125" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1125" s="7" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1126" s="3" t="inlineStr">
+        <is>
+          <t>04:22:49</t>
+        </is>
+      </c>
+      <c r="C1126" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1126" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1126" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1126" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1126" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261002042249998287.xls</t>
+        </is>
+      </c>
+      <c r="H1126" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1126" s="4" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1127" s="6" t="inlineStr">
+        <is>
+          <t>04:22:50</t>
+        </is>
+      </c>
+      <c r="C1127" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1127" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1127" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1127" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1127" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261002042250272579.png</t>
+        </is>
+      </c>
+      <c r="H1127" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1127" s="7" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1128" s="3" t="inlineStr">
+        <is>
+          <t>04:22:50</t>
+        </is>
+      </c>
+      <c r="C1128" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1128" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1128" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1128" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1128" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261002042250522258.dat</t>
+        </is>
+      </c>
+      <c r="H1128" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1128" s="4" t="inlineStr"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1129" s="6" t="inlineStr">
+        <is>
+          <t>04:22:52</t>
+        </is>
+      </c>
+      <c r="C1129" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1129" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1129" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1129" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1129" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261002042252553985.docx</t>
+        </is>
+      </c>
+      <c r="H1129" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1129" s="7" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1130" s="3" t="inlineStr">
+        <is>
+          <t>04:22:52</t>
+        </is>
+      </c>
+      <c r="C1130" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1130" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1130" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1130" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1130" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261002042252796595.pdf</t>
+        </is>
+      </c>
+      <c r="H1130" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1130" s="4" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1131" s="6" t="inlineStr">
+        <is>
+          <t>04:22:53</t>
+        </is>
+      </c>
+      <c r="C1131" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1131" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1131" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1131" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1131" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261002042253062035.jpeg</t>
+        </is>
+      </c>
+      <c r="H1131" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1131" s="7" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1132" s="3" t="inlineStr">
+        <is>
+          <t>04:22:53</t>
+        </is>
+      </c>
+      <c r="C1132" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1132" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1132" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1132" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1132" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261002042253304222.xlsx</t>
+        </is>
+      </c>
+      <c r="H1132" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1132" s="4" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1133" s="6" t="inlineStr">
+        <is>
+          <t>04:22:53</t>
+        </is>
+      </c>
+      <c r="C1133" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1133" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1133" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1133" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1133" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261002042253930714.txt</t>
+        </is>
+      </c>
+      <c r="H1133" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1133" s="7" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1134" s="3" t="inlineStr">
+        <is>
+          <t>04:22:54</t>
+        </is>
+      </c>
+      <c r="C1134" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1134" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1134" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1134" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1134" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261002042254177449.xlsx</t>
+        </is>
+      </c>
+      <c r="H1134" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1134" s="4" t="inlineStr"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1135" s="6" t="inlineStr">
+        <is>
+          <t>04:22:54</t>
+        </is>
+      </c>
+      <c r="C1135" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1135" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1135" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1135" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1135" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1135" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1135" s="7" t="inlineStr"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1136" s="3" t="inlineStr">
+        <is>
+          <t>04:22:55</t>
+        </is>
+      </c>
+      <c r="C1136" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1136" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1136" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1136" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1136" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261002042255229662.pdf</t>
+        </is>
+      </c>
+      <c r="H1136" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1136" s="4" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1137" s="6" t="inlineStr">
+        <is>
+          <t>04:22:55</t>
+        </is>
+      </c>
+      <c r="C1137" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1137" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1137" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1137" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1137" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261002042255472969.jpeg</t>
+        </is>
+      </c>
+      <c r="H1137" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1137" s="7" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1138" s="3" t="inlineStr">
+        <is>
+          <t>04:22:55</t>
+        </is>
+      </c>
+      <c r="C1138" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1138" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1138" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1138" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1138" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261002042255741671.pages</t>
+        </is>
+      </c>
+      <c r="H1138" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1138" s="4" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1139" s="6" t="inlineStr">
+        <is>
+          <t>04:22:56</t>
+        </is>
+      </c>
+      <c r="C1139" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1139" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1139" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1139" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1139" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261002042256681038.pdf</t>
+        </is>
+      </c>
+      <c r="H1139" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1139" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1139"/>
+  <dimension ref="A1:I1162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49476,6 +49476,995 @@
       </c>
       <c r="I1139" s="7" t="inlineStr"/>
     </row>
+    <row r="1140">
+      <c r="A1140" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1140" s="3" t="inlineStr">
+        <is>
+          <t>04:05:05</t>
+        </is>
+      </c>
+      <c r="C1140" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1140" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1140" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1140" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1140" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261003040505208742.gif</t>
+        </is>
+      </c>
+      <c r="H1140" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1140" s="4" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1141" s="6" t="inlineStr">
+        <is>
+          <t>04:05:05</t>
+        </is>
+      </c>
+      <c r="C1141" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1141" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1141" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1141" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1141" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261003040505448691.xlsx</t>
+        </is>
+      </c>
+      <c r="H1141" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1141" s="7" t="inlineStr"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1142" s="3" t="inlineStr">
+        <is>
+          <t>04:05:05</t>
+        </is>
+      </c>
+      <c r="C1142" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1142" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1142" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1142" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1142" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261003040505677501.csv</t>
+        </is>
+      </c>
+      <c r="H1142" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1142" s="4" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1143" s="6" t="inlineStr">
+        <is>
+          <t>04:05:05</t>
+        </is>
+      </c>
+      <c r="C1143" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1143" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1143" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1143" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1143" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261003040505927785.pdf</t>
+        </is>
+      </c>
+      <c r="H1143" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1143" s="7" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1144" s="3" t="inlineStr">
+        <is>
+          <t>04:05:06</t>
+        </is>
+      </c>
+      <c r="C1144" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1144" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1144" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1144" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1144" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261003040506154549.docx</t>
+        </is>
+      </c>
+      <c r="H1144" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1144" s="4" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1145" s="6" t="inlineStr">
+        <is>
+          <t>04:05:06</t>
+        </is>
+      </c>
+      <c r="C1145" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1145" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1145" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1145" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1145" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261003040506402634.pptx</t>
+        </is>
+      </c>
+      <c r="H1145" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1145" s="7" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1146" s="3" t="inlineStr">
+        <is>
+          <t>04:05:06</t>
+        </is>
+      </c>
+      <c r="C1146" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1146" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1146" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1146" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1146" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261003040506628819.jpg</t>
+        </is>
+      </c>
+      <c r="H1146" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1146" s="4" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1147" s="6" t="inlineStr">
+        <is>
+          <t>04:05:06</t>
+        </is>
+      </c>
+      <c r="C1147" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1147" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1147" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1147" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1147" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261003040506855430.doc</t>
+        </is>
+      </c>
+      <c r="H1147" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1147" s="7" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1148" s="3" t="inlineStr">
+        <is>
+          <t>04:05:07</t>
+        </is>
+      </c>
+      <c r="C1148" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1148" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1148" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1148" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1148" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261003040507108577.txt</t>
+        </is>
+      </c>
+      <c r="H1148" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1148" s="4" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1149" s="6" t="inlineStr">
+        <is>
+          <t>04:05:07</t>
+        </is>
+      </c>
+      <c r="C1149" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1149" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1149" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1149" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1149" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261003040507334600.xls</t>
+        </is>
+      </c>
+      <c r="H1149" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1149" s="7" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1150" s="3" t="inlineStr">
+        <is>
+          <t>04:05:07</t>
+        </is>
+      </c>
+      <c r="C1150" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1150" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1150" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1150" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1150" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261003040507581454.png</t>
+        </is>
+      </c>
+      <c r="H1150" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1150" s="4" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1151" s="6" t="inlineStr">
+        <is>
+          <t>04:05:07</t>
+        </is>
+      </c>
+      <c r="C1151" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1151" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1151" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1151" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1151" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261003040507809750.dat</t>
+        </is>
+      </c>
+      <c r="H1151" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1151" s="7" t="inlineStr"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1152" s="3" t="inlineStr">
+        <is>
+          <t>04:05:09</t>
+        </is>
+      </c>
+      <c r="C1152" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1152" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1152" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1152" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1152" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261003040509619125.docx</t>
+        </is>
+      </c>
+      <c r="H1152" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1152" s="4" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1153" s="6" t="inlineStr">
+        <is>
+          <t>04:05:09</t>
+        </is>
+      </c>
+      <c r="C1153" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1153" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1153" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1153" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1153" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261003040509848335.pdf</t>
+        </is>
+      </c>
+      <c r="H1153" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1153" s="7" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1154" s="3" t="inlineStr">
+        <is>
+          <t>04:05:10</t>
+        </is>
+      </c>
+      <c r="C1154" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1154" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1154" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1154" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1154" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261003040510101598.jpeg</t>
+        </is>
+      </c>
+      <c r="H1154" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1154" s="4" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1155" s="6" t="inlineStr">
+        <is>
+          <t>04:05:10</t>
+        </is>
+      </c>
+      <c r="C1155" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1155" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1155" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1155" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1155" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261003040510330070.xlsx</t>
+        </is>
+      </c>
+      <c r="H1155" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1155" s="7" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1156" s="3" t="inlineStr">
+        <is>
+          <t>04:05:11</t>
+        </is>
+      </c>
+      <c r="C1156" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1156" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1156" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1156" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1156" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261003040511280871.txt</t>
+        </is>
+      </c>
+      <c r="H1156" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1156" s="4" t="inlineStr"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1157" s="6" t="inlineStr">
+        <is>
+          <t>04:05:11</t>
+        </is>
+      </c>
+      <c r="C1157" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1157" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1157" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1157" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1157" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261003040511511111.xlsx</t>
+        </is>
+      </c>
+      <c r="H1157" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1157" s="7" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1158" s="3" t="inlineStr">
+        <is>
+          <t>04:05:11</t>
+        </is>
+      </c>
+      <c r="C1158" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1158" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1158" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1158" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1158" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1158" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1158" s="4" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1159" s="6" t="inlineStr">
+        <is>
+          <t>04:05:12</t>
+        </is>
+      </c>
+      <c r="C1159" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1159" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1159" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1159" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1159" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261003040512517431.pdf</t>
+        </is>
+      </c>
+      <c r="H1159" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1159" s="7" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1160" s="3" t="inlineStr">
+        <is>
+          <t>04:05:12</t>
+        </is>
+      </c>
+      <c r="C1160" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1160" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1160" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1160" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1160" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261003040512775007.jpeg</t>
+        </is>
+      </c>
+      <c r="H1160" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1160" s="4" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1161" s="6" t="inlineStr">
+        <is>
+          <t>04:05:13</t>
+        </is>
+      </c>
+      <c r="C1161" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1161" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1161" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1161" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1161" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261003040513006562.pages</t>
+        </is>
+      </c>
+      <c r="H1161" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1161" s="7" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1162" s="3" t="inlineStr">
+        <is>
+          <t>04:05:13</t>
+        </is>
+      </c>
+      <c r="C1162" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1162" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1162" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1162" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1162" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261003040513884241.pdf</t>
+        </is>
+      </c>
+      <c r="H1162" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1162" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1162"/>
+  <dimension ref="A1:I1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50465,6 +50465,995 @@
       </c>
       <c r="I1162" s="4" t="inlineStr"/>
     </row>
+    <row r="1163">
+      <c r="A1163" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1163" s="6" t="inlineStr">
+        <is>
+          <t>04:37:52</t>
+        </is>
+      </c>
+      <c r="C1163" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1163" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1163" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1163" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1163" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261004043752940099.gif</t>
+        </is>
+      </c>
+      <c r="H1163" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1163" s="7" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1164" s="3" t="inlineStr">
+        <is>
+          <t>04:37:53</t>
+        </is>
+      </c>
+      <c r="C1164" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1164" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1164" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1164" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1164" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261004043753173643.xlsx</t>
+        </is>
+      </c>
+      <c r="H1164" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1164" s="4" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1165" s="6" t="inlineStr">
+        <is>
+          <t>04:37:53</t>
+        </is>
+      </c>
+      <c r="C1165" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1165" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1165" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1165" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1165" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261004043753393121.csv</t>
+        </is>
+      </c>
+      <c r="H1165" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1165" s="7" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1166" s="3" t="inlineStr">
+        <is>
+          <t>04:37:53</t>
+        </is>
+      </c>
+      <c r="C1166" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1166" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1166" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1166" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1166" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261004043753637741.pdf</t>
+        </is>
+      </c>
+      <c r="H1166" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1166" s="4" t="inlineStr"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1167" s="6" t="inlineStr">
+        <is>
+          <t>04:37:53</t>
+        </is>
+      </c>
+      <c r="C1167" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1167" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1167" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1167" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1167" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261004043753868072.docx</t>
+        </is>
+      </c>
+      <c r="H1167" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1167" s="7" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1168" s="3" t="inlineStr">
+        <is>
+          <t>04:37:54</t>
+        </is>
+      </c>
+      <c r="C1168" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1168" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1168" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1168" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1168" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261004043754110109.pptx</t>
+        </is>
+      </c>
+      <c r="H1168" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1168" s="4" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1169" s="6" t="inlineStr">
+        <is>
+          <t>04:37:54</t>
+        </is>
+      </c>
+      <c r="C1169" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1169" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1169" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1169" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1169" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261004043754332065.jpg</t>
+        </is>
+      </c>
+      <c r="H1169" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1169" s="7" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1170" s="3" t="inlineStr">
+        <is>
+          <t>04:37:54</t>
+        </is>
+      </c>
+      <c r="C1170" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1170" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1170" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1170" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1170" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261004043754574528.doc</t>
+        </is>
+      </c>
+      <c r="H1170" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1170" s="4" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1171" s="6" t="inlineStr">
+        <is>
+          <t>04:37:54</t>
+        </is>
+      </c>
+      <c r="C1171" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1171" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1171" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1171" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1171" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261004043754794430.txt</t>
+        </is>
+      </c>
+      <c r="H1171" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1171" s="7" t="inlineStr"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1172" s="3" t="inlineStr">
+        <is>
+          <t>04:37:55</t>
+        </is>
+      </c>
+      <c r="C1172" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1172" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1172" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1172" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1172" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261004043755013723.xls</t>
+        </is>
+      </c>
+      <c r="H1172" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1172" s="4" t="inlineStr"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1173" s="6" t="inlineStr">
+        <is>
+          <t>04:37:55</t>
+        </is>
+      </c>
+      <c r="C1173" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1173" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1173" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1173" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1173" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261004043755260661.png</t>
+        </is>
+      </c>
+      <c r="H1173" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1173" s="7" t="inlineStr"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1174" s="3" t="inlineStr">
+        <is>
+          <t>04:37:55</t>
+        </is>
+      </c>
+      <c r="C1174" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1174" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1174" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1174" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1174" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261004043755480274.dat</t>
+        </is>
+      </c>
+      <c r="H1174" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1174" s="4" t="inlineStr"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1175" s="6" t="inlineStr">
+        <is>
+          <t>04:37:57</t>
+        </is>
+      </c>
+      <c r="C1175" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1175" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1175" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1175" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1175" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261004043757279184.docx</t>
+        </is>
+      </c>
+      <c r="H1175" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1175" s="7" t="inlineStr"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1176" s="3" t="inlineStr">
+        <is>
+          <t>04:37:57</t>
+        </is>
+      </c>
+      <c r="C1176" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1176" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1176" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1176" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1176" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261004043757500088.pdf</t>
+        </is>
+      </c>
+      <c r="H1176" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1176" s="4" t="inlineStr"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1177" s="6" t="inlineStr">
+        <is>
+          <t>04:37:57</t>
+        </is>
+      </c>
+      <c r="C1177" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1177" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1177" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1177" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1177" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261004043757742402.jpeg</t>
+        </is>
+      </c>
+      <c r="H1177" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1177" s="7" t="inlineStr"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1178" s="3" t="inlineStr">
+        <is>
+          <t>04:37:57</t>
+        </is>
+      </c>
+      <c r="C1178" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1178" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1178" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1178" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1178" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261004043757964368.xlsx</t>
+        </is>
+      </c>
+      <c r="H1178" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1178" s="4" t="inlineStr"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1179" s="6" t="inlineStr">
+        <is>
+          <t>04:37:58</t>
+        </is>
+      </c>
+      <c r="C1179" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1179" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1179" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1179" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1179" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261004043758546403.txt</t>
+        </is>
+      </c>
+      <c r="H1179" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1179" s="7" t="inlineStr"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1180" s="3" t="inlineStr">
+        <is>
+          <t>04:37:58</t>
+        </is>
+      </c>
+      <c r="C1180" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1180" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1180" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1180" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1180" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261004043758770029.xlsx</t>
+        </is>
+      </c>
+      <c r="H1180" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1180" s="4" t="inlineStr"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1181" s="6" t="inlineStr">
+        <is>
+          <t>04:37:59</t>
+        </is>
+      </c>
+      <c r="C1181" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1181" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1181" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1181" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1181" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1181" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1181" s="7" t="inlineStr"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1182" s="3" t="inlineStr">
+        <is>
+          <t>04:37:59</t>
+        </is>
+      </c>
+      <c r="C1182" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1182" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1182" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1182" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1182" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261004043759463255.pdf</t>
+        </is>
+      </c>
+      <c r="H1182" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1182" s="4" t="inlineStr"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1183" s="6" t="inlineStr">
+        <is>
+          <t>04:37:59</t>
+        </is>
+      </c>
+      <c r="C1183" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1183" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1183" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1183" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1183" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261004043759711773.jpeg</t>
+        </is>
+      </c>
+      <c r="H1183" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1183" s="7" t="inlineStr"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1184" s="3" t="inlineStr">
+        <is>
+          <t>04:37:59</t>
+        </is>
+      </c>
+      <c r="C1184" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1184" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1184" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1184" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1184" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261004043759936203.pages</t>
+        </is>
+      </c>
+      <c r="H1184" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1184" s="4" t="inlineStr"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1185" s="6" t="inlineStr">
+        <is>
+          <t>04:38:01</t>
+        </is>
+      </c>
+      <c r="C1185" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1185" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1185" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1185" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1185" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261004043801237042.pdf</t>
+        </is>
+      </c>
+      <c r="H1185" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1185" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1185"/>
+  <dimension ref="A1:I1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -51454,6 +51454,995 @@
       </c>
       <c r="I1185" s="7" t="inlineStr"/>
     </row>
+    <row r="1186">
+      <c r="A1186" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1186" s="3" t="inlineStr">
+        <is>
+          <t>04:24:09</t>
+        </is>
+      </c>
+      <c r="C1186" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1186" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1186" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1186" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1186" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261005042409778012.gif</t>
+        </is>
+      </c>
+      <c r="H1186" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1186" s="4" t="inlineStr"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1187" s="6" t="inlineStr">
+        <is>
+          <t>04:24:09</t>
+        </is>
+      </c>
+      <c r="C1187" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1187" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1187" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1187" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1187" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261005042409909432.xlsx</t>
+        </is>
+      </c>
+      <c r="H1187" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1187" s="7" t="inlineStr"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1188" s="3" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1188" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1188" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1188" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1188" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1188" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261005042410037175.csv</t>
+        </is>
+      </c>
+      <c r="H1188" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1188" s="4" t="inlineStr"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1189" s="6" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1189" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1189" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1189" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1189" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1189" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261005042410179626.pdf</t>
+        </is>
+      </c>
+      <c r="H1189" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1189" s="7" t="inlineStr"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1190" s="3" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1190" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1190" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1190" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1190" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1190" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261005042410310828.docx</t>
+        </is>
+      </c>
+      <c r="H1190" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1190" s="4" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1191" s="6" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1191" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1191" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1191" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1191" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1191" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261005042410460797.pptx</t>
+        </is>
+      </c>
+      <c r="H1191" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1191" s="7" t="inlineStr"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1192" s="3" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1192" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1192" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1192" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1192" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1192" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261005042410588851.jpg</t>
+        </is>
+      </c>
+      <c r="H1192" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1192" s="4" t="inlineStr"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1193" s="6" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1193" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1193" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1193" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1193" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1193" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261005042410744676.doc</t>
+        </is>
+      </c>
+      <c r="H1193" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1193" s="7" t="inlineStr"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1194" s="3" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1194" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1194" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1194" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1194" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1194" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261005042410875107.txt</t>
+        </is>
+      </c>
+      <c r="H1194" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1194" s="4" t="inlineStr"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1195" s="6" t="inlineStr">
+        <is>
+          <t>04:24:11</t>
+        </is>
+      </c>
+      <c r="C1195" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1195" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1195" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1195" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1195" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261005042411027126.xls</t>
+        </is>
+      </c>
+      <c r="H1195" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1195" s="7" t="inlineStr"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1196" s="3" t="inlineStr">
+        <is>
+          <t>04:24:11</t>
+        </is>
+      </c>
+      <c r="C1196" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1196" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1196" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1196" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1196" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261005042411158377.png</t>
+        </is>
+      </c>
+      <c r="H1196" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1196" s="4" t="inlineStr"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1197" s="6" t="inlineStr">
+        <is>
+          <t>04:24:11</t>
+        </is>
+      </c>
+      <c r="C1197" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1197" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1197" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1197" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1197" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261005042411317158.dat</t>
+        </is>
+      </c>
+      <c r="H1197" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1197" s="7" t="inlineStr"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1198" s="3" t="inlineStr">
+        <is>
+          <t>04:24:12</t>
+        </is>
+      </c>
+      <c r="C1198" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1198" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1198" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1198" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1198" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261005042412822604.docx</t>
+        </is>
+      </c>
+      <c r="H1198" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1198" s="4" t="inlineStr"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1199" s="6" t="inlineStr">
+        <is>
+          <t>04:24:12</t>
+        </is>
+      </c>
+      <c r="C1199" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1199" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1199" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1199" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1199" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261005042412948642.pdf</t>
+        </is>
+      </c>
+      <c r="H1199" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1199" s="7" t="inlineStr"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1200" s="3" t="inlineStr">
+        <is>
+          <t>04:24:13</t>
+        </is>
+      </c>
+      <c r="C1200" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1200" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1200" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1200" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1200" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261005042413108090.jpeg</t>
+        </is>
+      </c>
+      <c r="H1200" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1200" s="4" t="inlineStr"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1201" s="6" t="inlineStr">
+        <is>
+          <t>04:24:13</t>
+        </is>
+      </c>
+      <c r="C1201" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1201" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1201" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1201" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1201" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261005042413237077.xlsx</t>
+        </is>
+      </c>
+      <c r="H1201" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1201" s="7" t="inlineStr"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1202" s="3" t="inlineStr">
+        <is>
+          <t>04:24:13</t>
+        </is>
+      </c>
+      <c r="C1202" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1202" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1202" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1202" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1202" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261005042413741558.txt</t>
+        </is>
+      </c>
+      <c r="H1202" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1202" s="4" t="inlineStr"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1203" s="6" t="inlineStr">
+        <is>
+          <t>04:24:13</t>
+        </is>
+      </c>
+      <c r="C1203" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1203" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1203" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1203" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1203" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261005042413872788.xlsx</t>
+        </is>
+      </c>
+      <c r="H1203" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1203" s="7" t="inlineStr"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1204" s="3" t="inlineStr">
+        <is>
+          <t>04:24:14</t>
+        </is>
+      </c>
+      <c r="C1204" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1204" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1204" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1204" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1204" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1204" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1204" s="4" t="inlineStr"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1205" s="6" t="inlineStr">
+        <is>
+          <t>04:24:14</t>
+        </is>
+      </c>
+      <c r="C1205" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1205" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1205" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1205" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1205" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261005042414372949.pdf</t>
+        </is>
+      </c>
+      <c r="H1205" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1205" s="7" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1206" s="3" t="inlineStr">
+        <is>
+          <t>04:24:14</t>
+        </is>
+      </c>
+      <c r="C1206" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1206" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1206" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1206" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1206" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261005042414521515.jpeg</t>
+        </is>
+      </c>
+      <c r="H1206" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1206" s="4" t="inlineStr"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1207" s="6" t="inlineStr">
+        <is>
+          <t>04:24:14</t>
+        </is>
+      </c>
+      <c r="C1207" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1207" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1207" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1207" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1207" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261005042414651547.pages</t>
+        </is>
+      </c>
+      <c r="H1207" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1207" s="7" t="inlineStr"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1208" s="3" t="inlineStr">
+        <is>
+          <t>04:24:15</t>
+        </is>
+      </c>
+      <c r="C1208" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1208" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1208" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1208" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1208" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261005042415179727.pdf</t>
+        </is>
+      </c>
+      <c r="H1208" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1208" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1208"/>
+  <dimension ref="A1:I1231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52443,6 +52443,995 @@
       </c>
       <c r="I1208" s="4" t="inlineStr"/>
     </row>
+    <row r="1209">
+      <c r="A1209" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1209" s="6" t="inlineStr">
+        <is>
+          <t>05:11:30</t>
+        </is>
+      </c>
+      <c r="C1209" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1209" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1209" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1209" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1209" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261006051130091717.gif</t>
+        </is>
+      </c>
+      <c r="H1209" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1209" s="7" t="inlineStr"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1210" s="3" t="inlineStr">
+        <is>
+          <t>05:11:30</t>
+        </is>
+      </c>
+      <c r="C1210" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1210" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1210" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1210" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1210" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261006051130324716.xlsx</t>
+        </is>
+      </c>
+      <c r="H1210" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1210" s="4" t="inlineStr"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1211" s="6" t="inlineStr">
+        <is>
+          <t>05:11:30</t>
+        </is>
+      </c>
+      <c r="C1211" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1211" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1211" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1211" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1211" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261006051130541692.csv</t>
+        </is>
+      </c>
+      <c r="H1211" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1211" s="7" t="inlineStr"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1212" s="3" t="inlineStr">
+        <is>
+          <t>05:11:30</t>
+        </is>
+      </c>
+      <c r="C1212" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1212" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1212" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1212" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1212" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261006051130787913.pdf</t>
+        </is>
+      </c>
+      <c r="H1212" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1212" s="4" t="inlineStr"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1213" s="6" t="inlineStr">
+        <is>
+          <t>05:11:31</t>
+        </is>
+      </c>
+      <c r="C1213" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1213" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1213" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1213" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1213" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261006051131013176.docx</t>
+        </is>
+      </c>
+      <c r="H1213" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1213" s="7" t="inlineStr"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1214" s="3" t="inlineStr">
+        <is>
+          <t>05:11:31</t>
+        </is>
+      </c>
+      <c r="C1214" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1214" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1214" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1214" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1214" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261006051131269381.pptx</t>
+        </is>
+      </c>
+      <c r="H1214" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1214" s="4" t="inlineStr"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1215" s="6" t="inlineStr">
+        <is>
+          <t>05:11:31</t>
+        </is>
+      </c>
+      <c r="C1215" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1215" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1215" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1215" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1215" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261006051131486899.jpg</t>
+        </is>
+      </c>
+      <c r="H1215" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1215" s="7" t="inlineStr"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1216" s="3" t="inlineStr">
+        <is>
+          <t>05:11:31</t>
+        </is>
+      </c>
+      <c r="C1216" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1216" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1216" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1216" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1216" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261006051131728753.doc</t>
+        </is>
+      </c>
+      <c r="H1216" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1216" s="4" t="inlineStr"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1217" s="6" t="inlineStr">
+        <is>
+          <t>05:11:31</t>
+        </is>
+      </c>
+      <c r="C1217" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1217" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1217" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1217" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1217" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261006051131957984.txt</t>
+        </is>
+      </c>
+      <c r="H1217" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1217" s="7" t="inlineStr"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1218" s="3" t="inlineStr">
+        <is>
+          <t>05:11:32</t>
+        </is>
+      </c>
+      <c r="C1218" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1218" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1218" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1218" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1218" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261006051132201674.xls</t>
+        </is>
+      </c>
+      <c r="H1218" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1218" s="4" t="inlineStr"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1219" s="6" t="inlineStr">
+        <is>
+          <t>05:11:32</t>
+        </is>
+      </c>
+      <c r="C1219" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1219" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1219" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1219" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1219" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261006051132423053.png</t>
+        </is>
+      </c>
+      <c r="H1219" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1219" s="7" t="inlineStr"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1220" s="3" t="inlineStr">
+        <is>
+          <t>05:11:32</t>
+        </is>
+      </c>
+      <c r="C1220" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1220" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1220" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1220" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1220" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261006051132670393.dat</t>
+        </is>
+      </c>
+      <c r="H1220" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1220" s="4" t="inlineStr"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1221" s="6" t="inlineStr">
+        <is>
+          <t>05:11:34</t>
+        </is>
+      </c>
+      <c r="C1221" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1221" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1221" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1221" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1221" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261006051134152786.docx</t>
+        </is>
+      </c>
+      <c r="H1221" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1221" s="7" t="inlineStr"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1222" s="3" t="inlineStr">
+        <is>
+          <t>05:11:34</t>
+        </is>
+      </c>
+      <c r="C1222" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1222" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1222" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1222" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1222" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261006051134402802.pdf</t>
+        </is>
+      </c>
+      <c r="H1222" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1222" s="4" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1223" s="6" t="inlineStr">
+        <is>
+          <t>05:11:34</t>
+        </is>
+      </c>
+      <c r="C1223" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1223" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1223" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1223" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1223" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261006051134627839.jpeg</t>
+        </is>
+      </c>
+      <c r="H1223" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1223" s="7" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1224" s="3" t="inlineStr">
+        <is>
+          <t>05:11:34</t>
+        </is>
+      </c>
+      <c r="C1224" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1224" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1224" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1224" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1224" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261006051134876093.xlsx</t>
+        </is>
+      </c>
+      <c r="H1224" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1224" s="4" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1225" s="6" t="inlineStr">
+        <is>
+          <t>05:11:35</t>
+        </is>
+      </c>
+      <c r="C1225" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1225" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1225" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1225" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1225" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261006051135501729.txt</t>
+        </is>
+      </c>
+      <c r="H1225" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1225" s="7" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1226" s="3" t="inlineStr">
+        <is>
+          <t>05:11:35</t>
+        </is>
+      </c>
+      <c r="C1226" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1226" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1226" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1226" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1226" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261006051135752699.xlsx</t>
+        </is>
+      </c>
+      <c r="H1226" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1226" s="4" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1227" s="6" t="inlineStr">
+        <is>
+          <t>05:11:35</t>
+        </is>
+      </c>
+      <c r="C1227" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1227" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1227" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1227" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1227" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1227" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1227" s="7" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="inlineStr">
+        <is>
+          <t>05:11:36</t>
+        </is>
+      </c>
+      <c r="C1228" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1228" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1228" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1228" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1228" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261006051136453291.pdf</t>
+        </is>
+      </c>
+      <c r="H1228" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1228" s="4" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1229" s="6" t="inlineStr">
+        <is>
+          <t>05:11:36</t>
+        </is>
+      </c>
+      <c r="C1229" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1229" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1229" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1229" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1229" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261006051136676032.jpeg</t>
+        </is>
+      </c>
+      <c r="H1229" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1229" s="7" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1230" s="3" t="inlineStr">
+        <is>
+          <t>05:11:36</t>
+        </is>
+      </c>
+      <c r="C1230" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1230" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1230" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1230" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1230" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261006051136929778.pages</t>
+        </is>
+      </c>
+      <c r="H1230" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1230" s="4" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1231" s="6" t="inlineStr">
+        <is>
+          <t>05:11:37</t>
+        </is>
+      </c>
+      <c r="C1231" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1231" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1231" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1231" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1231" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261006051137786648.pdf</t>
+        </is>
+      </c>
+      <c r="H1231" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1231" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1231"/>
+  <dimension ref="A1:I1254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -53432,6 +53432,995 @@
       </c>
       <c r="I1231" s="7" t="inlineStr"/>
     </row>
+    <row r="1232">
+      <c r="A1232" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1232" s="3" t="inlineStr">
+        <is>
+          <t>04:38:56</t>
+        </is>
+      </c>
+      <c r="C1232" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1232" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1232" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1232" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1232" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261007043856980647.gif</t>
+        </is>
+      </c>
+      <c r="H1232" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1232" s="4" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1233" s="6" t="inlineStr">
+        <is>
+          <t>04:38:57</t>
+        </is>
+      </c>
+      <c r="C1233" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1233" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1233" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1233" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1233" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261007043857204049.xlsx</t>
+        </is>
+      </c>
+      <c r="H1233" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1233" s="7" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1234" s="3" t="inlineStr">
+        <is>
+          <t>04:38:57</t>
+        </is>
+      </c>
+      <c r="C1234" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1234" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1234" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1234" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1234" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261007043857484959.csv</t>
+        </is>
+      </c>
+      <c r="H1234" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1234" s="4" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1235" s="6" t="inlineStr">
+        <is>
+          <t>04:38:57</t>
+        </is>
+      </c>
+      <c r="C1235" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1235" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1235" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1235" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1235" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261007043857893854.pdf</t>
+        </is>
+      </c>
+      <c r="H1235" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1235" s="7" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1236" s="3" t="inlineStr">
+        <is>
+          <t>04:38:58</t>
+        </is>
+      </c>
+      <c r="C1236" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1236" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1236" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1236" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1236" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261007043858244172.docx</t>
+        </is>
+      </c>
+      <c r="H1236" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1236" s="4" t="inlineStr"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1237" s="6" t="inlineStr">
+        <is>
+          <t>04:38:58</t>
+        </is>
+      </c>
+      <c r="C1237" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1237" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1237" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1237" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1237" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261007043858611565.pptx</t>
+        </is>
+      </c>
+      <c r="H1237" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1237" s="7" t="inlineStr"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1238" s="3" t="inlineStr">
+        <is>
+          <t>04:38:58</t>
+        </is>
+      </c>
+      <c r="C1238" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1238" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1238" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1238" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1238" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261007043858957879.jpg</t>
+        </is>
+      </c>
+      <c r="H1238" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1238" s="4" t="inlineStr"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1239" s="6" t="inlineStr">
+        <is>
+          <t>04:38:59</t>
+        </is>
+      </c>
+      <c r="C1239" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1239" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1239" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1239" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1239" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261007043859365861.doc</t>
+        </is>
+      </c>
+      <c r="H1239" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1239" s="7" t="inlineStr"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1240" s="3" t="inlineStr">
+        <is>
+          <t>04:38:59</t>
+        </is>
+      </c>
+      <c r="C1240" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1240" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1240" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1240" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1240" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261007043859697182.txt</t>
+        </is>
+      </c>
+      <c r="H1240" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1240" s="4" t="inlineStr"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1241" s="6" t="inlineStr">
+        <is>
+          <t>04:38:59</t>
+        </is>
+      </c>
+      <c r="C1241" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1241" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1241" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1241" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1241" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261007043859937125.xls</t>
+        </is>
+      </c>
+      <c r="H1241" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1241" s="7" t="inlineStr"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1242" s="3" t="inlineStr">
+        <is>
+          <t>04:39:00</t>
+        </is>
+      </c>
+      <c r="C1242" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1242" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1242" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1242" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1242" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261007043900305976.png</t>
+        </is>
+      </c>
+      <c r="H1242" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1242" s="4" t="inlineStr"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1243" s="6" t="inlineStr">
+        <is>
+          <t>04:39:00</t>
+        </is>
+      </c>
+      <c r="C1243" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1243" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1243" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1243" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1243" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261007043900695255.dat</t>
+        </is>
+      </c>
+      <c r="H1243" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1243" s="7" t="inlineStr"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1244" s="3" t="inlineStr">
+        <is>
+          <t>04:39:02</t>
+        </is>
+      </c>
+      <c r="C1244" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1244" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1244" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1244" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1244" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261007043902042788.docx</t>
+        </is>
+      </c>
+      <c r="H1244" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1244" s="4" t="inlineStr"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1245" s="6" t="inlineStr">
+        <is>
+          <t>04:39:02</t>
+        </is>
+      </c>
+      <c r="C1245" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1245" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1245" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1245" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1245" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261007043902269460.pdf</t>
+        </is>
+      </c>
+      <c r="H1245" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1245" s="7" t="inlineStr"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1246" s="3" t="inlineStr">
+        <is>
+          <t>04:39:02</t>
+        </is>
+      </c>
+      <c r="C1246" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1246" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1246" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1246" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1246" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261007043902467294.jpeg</t>
+        </is>
+      </c>
+      <c r="H1246" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1246" s="4" t="inlineStr"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1247" s="6" t="inlineStr">
+        <is>
+          <t>04:39:02</t>
+        </is>
+      </c>
+      <c r="C1247" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1247" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1247" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1247" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1247" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261007043902694240.xlsx</t>
+        </is>
+      </c>
+      <c r="H1247" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1247" s="7" t="inlineStr"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1248" s="3" t="inlineStr">
+        <is>
+          <t>04:39:03</t>
+        </is>
+      </c>
+      <c r="C1248" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1248" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1248" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1248" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1248" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261007043903213775.txt</t>
+        </is>
+      </c>
+      <c r="H1248" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1248" s="4" t="inlineStr"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1249" s="6" t="inlineStr">
+        <is>
+          <t>04:39:03</t>
+        </is>
+      </c>
+      <c r="C1249" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1249" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1249" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1249" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1249" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261007043903435680.xlsx</t>
+        </is>
+      </c>
+      <c r="H1249" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1249" s="7" t="inlineStr"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1250" s="3" t="inlineStr">
+        <is>
+          <t>04:39:03</t>
+        </is>
+      </c>
+      <c r="C1250" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1250" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1250" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1250" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1250" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1250" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1250" s="4" t="inlineStr"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1251" s="6" t="inlineStr">
+        <is>
+          <t>04:39:04</t>
+        </is>
+      </c>
+      <c r="C1251" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1251" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1251" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1251" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1251" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261007043904050655.pdf</t>
+        </is>
+      </c>
+      <c r="H1251" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1251" s="7" t="inlineStr"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1252" s="3" t="inlineStr">
+        <is>
+          <t>04:39:04</t>
+        </is>
+      </c>
+      <c r="C1252" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1252" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1252" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1252" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1252" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261007043904249583.jpeg</t>
+        </is>
+      </c>
+      <c r="H1252" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1252" s="4" t="inlineStr"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1253" s="6" t="inlineStr">
+        <is>
+          <t>04:39:04</t>
+        </is>
+      </c>
+      <c r="C1253" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1253" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1253" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1253" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1253" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261007043904736587.pages</t>
+        </is>
+      </c>
+      <c r="H1253" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1253" s="7" t="inlineStr"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1254" s="3" t="inlineStr">
+        <is>
+          <t>04:39:05</t>
+        </is>
+      </c>
+      <c r="C1254" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1254" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1254" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1254" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1254" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261007043905258759.pdf</t>
+        </is>
+      </c>
+      <c r="H1254" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1254" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1254"/>
+  <dimension ref="A1:I1277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54421,6 +54421,995 @@
       </c>
       <c r="I1254" s="4" t="inlineStr"/>
     </row>
+    <row r="1255">
+      <c r="A1255" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1255" s="6" t="inlineStr">
+        <is>
+          <t>04:49:30</t>
+        </is>
+      </c>
+      <c r="C1255" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1255" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1255" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1255" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1255" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261008044930387538.gif</t>
+        </is>
+      </c>
+      <c r="H1255" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1255" s="7" t="inlineStr"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1256" s="3" t="inlineStr">
+        <is>
+          <t>04:49:30</t>
+        </is>
+      </c>
+      <c r="C1256" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1256" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1256" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1256" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1256" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261008044930605173.xlsx</t>
+        </is>
+      </c>
+      <c r="H1256" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1256" s="4" t="inlineStr"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1257" s="6" t="inlineStr">
+        <is>
+          <t>04:49:30</t>
+        </is>
+      </c>
+      <c r="C1257" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1257" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1257" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1257" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1257" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261008044930810198.csv</t>
+        </is>
+      </c>
+      <c r="H1257" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1257" s="7" t="inlineStr"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1258" s="3" t="inlineStr">
+        <is>
+          <t>04:49:31</t>
+        </is>
+      </c>
+      <c r="C1258" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1258" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1258" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1258" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1258" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261008044931029191.pdf</t>
+        </is>
+      </c>
+      <c r="H1258" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1258" s="4" t="inlineStr"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1259" s="6" t="inlineStr">
+        <is>
+          <t>04:49:31</t>
+        </is>
+      </c>
+      <c r="C1259" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1259" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1259" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1259" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1259" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261008044931237900.docx</t>
+        </is>
+      </c>
+      <c r="H1259" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1259" s="7" t="inlineStr"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1260" s="3" t="inlineStr">
+        <is>
+          <t>04:49:31</t>
+        </is>
+      </c>
+      <c r="C1260" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1260" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1260" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1260" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1260" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261008044931458016.pptx</t>
+        </is>
+      </c>
+      <c r="H1260" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1260" s="4" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1261" s="6" t="inlineStr">
+        <is>
+          <t>04:49:31</t>
+        </is>
+      </c>
+      <c r="C1261" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1261" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1261" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1261" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1261" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261008044931660247.jpg</t>
+        </is>
+      </c>
+      <c r="H1261" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1261" s="7" t="inlineStr"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1262" s="3" t="inlineStr">
+        <is>
+          <t>04:49:31</t>
+        </is>
+      </c>
+      <c r="C1262" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1262" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1262" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1262" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1262" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261008044931880256.doc</t>
+        </is>
+      </c>
+      <c r="H1262" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1262" s="4" t="inlineStr"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1263" s="6" t="inlineStr">
+        <is>
+          <t>04:49:32</t>
+        </is>
+      </c>
+      <c r="C1263" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1263" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1263" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1263" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1263" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261008044932075363.txt</t>
+        </is>
+      </c>
+      <c r="H1263" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1263" s="7" t="inlineStr"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1264" s="3" t="inlineStr">
+        <is>
+          <t>04:49:32</t>
+        </is>
+      </c>
+      <c r="C1264" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1264" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1264" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1264" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1264" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261008044932294570.xls</t>
+        </is>
+      </c>
+      <c r="H1264" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1264" s="4" t="inlineStr"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1265" s="6" t="inlineStr">
+        <is>
+          <t>04:49:32</t>
+        </is>
+      </c>
+      <c r="C1265" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1265" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1265" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1265" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1265" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261008044932490066.png</t>
+        </is>
+      </c>
+      <c r="H1265" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1265" s="7" t="inlineStr"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1266" s="3" t="inlineStr">
+        <is>
+          <t>04:49:32</t>
+        </is>
+      </c>
+      <c r="C1266" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1266" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1266" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1266" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1266" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261008044932709031.dat</t>
+        </is>
+      </c>
+      <c r="H1266" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1266" s="4" t="inlineStr"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1267" s="6" t="inlineStr">
+        <is>
+          <t>04:49:34</t>
+        </is>
+      </c>
+      <c r="C1267" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1267" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1267" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1267" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1267" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261008044934096750.docx</t>
+        </is>
+      </c>
+      <c r="H1267" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1267" s="7" t="inlineStr"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1268" s="3" t="inlineStr">
+        <is>
+          <t>04:49:34</t>
+        </is>
+      </c>
+      <c r="C1268" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1268" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1268" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1268" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1268" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261008044934319523.pdf</t>
+        </is>
+      </c>
+      <c r="H1268" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1268" s="4" t="inlineStr"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1269" s="6" t="inlineStr">
+        <is>
+          <t>04:49:34</t>
+        </is>
+      </c>
+      <c r="C1269" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1269" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1269" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1269" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1269" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261008044934519857.jpeg</t>
+        </is>
+      </c>
+      <c r="H1269" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1269" s="7" t="inlineStr"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1270" s="3" t="inlineStr">
+        <is>
+          <t>04:49:34</t>
+        </is>
+      </c>
+      <c r="C1270" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1270" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1270" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1270" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1270" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261008044934750799.xlsx</t>
+        </is>
+      </c>
+      <c r="H1270" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1270" s="4" t="inlineStr"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1271" s="6" t="inlineStr">
+        <is>
+          <t>04:49:35</t>
+        </is>
+      </c>
+      <c r="C1271" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1271" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1271" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1271" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1271" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261008044935238454.txt</t>
+        </is>
+      </c>
+      <c r="H1271" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1271" s="7" t="inlineStr"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1272" s="3" t="inlineStr">
+        <is>
+          <t>04:49:35</t>
+        </is>
+      </c>
+      <c r="C1272" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1272" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1272" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1272" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1272" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261008044935460156.xlsx</t>
+        </is>
+      </c>
+      <c r="H1272" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1272" s="4" t="inlineStr"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1273" s="6" t="inlineStr">
+        <is>
+          <t>04:49:35</t>
+        </is>
+      </c>
+      <c r="C1273" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1273" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1273" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1273" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1273" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1273" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1273" s="7" t="inlineStr"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1274" s="3" t="inlineStr">
+        <is>
+          <t>04:49:36</t>
+        </is>
+      </c>
+      <c r="C1274" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1274" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1274" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1274" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1274" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261008044936117588.pdf</t>
+        </is>
+      </c>
+      <c r="H1274" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1274" s="4" t="inlineStr"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1275" s="6" t="inlineStr">
+        <is>
+          <t>04:49:36</t>
+        </is>
+      </c>
+      <c r="C1275" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1275" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1275" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1275" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1275" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261008044936325622.jpeg</t>
+        </is>
+      </c>
+      <c r="H1275" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1275" s="7" t="inlineStr"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1276" s="3" t="inlineStr">
+        <is>
+          <t>04:49:36</t>
+        </is>
+      </c>
+      <c r="C1276" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1276" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1276" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1276" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1276" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261008044936551031.pages</t>
+        </is>
+      </c>
+      <c r="H1276" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1276" s="4" t="inlineStr"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1277" s="6" t="inlineStr">
+        <is>
+          <t>04:49:37</t>
+        </is>
+      </c>
+      <c r="C1277" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1277" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1277" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1277" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1277" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261008044937089873.pdf</t>
+        </is>
+      </c>
+      <c r="H1277" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1277" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1277"/>
+  <dimension ref="A1:I1300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -55410,6 +55410,995 @@
       </c>
       <c r="I1277" s="7" t="inlineStr"/>
     </row>
+    <row r="1278">
+      <c r="A1278" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1278" s="3" t="inlineStr">
+        <is>
+          <t>04:52:27</t>
+        </is>
+      </c>
+      <c r="C1278" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1278" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1278" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1278" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1278" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261009045227123365.gif</t>
+        </is>
+      </c>
+      <c r="H1278" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1278" s="4" t="inlineStr"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1279" s="6" t="inlineStr">
+        <is>
+          <t>04:52:27</t>
+        </is>
+      </c>
+      <c r="C1279" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1279" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1279" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1279" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1279" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261009045227330991.xlsx</t>
+        </is>
+      </c>
+      <c r="H1279" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1279" s="7" t="inlineStr"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1280" s="3" t="inlineStr">
+        <is>
+          <t>04:52:27</t>
+        </is>
+      </c>
+      <c r="C1280" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1280" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1280" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1280" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1280" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261009045227529139.csv</t>
+        </is>
+      </c>
+      <c r="H1280" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1280" s="4" t="inlineStr"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1281" s="6" t="inlineStr">
+        <is>
+          <t>04:52:27</t>
+        </is>
+      </c>
+      <c r="C1281" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1281" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1281" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1281" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1281" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261009045227747146.pdf</t>
+        </is>
+      </c>
+      <c r="H1281" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1281" s="7" t="inlineStr"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1282" s="3" t="inlineStr">
+        <is>
+          <t>04:52:27</t>
+        </is>
+      </c>
+      <c r="C1282" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1282" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1282" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1282" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1282" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261009045227945697.docx</t>
+        </is>
+      </c>
+      <c r="H1282" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1282" s="4" t="inlineStr"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1283" s="6" t="inlineStr">
+        <is>
+          <t>04:52:28</t>
+        </is>
+      </c>
+      <c r="C1283" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1283" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1283" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1283" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1283" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261009045228168313.pptx</t>
+        </is>
+      </c>
+      <c r="H1283" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1283" s="7" t="inlineStr"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1284" s="3" t="inlineStr">
+        <is>
+          <t>04:52:28</t>
+        </is>
+      </c>
+      <c r="C1284" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1284" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1284" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1284" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1284" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261009045228366678.jpg</t>
+        </is>
+      </c>
+      <c r="H1284" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1284" s="4" t="inlineStr"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1285" s="6" t="inlineStr">
+        <is>
+          <t>04:52:28</t>
+        </is>
+      </c>
+      <c r="C1285" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1285" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1285" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1285" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1285" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261009045228591100.doc</t>
+        </is>
+      </c>
+      <c r="H1285" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1285" s="7" t="inlineStr"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1286" s="3" t="inlineStr">
+        <is>
+          <t>04:52:28</t>
+        </is>
+      </c>
+      <c r="C1286" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1286" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1286" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1286" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1286" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261009045228788960.txt</t>
+        </is>
+      </c>
+      <c r="H1286" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1286" s="4" t="inlineStr"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1287" s="6" t="inlineStr">
+        <is>
+          <t>04:52:29</t>
+        </is>
+      </c>
+      <c r="C1287" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1287" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1287" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1287" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1287" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261009045229011381.xls</t>
+        </is>
+      </c>
+      <c r="H1287" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1287" s="7" t="inlineStr"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1288" s="3" t="inlineStr">
+        <is>
+          <t>04:52:29</t>
+        </is>
+      </c>
+      <c r="C1288" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1288" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1288" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1288" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1288" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261009045229209214.png</t>
+        </is>
+      </c>
+      <c r="H1288" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1288" s="4" t="inlineStr"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1289" s="6" t="inlineStr">
+        <is>
+          <t>04:52:29</t>
+        </is>
+      </c>
+      <c r="C1289" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1289" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1289" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1289" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1289" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261009045229434656.dat</t>
+        </is>
+      </c>
+      <c r="H1289" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1289" s="7" t="inlineStr"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1290" s="3" t="inlineStr">
+        <is>
+          <t>04:52:31</t>
+        </is>
+      </c>
+      <c r="C1290" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1290" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1290" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1290" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1290" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261009045231508638.docx</t>
+        </is>
+      </c>
+      <c r="H1290" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1290" s="4" t="inlineStr"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1291" s="6" t="inlineStr">
+        <is>
+          <t>04:52:31</t>
+        </is>
+      </c>
+      <c r="C1291" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1291" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1291" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1291" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1291" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261009045231808283.pdf</t>
+        </is>
+      </c>
+      <c r="H1291" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1291" s="7" t="inlineStr"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1292" s="3" t="inlineStr">
+        <is>
+          <t>04:52:32</t>
+        </is>
+      </c>
+      <c r="C1292" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1292" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1292" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1292" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1292" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261009045232026045.jpeg</t>
+        </is>
+      </c>
+      <c r="H1292" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1292" s="4" t="inlineStr"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1293" s="6" t="inlineStr">
+        <is>
+          <t>04:52:32</t>
+        </is>
+      </c>
+      <c r="C1293" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1293" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1293" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1293" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1293" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261009045232224740.xlsx</t>
+        </is>
+      </c>
+      <c r="H1293" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1293" s="7" t="inlineStr"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1294" s="3" t="inlineStr">
+        <is>
+          <t>04:52:32</t>
+        </is>
+      </c>
+      <c r="C1294" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1294" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1294" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1294" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1294" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261009045232771475.txt</t>
+        </is>
+      </c>
+      <c r="H1294" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1294" s="4" t="inlineStr"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1295" s="6" t="inlineStr">
+        <is>
+          <t>04:52:32</t>
+        </is>
+      </c>
+      <c r="C1295" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1295" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1295" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1295" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1295" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261009045232972051.xlsx</t>
+        </is>
+      </c>
+      <c r="H1295" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1295" s="7" t="inlineStr"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1296" s="3" t="inlineStr">
+        <is>
+          <t>04:52:33</t>
+        </is>
+      </c>
+      <c r="C1296" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1296" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1296" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1296" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1296" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1296" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1296" s="4" t="inlineStr"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1297" s="6" t="inlineStr">
+        <is>
+          <t>04:52:33</t>
+        </is>
+      </c>
+      <c r="C1297" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1297" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1297" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1297" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1297" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261009045233586964.pdf</t>
+        </is>
+      </c>
+      <c r="H1297" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1297" s="7" t="inlineStr"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1298" s="3" t="inlineStr">
+        <is>
+          <t>04:52:33</t>
+        </is>
+      </c>
+      <c r="C1298" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1298" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1298" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1298" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1298" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261009045233812393.jpeg</t>
+        </is>
+      </c>
+      <c r="H1298" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1298" s="4" t="inlineStr"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1299" s="6" t="inlineStr">
+        <is>
+          <t>04:52:34</t>
+        </is>
+      </c>
+      <c r="C1299" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1299" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1299" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1299" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1299" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261009045234014006.pages</t>
+        </is>
+      </c>
+      <c r="H1299" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1299" s="7" t="inlineStr"/>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1300" s="3" t="inlineStr">
+        <is>
+          <t>04:52:34</t>
+        </is>
+      </c>
+      <c r="C1300" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1300" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1300" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1300" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1300" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261009045234645766.pdf</t>
+        </is>
+      </c>
+      <c r="H1300" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1300" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1300"/>
+  <dimension ref="A1:I1323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56399,6 +56399,995 @@
       </c>
       <c r="I1300" s="4" t="inlineStr"/>
     </row>
+    <row r="1301">
+      <c r="A1301" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1301" s="6" t="inlineStr">
+        <is>
+          <t>04:38:14</t>
+        </is>
+      </c>
+      <c r="C1301" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1301" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1301" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1301" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1301" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261010043814934864.gif</t>
+        </is>
+      </c>
+      <c r="H1301" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1301" s="7" t="inlineStr"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1302" s="3" t="inlineStr">
+        <is>
+          <t>04:38:15</t>
+        </is>
+      </c>
+      <c r="C1302" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1302" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1302" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1302" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1302" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261010043815149193.xlsx</t>
+        </is>
+      </c>
+      <c r="H1302" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1302" s="4" t="inlineStr"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1303" s="6" t="inlineStr">
+        <is>
+          <t>04:38:15</t>
+        </is>
+      </c>
+      <c r="C1303" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1303" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1303" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1303" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1303" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261010043815341707.csv</t>
+        </is>
+      </c>
+      <c r="H1303" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1303" s="7" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1304" s="3" t="inlineStr">
+        <is>
+          <t>04:38:15</t>
+        </is>
+      </c>
+      <c r="C1304" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1304" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1304" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1304" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1304" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261010043815545116.pdf</t>
+        </is>
+      </c>
+      <c r="H1304" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1304" s="4" t="inlineStr"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1305" s="6" t="inlineStr">
+        <is>
+          <t>04:38:15</t>
+        </is>
+      </c>
+      <c r="C1305" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1305" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1305" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1305" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1305" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261010043815734815.docx</t>
+        </is>
+      </c>
+      <c r="H1305" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1305" s="7" t="inlineStr"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1306" s="3" t="inlineStr">
+        <is>
+          <t>04:38:15</t>
+        </is>
+      </c>
+      <c r="C1306" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1306" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1306" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1306" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1306" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261010043815941895.pptx</t>
+        </is>
+      </c>
+      <c r="H1306" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1306" s="4" t="inlineStr"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1307" s="6" t="inlineStr">
+        <is>
+          <t>04:38:16</t>
+        </is>
+      </c>
+      <c r="C1307" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1307" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1307" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1307" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1307" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261010043816131697.jpg</t>
+        </is>
+      </c>
+      <c r="H1307" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1307" s="7" t="inlineStr"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1308" s="3" t="inlineStr">
+        <is>
+          <t>04:38:16</t>
+        </is>
+      </c>
+      <c r="C1308" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1308" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1308" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1308" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1308" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261010043816343222.doc</t>
+        </is>
+      </c>
+      <c r="H1308" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1308" s="4" t="inlineStr"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1309" s="6" t="inlineStr">
+        <is>
+          <t>04:38:16</t>
+        </is>
+      </c>
+      <c r="C1309" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1309" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1309" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1309" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1309" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261010043816529051.txt</t>
+        </is>
+      </c>
+      <c r="H1309" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1309" s="7" t="inlineStr"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1310" s="3" t="inlineStr">
+        <is>
+          <t>04:38:16</t>
+        </is>
+      </c>
+      <c r="C1310" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1310" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1310" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1310" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1310" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261010043816737844.xls</t>
+        </is>
+      </c>
+      <c r="H1310" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1310" s="4" t="inlineStr"/>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1311" s="6" t="inlineStr">
+        <is>
+          <t>04:38:16</t>
+        </is>
+      </c>
+      <c r="C1311" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1311" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1311" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1311" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1311" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261010043816944674.png</t>
+        </is>
+      </c>
+      <c r="H1311" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1311" s="7" t="inlineStr"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1312" s="3" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="C1312" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1312" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1312" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1312" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1312" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261010043817133330.dat</t>
+        </is>
+      </c>
+      <c r="H1312" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1312" s="4" t="inlineStr"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1313" s="6" t="inlineStr">
+        <is>
+          <t>04:38:19</t>
+        </is>
+      </c>
+      <c r="C1313" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1313" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1313" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1313" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1313" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261010043819857805.docx</t>
+        </is>
+      </c>
+      <c r="H1313" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1313" s="7" t="inlineStr"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1314" s="3" t="inlineStr">
+        <is>
+          <t>04:38:20</t>
+        </is>
+      </c>
+      <c r="C1314" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1314" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1314" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1314" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1314" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261010043820046624.pdf</t>
+        </is>
+      </c>
+      <c r="H1314" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1314" s="4" t="inlineStr"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1315" s="6" t="inlineStr">
+        <is>
+          <t>04:38:20</t>
+        </is>
+      </c>
+      <c r="C1315" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1315" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1315" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1315" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1315" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261010043820258406.jpeg</t>
+        </is>
+      </c>
+      <c r="H1315" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1315" s="7" t="inlineStr"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1316" s="3" t="inlineStr">
+        <is>
+          <t>04:38:20</t>
+        </is>
+      </c>
+      <c r="C1316" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1316" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1316" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1316" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1316" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261010043820446049.xlsx</t>
+        </is>
+      </c>
+      <c r="H1316" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1316" s="4" t="inlineStr"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1317" s="6" t="inlineStr">
+        <is>
+          <t>04:38:20</t>
+        </is>
+      </c>
+      <c r="C1317" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1317" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1317" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1317" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1317" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261010043820964212.txt</t>
+        </is>
+      </c>
+      <c r="H1317" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1317" s="7" t="inlineStr"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1318" s="3" t="inlineStr">
+        <is>
+          <t>04:38:21</t>
+        </is>
+      </c>
+      <c r="C1318" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1318" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1318" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1318" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1318" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261010043821151393.xlsx</t>
+        </is>
+      </c>
+      <c r="H1318" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1318" s="4" t="inlineStr"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1319" s="6" t="inlineStr">
+        <is>
+          <t>04:38:21</t>
+        </is>
+      </c>
+      <c r="C1319" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1319" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1319" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1319" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1319" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1319" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1319" s="7" t="inlineStr"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1320" s="3" t="inlineStr">
+        <is>
+          <t>04:38:21</t>
+        </is>
+      </c>
+      <c r="C1320" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1320" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1320" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1320" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1320" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261010043821935842.pdf</t>
+        </is>
+      </c>
+      <c r="H1320" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1320" s="4" t="inlineStr"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1321" s="6" t="inlineStr">
+        <is>
+          <t>04:38:22</t>
+        </is>
+      </c>
+      <c r="C1321" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1321" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1321" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1321" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1321" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261010043822155468.jpeg</t>
+        </is>
+      </c>
+      <c r="H1321" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1321" s="7" t="inlineStr"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1322" s="3" t="inlineStr">
+        <is>
+          <t>04:38:22</t>
+        </is>
+      </c>
+      <c r="C1322" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1322" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1322" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1322" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1322" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261010043822361867.pages</t>
+        </is>
+      </c>
+      <c r="H1322" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1322" s="4" t="inlineStr"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B1323" s="6" t="inlineStr">
+        <is>
+          <t>04:38:22</t>
+        </is>
+      </c>
+      <c r="C1323" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1323" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1323" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1323" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1323" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261010043822993614.pdf</t>
+        </is>
+      </c>
+      <c r="H1323" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1323" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1323"/>
+  <dimension ref="A1:I1346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -57388,6 +57388,995 @@
       </c>
       <c r="I1323" s="7" t="inlineStr"/>
     </row>
+    <row r="1324">
+      <c r="A1324" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1324" s="3" t="inlineStr">
+        <is>
+          <t>04:23:08</t>
+        </is>
+      </c>
+      <c r="C1324" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1324" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1324" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1324" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1324" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261011042308714309.gif</t>
+        </is>
+      </c>
+      <c r="H1324" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1324" s="4" t="inlineStr"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1325" s="6" t="inlineStr">
+        <is>
+          <t>04:23:09</t>
+        </is>
+      </c>
+      <c r="C1325" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1325" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1325" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1325" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1325" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261011042309015434.xlsx</t>
+        </is>
+      </c>
+      <c r="H1325" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1325" s="7" t="inlineStr"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1326" s="3" t="inlineStr">
+        <is>
+          <t>04:23:09</t>
+        </is>
+      </c>
+      <c r="C1326" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1326" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1326" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1326" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1326" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261011042309305709.csv</t>
+        </is>
+      </c>
+      <c r="H1326" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1326" s="4" t="inlineStr"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1327" s="6" t="inlineStr">
+        <is>
+          <t>04:23:09</t>
+        </is>
+      </c>
+      <c r="C1327" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1327" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1327" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1327" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1327" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261011042309622811.pdf</t>
+        </is>
+      </c>
+      <c r="H1327" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1327" s="7" t="inlineStr"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1328" s="3" t="inlineStr">
+        <is>
+          <t>04:23:09</t>
+        </is>
+      </c>
+      <c r="C1328" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1328" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1328" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1328" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1328" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261011042309916383.docx</t>
+        </is>
+      </c>
+      <c r="H1328" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1328" s="4" t="inlineStr"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1329" s="6" t="inlineStr">
+        <is>
+          <t>04:23:10</t>
+        </is>
+      </c>
+      <c r="C1329" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1329" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1329" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1329" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1329" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261011042310232383.pptx</t>
+        </is>
+      </c>
+      <c r="H1329" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1329" s="7" t="inlineStr"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1330" s="3" t="inlineStr">
+        <is>
+          <t>04:23:10</t>
+        </is>
+      </c>
+      <c r="C1330" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1330" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1330" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1330" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1330" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261011042310521189.jpg</t>
+        </is>
+      </c>
+      <c r="H1330" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1330" s="4" t="inlineStr"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1331" s="6" t="inlineStr">
+        <is>
+          <t>04:23:10</t>
+        </is>
+      </c>
+      <c r="C1331" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1331" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1331" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1331" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1331" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261011042310840163.doc</t>
+        </is>
+      </c>
+      <c r="H1331" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1331" s="7" t="inlineStr"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1332" s="3" t="inlineStr">
+        <is>
+          <t>04:23:11</t>
+        </is>
+      </c>
+      <c r="C1332" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1332" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1332" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1332" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1332" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261011042311164397.txt</t>
+        </is>
+      </c>
+      <c r="H1332" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1332" s="4" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1333" s="6" t="inlineStr">
+        <is>
+          <t>04:23:11</t>
+        </is>
+      </c>
+      <c r="C1333" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1333" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1333" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1333" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1333" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261011042311460123.xls</t>
+        </is>
+      </c>
+      <c r="H1333" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1333" s="7" t="inlineStr"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1334" s="3" t="inlineStr">
+        <is>
+          <t>04:23:11</t>
+        </is>
+      </c>
+      <c r="C1334" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1334" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1334" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1334" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1334" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261011042311780842.png</t>
+        </is>
+      </c>
+      <c r="H1334" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1334" s="4" t="inlineStr"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1335" s="6" t="inlineStr">
+        <is>
+          <t>04:23:12</t>
+        </is>
+      </c>
+      <c r="C1335" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1335" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1335" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1335" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1335" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261011042312073516.dat</t>
+        </is>
+      </c>
+      <c r="H1335" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1335" s="7" t="inlineStr"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1336" s="3" t="inlineStr">
+        <is>
+          <t>04:23:13</t>
+        </is>
+      </c>
+      <c r="C1336" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1336" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1336" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1336" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1336" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261011042313354861.docx</t>
+        </is>
+      </c>
+      <c r="H1336" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1336" s="4" t="inlineStr"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1337" s="6" t="inlineStr">
+        <is>
+          <t>04:23:13</t>
+        </is>
+      </c>
+      <c r="C1337" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1337" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1337" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1337" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1337" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261011042313651470.pdf</t>
+        </is>
+      </c>
+      <c r="H1337" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1337" s="7" t="inlineStr"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1338" s="3" t="inlineStr">
+        <is>
+          <t>04:23:13</t>
+        </is>
+      </c>
+      <c r="C1338" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1338" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1338" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1338" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1338" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261011042313981995.jpeg</t>
+        </is>
+      </c>
+      <c r="H1338" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1338" s="4" t="inlineStr"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1339" s="6" t="inlineStr">
+        <is>
+          <t>04:23:14</t>
+        </is>
+      </c>
+      <c r="C1339" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1339" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1339" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1339" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1339" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261011042314277042.xlsx</t>
+        </is>
+      </c>
+      <c r="H1339" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1339" s="7" t="inlineStr"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1340" s="3" t="inlineStr">
+        <is>
+          <t>04:23:14</t>
+        </is>
+      </c>
+      <c r="C1340" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1340" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1340" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1340" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1340" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261011042314909523.txt</t>
+        </is>
+      </c>
+      <c r="H1340" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1340" s="4" t="inlineStr"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1341" s="6" t="inlineStr">
+        <is>
+          <t>04:23:15</t>
+        </is>
+      </c>
+      <c r="C1341" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1341" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1341" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1341" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1341" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261011042315205123.xlsx</t>
+        </is>
+      </c>
+      <c r="H1341" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1341" s="7" t="inlineStr"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1342" s="3" t="inlineStr">
+        <is>
+          <t>04:23:15</t>
+        </is>
+      </c>
+      <c r="C1342" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1342" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1342" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1342" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1342" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1342" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1342" s="4" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1343" s="6" t="inlineStr">
+        <is>
+          <t>04:23:16</t>
+        </is>
+      </c>
+      <c r="C1343" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1343" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1343" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1343" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1343" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261011042316057761.pdf</t>
+        </is>
+      </c>
+      <c r="H1343" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1343" s="7" t="inlineStr"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1344" s="3" t="inlineStr">
+        <is>
+          <t>04:23:16</t>
+        </is>
+      </c>
+      <c r="C1344" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1344" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1344" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1344" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1344" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261011042316353322.jpeg</t>
+        </is>
+      </c>
+      <c r="H1344" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1344" s="4" t="inlineStr"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1345" s="6" t="inlineStr">
+        <is>
+          <t>04:23:16</t>
+        </is>
+      </c>
+      <c r="C1345" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1345" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1345" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1345" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1345" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261011042316694266.pages</t>
+        </is>
+      </c>
+      <c r="H1345" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1345" s="7" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B1346" s="3" t="inlineStr">
+        <is>
+          <t>04:23:17</t>
+        </is>
+      </c>
+      <c r="C1346" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1346" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1346" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1346" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1346" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261011042317361893.pdf</t>
+        </is>
+      </c>
+      <c r="H1346" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1346" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1346"/>
+  <dimension ref="A1:I1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -58377,6 +58377,995 @@
       </c>
       <c r="I1346" s="4" t="inlineStr"/>
     </row>
+    <row r="1347">
+      <c r="A1347" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1347" s="6" t="inlineStr">
+        <is>
+          <t>04:39:07</t>
+        </is>
+      </c>
+      <c r="C1347" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1347" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1347" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1347" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1347" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261012043907030246.gif</t>
+        </is>
+      </c>
+      <c r="H1347" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1347" s="7" t="inlineStr"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1348" s="3" t="inlineStr">
+        <is>
+          <t>04:39:07</t>
+        </is>
+      </c>
+      <c r="C1348" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1348" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1348" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1348" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1348" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261012043907363035.xlsx</t>
+        </is>
+      </c>
+      <c r="H1348" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1348" s="4" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1349" s="6" t="inlineStr">
+        <is>
+          <t>04:39:07</t>
+        </is>
+      </c>
+      <c r="C1349" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1349" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1349" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1349" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1349" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261012043907657051.csv</t>
+        </is>
+      </c>
+      <c r="H1349" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1349" s="7" t="inlineStr"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1350" s="3" t="inlineStr">
+        <is>
+          <t>04:39:07</t>
+        </is>
+      </c>
+      <c r="C1350" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1350" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1350" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1350" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1350" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261012043907990620.pdf</t>
+        </is>
+      </c>
+      <c r="H1350" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1350" s="4" t="inlineStr"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1351" s="6" t="inlineStr">
+        <is>
+          <t>04:39:08</t>
+        </is>
+      </c>
+      <c r="C1351" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1351" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1351" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1351" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1351" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261012043908281680.docx</t>
+        </is>
+      </c>
+      <c r="H1351" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1351" s="7" t="inlineStr"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1352" s="3" t="inlineStr">
+        <is>
+          <t>04:39:08</t>
+        </is>
+      </c>
+      <c r="C1352" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1352" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1352" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1352" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1352" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261012043908589491.pptx</t>
+        </is>
+      </c>
+      <c r="H1352" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1352" s="4" t="inlineStr"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1353" s="6" t="inlineStr">
+        <is>
+          <t>04:39:08</t>
+        </is>
+      </c>
+      <c r="C1353" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1353" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1353" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1353" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1353" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261012043908903143.jpg</t>
+        </is>
+      </c>
+      <c r="H1353" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1353" s="7" t="inlineStr"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1354" s="3" t="inlineStr">
+        <is>
+          <t>04:39:09</t>
+        </is>
+      </c>
+      <c r="C1354" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1354" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1354" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1354" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1354" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261012043909197538.doc</t>
+        </is>
+      </c>
+      <c r="H1354" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1354" s="4" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1355" s="6" t="inlineStr">
+        <is>
+          <t>04:39:09</t>
+        </is>
+      </c>
+      <c r="C1355" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1355" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1355" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1355" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1355" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261012043909516746.txt</t>
+        </is>
+      </c>
+      <c r="H1355" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1355" s="7" t="inlineStr"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1356" s="3" t="inlineStr">
+        <is>
+          <t>04:39:09</t>
+        </is>
+      </c>
+      <c r="C1356" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1356" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1356" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1356" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1356" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261012043909810132.xls</t>
+        </is>
+      </c>
+      <c r="H1356" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1356" s="4" t="inlineStr"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1357" s="6" t="inlineStr">
+        <is>
+          <t>04:39:10</t>
+        </is>
+      </c>
+      <c r="C1357" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1357" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1357" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1357" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1357" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261012043910124900.png</t>
+        </is>
+      </c>
+      <c r="H1357" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1357" s="7" t="inlineStr"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1358" s="3" t="inlineStr">
+        <is>
+          <t>04:39:10</t>
+        </is>
+      </c>
+      <c r="C1358" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1358" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1358" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1358" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1358" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261012043910418684.dat</t>
+        </is>
+      </c>
+      <c r="H1358" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1358" s="4" t="inlineStr"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1359" s="6" t="inlineStr">
+        <is>
+          <t>04:39:12</t>
+        </is>
+      </c>
+      <c r="C1359" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1359" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1359" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1359" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1359" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261012043912006906.docx</t>
+        </is>
+      </c>
+      <c r="H1359" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1359" s="7" t="inlineStr"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1360" s="3" t="inlineStr">
+        <is>
+          <t>04:39:12</t>
+        </is>
+      </c>
+      <c r="C1360" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1360" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1360" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1360" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1360" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261012043912300943.pdf</t>
+        </is>
+      </c>
+      <c r="H1360" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1360" s="4" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1361" s="6" t="inlineStr">
+        <is>
+          <t>04:39:12</t>
+        </is>
+      </c>
+      <c r="C1361" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1361" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1361" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1361" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1361" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261012043912616231.jpeg</t>
+        </is>
+      </c>
+      <c r="H1361" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1361" s="7" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1362" s="3" t="inlineStr">
+        <is>
+          <t>04:39:12</t>
+        </is>
+      </c>
+      <c r="C1362" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1362" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1362" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1362" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1362" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261012043912926089.xlsx</t>
+        </is>
+      </c>
+      <c r="H1362" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1362" s="4" t="inlineStr"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1363" s="6" t="inlineStr">
+        <is>
+          <t>04:39:13</t>
+        </is>
+      </c>
+      <c r="C1363" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1363" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1363" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1363" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1363" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261012043913461780.txt</t>
+        </is>
+      </c>
+      <c r="H1363" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1363" s="7" t="inlineStr"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1364" s="3" t="inlineStr">
+        <is>
+          <t>04:39:13</t>
+        </is>
+      </c>
+      <c r="C1364" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1364" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1364" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1364" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1364" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261012043913783113.xlsx</t>
+        </is>
+      </c>
+      <c r="H1364" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1364" s="4" t="inlineStr"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1365" s="6" t="inlineStr">
+        <is>
+          <t>04:39:14</t>
+        </is>
+      </c>
+      <c r="C1365" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1365" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1365" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1365" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1365" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1365" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1365" s="7" t="inlineStr"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1366" s="3" t="inlineStr">
+        <is>
+          <t>04:39:14</t>
+        </is>
+      </c>
+      <c r="C1366" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1366" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1366" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1366" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1366" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261012043914689294.pdf</t>
+        </is>
+      </c>
+      <c r="H1366" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1366" s="4" t="inlineStr"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1367" s="6" t="inlineStr">
+        <is>
+          <t>04:39:14</t>
+        </is>
+      </c>
+      <c r="C1367" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1367" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1367" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1367" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1367" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261012043914984037.jpeg</t>
+        </is>
+      </c>
+      <c r="H1367" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1367" s="7" t="inlineStr"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1368" s="3" t="inlineStr">
+        <is>
+          <t>04:39:15</t>
+        </is>
+      </c>
+      <c r="C1368" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1368" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1368" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1368" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1368" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261012043915302053.pages</t>
+        </is>
+      </c>
+      <c r="H1368" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1368" s="4" t="inlineStr"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1369" s="6" t="inlineStr">
+        <is>
+          <t>04:39:15</t>
+        </is>
+      </c>
+      <c r="C1369" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1369" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1369" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1369" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1369" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261012043915944932.pdf</t>
+        </is>
+      </c>
+      <c r="H1369" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1369" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1369"/>
+  <dimension ref="A1:I1392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -59366,6 +59366,995 @@
       </c>
       <c r="I1369" s="7" t="inlineStr"/>
     </row>
+    <row r="1370">
+      <c r="A1370" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1370" s="3" t="inlineStr">
+        <is>
+          <t>05:44:32</t>
+        </is>
+      </c>
+      <c r="C1370" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1370" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1370" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1370" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1370" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261013054432524950.gif</t>
+        </is>
+      </c>
+      <c r="H1370" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1370" s="4" t="inlineStr"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1371" s="6" t="inlineStr">
+        <is>
+          <t>05:44:32</t>
+        </is>
+      </c>
+      <c r="C1371" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1371" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1371" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1371" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1371" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261013054432843832.xlsx</t>
+        </is>
+      </c>
+      <c r="H1371" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1371" s="7" t="inlineStr"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1372" s="3" t="inlineStr">
+        <is>
+          <t>05:44:33</t>
+        </is>
+      </c>
+      <c r="C1372" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1372" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1372" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1372" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1372" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261013054433184284.csv</t>
+        </is>
+      </c>
+      <c r="H1372" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1372" s="4" t="inlineStr"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1373" s="6" t="inlineStr">
+        <is>
+          <t>05:44:33</t>
+        </is>
+      </c>
+      <c r="C1373" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1373" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1373" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1373" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1373" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261013054433509072.pdf</t>
+        </is>
+      </c>
+      <c r="H1373" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1373" s="7" t="inlineStr"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1374" s="3" t="inlineStr">
+        <is>
+          <t>05:44:33</t>
+        </is>
+      </c>
+      <c r="C1374" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1374" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1374" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1374" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1374" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261013054433802406.docx</t>
+        </is>
+      </c>
+      <c r="H1374" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1374" s="4" t="inlineStr"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1375" s="6" t="inlineStr">
+        <is>
+          <t>05:44:34</t>
+        </is>
+      </c>
+      <c r="C1375" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1375" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1375" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1375" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1375" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261013054434118536.pptx</t>
+        </is>
+      </c>
+      <c r="H1375" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1375" s="7" t="inlineStr"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1376" s="3" t="inlineStr">
+        <is>
+          <t>05:44:34</t>
+        </is>
+      </c>
+      <c r="C1376" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1376" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1376" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1376" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1376" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261013054434428291.jpg</t>
+        </is>
+      </c>
+      <c r="H1376" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1376" s="4" t="inlineStr"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1377" s="6" t="inlineStr">
+        <is>
+          <t>05:44:34</t>
+        </is>
+      </c>
+      <c r="C1377" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1377" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1377" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1377" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1377" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261013054434723873.doc</t>
+        </is>
+      </c>
+      <c r="H1377" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1377" s="7" t="inlineStr"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1378" s="3" t="inlineStr">
+        <is>
+          <t>05:44:35</t>
+        </is>
+      </c>
+      <c r="C1378" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1378" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1378" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1378" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1378" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261013054435047398.txt</t>
+        </is>
+      </c>
+      <c r="H1378" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1378" s="4" t="inlineStr"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1379" s="6" t="inlineStr">
+        <is>
+          <t>05:44:35</t>
+        </is>
+      </c>
+      <c r="C1379" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1379" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1379" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1379" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1379" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261013054435343435.xls</t>
+        </is>
+      </c>
+      <c r="H1379" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1379" s="7" t="inlineStr"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1380" s="3" t="inlineStr">
+        <is>
+          <t>05:44:35</t>
+        </is>
+      </c>
+      <c r="C1380" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1380" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1380" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1380" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1380" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261013054435660612.png</t>
+        </is>
+      </c>
+      <c r="H1380" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1380" s="4" t="inlineStr"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1381" s="6" t="inlineStr">
+        <is>
+          <t>05:44:35</t>
+        </is>
+      </c>
+      <c r="C1381" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1381" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1381" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1381" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1381" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261013054435961845.dat</t>
+        </is>
+      </c>
+      <c r="H1381" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1381" s="7" t="inlineStr"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1382" s="3" t="inlineStr">
+        <is>
+          <t>05:44:38</t>
+        </is>
+      </c>
+      <c r="C1382" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1382" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1382" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1382" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1382" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261013054438100593.docx</t>
+        </is>
+      </c>
+      <c r="H1382" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1382" s="4" t="inlineStr"/>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1383" s="6" t="inlineStr">
+        <is>
+          <t>05:44:38</t>
+        </is>
+      </c>
+      <c r="C1383" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1383" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1383" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1383" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1383" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261013054438414261.pdf</t>
+        </is>
+      </c>
+      <c r="H1383" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1383" s="7" t="inlineStr"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1384" s="3" t="inlineStr">
+        <is>
+          <t>05:44:38</t>
+        </is>
+      </c>
+      <c r="C1384" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1384" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1384" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1384" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1384" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261013054438718922.jpeg</t>
+        </is>
+      </c>
+      <c r="H1384" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1384" s="4" t="inlineStr"/>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1385" s="6" t="inlineStr">
+        <is>
+          <t>05:44:39</t>
+        </is>
+      </c>
+      <c r="C1385" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1385" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1385" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1385" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1385" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261013054439052076.xlsx</t>
+        </is>
+      </c>
+      <c r="H1385" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1385" s="7" t="inlineStr"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1386" s="3" t="inlineStr">
+        <is>
+          <t>05:44:39</t>
+        </is>
+      </c>
+      <c r="C1386" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1386" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1386" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1386" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1386" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261013054439699614.txt</t>
+        </is>
+      </c>
+      <c r="H1386" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1386" s="4" t="inlineStr"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1387" s="6" t="inlineStr">
+        <is>
+          <t>05:44:40</t>
+        </is>
+      </c>
+      <c r="C1387" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1387" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1387" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1387" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1387" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261013054440034490.xlsx</t>
+        </is>
+      </c>
+      <c r="H1387" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1387" s="7" t="inlineStr"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1388" s="3" t="inlineStr">
+        <is>
+          <t>05:44:40</t>
+        </is>
+      </c>
+      <c r="C1388" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1388" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1388" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1388" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1388" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1388" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1388" s="4" t="inlineStr"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1389" s="6" t="inlineStr">
+        <is>
+          <t>05:44:41</t>
+        </is>
+      </c>
+      <c r="C1389" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1389" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1389" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1389" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1389" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261013054441235222.pdf</t>
+        </is>
+      </c>
+      <c r="H1389" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1389" s="7" t="inlineStr"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1390" s="3" t="inlineStr">
+        <is>
+          <t>05:44:41</t>
+        </is>
+      </c>
+      <c r="C1390" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1390" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1390" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1390" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1390" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261013054441652158.jpeg</t>
+        </is>
+      </c>
+      <c r="H1390" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1390" s="4" t="inlineStr"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1391" s="6" t="inlineStr">
+        <is>
+          <t>05:44:41</t>
+        </is>
+      </c>
+      <c r="C1391" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1391" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1391" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1391" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1391" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261013054441978771.pages</t>
+        </is>
+      </c>
+      <c r="H1391" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1391" s="7" t="inlineStr"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1392" s="3" t="inlineStr">
+        <is>
+          <t>05:44:43</t>
+        </is>
+      </c>
+      <c r="C1392" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1392" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1392" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1392" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1392" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261013054443094994.pdf</t>
+        </is>
+      </c>
+      <c r="H1392" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1392" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1392"/>
+  <dimension ref="A1:I1415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -60355,6 +60355,995 @@
       </c>
       <c r="I1392" s="4" t="inlineStr"/>
     </row>
+    <row r="1393">
+      <c r="A1393" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1393" s="6" t="inlineStr">
+        <is>
+          <t>03:47:59</t>
+        </is>
+      </c>
+      <c r="C1393" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1393" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1393" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1393" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1393" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261014034759058972.gif</t>
+        </is>
+      </c>
+      <c r="H1393" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1393" s="7" t="inlineStr"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1394" s="3" t="inlineStr">
+        <is>
+          <t>03:47:59</t>
+        </is>
+      </c>
+      <c r="C1394" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1394" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1394" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1394" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1394" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261014034759388181.xlsx</t>
+        </is>
+      </c>
+      <c r="H1394" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1394" s="4" t="inlineStr"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1395" s="6" t="inlineStr">
+        <is>
+          <t>03:47:59</t>
+        </is>
+      </c>
+      <c r="C1395" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1395" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1395" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1395" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1395" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261014034759695386.csv</t>
+        </is>
+      </c>
+      <c r="H1395" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1395" s="7" t="inlineStr"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1396" s="3" t="inlineStr">
+        <is>
+          <t>03:48:00</t>
+        </is>
+      </c>
+      <c r="C1396" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1396" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1396" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1396" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1396" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261014034800033136.pdf</t>
+        </is>
+      </c>
+      <c r="H1396" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1396" s="4" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1397" s="6" t="inlineStr">
+        <is>
+          <t>03:48:00</t>
+        </is>
+      </c>
+      <c r="C1397" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1397" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1397" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1397" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1397" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261014034800344999.docx</t>
+        </is>
+      </c>
+      <c r="H1397" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1397" s="7" t="inlineStr"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1398" s="3" t="inlineStr">
+        <is>
+          <t>03:48:00</t>
+        </is>
+      </c>
+      <c r="C1398" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1398" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1398" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1398" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1398" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261014034800681955.pptx</t>
+        </is>
+      </c>
+      <c r="H1398" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1398" s="4" t="inlineStr"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1399" s="6" t="inlineStr">
+        <is>
+          <t>03:48:01</t>
+        </is>
+      </c>
+      <c r="C1399" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1399" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1399" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1399" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1399" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261014034801014768.jpg</t>
+        </is>
+      </c>
+      <c r="H1399" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1399" s="7" t="inlineStr"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1400" s="3" t="inlineStr">
+        <is>
+          <t>03:48:01</t>
+        </is>
+      </c>
+      <c r="C1400" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1400" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1400" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1400" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1400" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261014034801329630.doc</t>
+        </is>
+      </c>
+      <c r="H1400" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1400" s="4" t="inlineStr"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1401" s="6" t="inlineStr">
+        <is>
+          <t>03:48:01</t>
+        </is>
+      </c>
+      <c r="C1401" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1401" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1401" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1401" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1401" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261014034801677419.txt</t>
+        </is>
+      </c>
+      <c r="H1401" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1401" s="7" t="inlineStr"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1402" s="3" t="inlineStr">
+        <is>
+          <t>03:48:01</t>
+        </is>
+      </c>
+      <c r="C1402" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1402" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1402" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1402" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1402" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261014034801988520.xls</t>
+        </is>
+      </c>
+      <c r="H1402" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1402" s="4" t="inlineStr"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1403" s="6" t="inlineStr">
+        <is>
+          <t>03:48:02</t>
+        </is>
+      </c>
+      <c r="C1403" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1403" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1403" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1403" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1403" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261014034802339992.png</t>
+        </is>
+      </c>
+      <c r="H1403" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1403" s="7" t="inlineStr"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1404" s="3" t="inlineStr">
+        <is>
+          <t>03:48:02</t>
+        </is>
+      </c>
+      <c r="C1404" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1404" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1404" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1404" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1404" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261014034802656578.dat</t>
+        </is>
+      </c>
+      <c r="H1404" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1404" s="4" t="inlineStr"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1405" s="6" t="inlineStr">
+        <is>
+          <t>03:48:04</t>
+        </is>
+      </c>
+      <c r="C1405" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1405" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1405" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1405" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1405" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261014034804781423.docx</t>
+        </is>
+      </c>
+      <c r="H1405" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1405" s="7" t="inlineStr"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1406" s="3" t="inlineStr">
+        <is>
+          <t>03:48:05</t>
+        </is>
+      </c>
+      <c r="C1406" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1406" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1406" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1406" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1406" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261014034805119344.pdf</t>
+        </is>
+      </c>
+      <c r="H1406" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1406" s="4" t="inlineStr"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1407" s="6" t="inlineStr">
+        <is>
+          <t>03:48:05</t>
+        </is>
+      </c>
+      <c r="C1407" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1407" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1407" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1407" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1407" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261014034805433451.jpeg</t>
+        </is>
+      </c>
+      <c r="H1407" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1407" s="7" t="inlineStr"/>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1408" s="3" t="inlineStr">
+        <is>
+          <t>03:48:05</t>
+        </is>
+      </c>
+      <c r="C1408" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1408" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1408" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1408" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1408" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261014034805783409.xlsx</t>
+        </is>
+      </c>
+      <c r="H1408" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1408" s="4" t="inlineStr"/>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1409" s="6" t="inlineStr">
+        <is>
+          <t>03:48:06</t>
+        </is>
+      </c>
+      <c r="C1409" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1409" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1409" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1409" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1409" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261014034806409441.txt</t>
+        </is>
+      </c>
+      <c r="H1409" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1409" s="7" t="inlineStr"/>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1410" s="3" t="inlineStr">
+        <is>
+          <t>03:48:06</t>
+        </is>
+      </c>
+      <c r="C1410" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1410" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1410" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1410" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1410" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261014034806761301.xlsx</t>
+        </is>
+      </c>
+      <c r="H1410" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1410" s="4" t="inlineStr"/>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1411" s="6" t="inlineStr">
+        <is>
+          <t>03:48:07</t>
+        </is>
+      </c>
+      <c r="C1411" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1411" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1411" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1411" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1411" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1411" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1411" s="7" t="inlineStr"/>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1412" s="3" t="inlineStr">
+        <is>
+          <t>03:48:07</t>
+        </is>
+      </c>
+      <c r="C1412" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1412" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1412" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1412" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1412" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261014034807661109.pdf</t>
+        </is>
+      </c>
+      <c r="H1412" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1412" s="4" t="inlineStr"/>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1413" s="6" t="inlineStr">
+        <is>
+          <t>03:48:08</t>
+        </is>
+      </c>
+      <c r="C1413" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1413" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1413" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1413" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1413" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261014034808001939.jpeg</t>
+        </is>
+      </c>
+      <c r="H1413" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1413" s="7" t="inlineStr"/>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1414" s="3" t="inlineStr">
+        <is>
+          <t>03:48:08</t>
+        </is>
+      </c>
+      <c r="C1414" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1414" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1414" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1414" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1414" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261014034808320086.pages</t>
+        </is>
+      </c>
+      <c r="H1414" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1414" s="4" t="inlineStr"/>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1415" s="6" t="inlineStr">
+        <is>
+          <t>03:48:09</t>
+        </is>
+      </c>
+      <c r="C1415" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1415" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1415" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1415" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1415" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261014034809150018.pdf</t>
+        </is>
+      </c>
+      <c r="H1415" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1415" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1415"/>
+  <dimension ref="A1:I1438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -61344,6 +61344,995 @@
       </c>
       <c r="I1415" s="7" t="inlineStr"/>
     </row>
+    <row r="1416">
+      <c r="A1416" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1416" s="3" t="inlineStr">
+        <is>
+          <t>03:29:40</t>
+        </is>
+      </c>
+      <c r="C1416" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1416" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1416" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1416" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1416" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261015032940963624.gif</t>
+        </is>
+      </c>
+      <c r="H1416" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1416" s="4" t="inlineStr"/>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1417" s="6" t="inlineStr">
+        <is>
+          <t>03:29:41</t>
+        </is>
+      </c>
+      <c r="C1417" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1417" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1417" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1417" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1417" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261015032941392357.xlsx</t>
+        </is>
+      </c>
+      <c r="H1417" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1417" s="7" t="inlineStr"/>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1418" s="3" t="inlineStr">
+        <is>
+          <t>03:29:41</t>
+        </is>
+      </c>
+      <c r="C1418" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1418" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1418" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1418" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1418" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261015032941704013.csv</t>
+        </is>
+      </c>
+      <c r="H1418" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1418" s="4" t="inlineStr"/>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1419" s="6" t="inlineStr">
+        <is>
+          <t>03:29:42</t>
+        </is>
+      </c>
+      <c r="C1419" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1419" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1419" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1419" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1419" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261015032942036074.pdf</t>
+        </is>
+      </c>
+      <c r="H1419" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1419" s="7" t="inlineStr"/>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1420" s="3" t="inlineStr">
+        <is>
+          <t>03:29:42</t>
+        </is>
+      </c>
+      <c r="C1420" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1420" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1420" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1420" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1420" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261015032942363452.docx</t>
+        </is>
+      </c>
+      <c r="H1420" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1420" s="4" t="inlineStr"/>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1421" s="6" t="inlineStr">
+        <is>
+          <t>03:29:42</t>
+        </is>
+      </c>
+      <c r="C1421" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1421" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1421" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1421" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1421" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261015032942673630.pptx</t>
+        </is>
+      </c>
+      <c r="H1421" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1421" s="7" t="inlineStr"/>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1422" s="3" t="inlineStr">
+        <is>
+          <t>03:29:43</t>
+        </is>
+      </c>
+      <c r="C1422" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1422" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1422" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1422" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1422" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261015032943013275.jpg</t>
+        </is>
+      </c>
+      <c r="H1422" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1422" s="4" t="inlineStr"/>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1423" s="6" t="inlineStr">
+        <is>
+          <t>03:29:43</t>
+        </is>
+      </c>
+      <c r="C1423" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1423" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1423" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1423" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1423" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261015032943330847.doc</t>
+        </is>
+      </c>
+      <c r="H1423" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1423" s="7" t="inlineStr"/>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1424" s="3" t="inlineStr">
+        <is>
+          <t>03:29:43</t>
+        </is>
+      </c>
+      <c r="C1424" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1424" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1424" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1424" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1424" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261015032943678514.txt</t>
+        </is>
+      </c>
+      <c r="H1424" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1424" s="4" t="inlineStr"/>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1425" s="6" t="inlineStr">
+        <is>
+          <t>03:29:43</t>
+        </is>
+      </c>
+      <c r="C1425" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1425" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1425" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1425" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1425" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261015032943992048.xls</t>
+        </is>
+      </c>
+      <c r="H1425" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1425" s="7" t="inlineStr"/>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1426" s="3" t="inlineStr">
+        <is>
+          <t>03:29:44</t>
+        </is>
+      </c>
+      <c r="C1426" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1426" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1426" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1426" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1426" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261015032944329261.png</t>
+        </is>
+      </c>
+      <c r="H1426" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1426" s="4" t="inlineStr"/>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1427" s="6" t="inlineStr">
+        <is>
+          <t>03:29:44</t>
+        </is>
+      </c>
+      <c r="C1427" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1427" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1427" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1427" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1427" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261015032944662020.dat</t>
+        </is>
+      </c>
+      <c r="H1427" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1427" s="7" t="inlineStr"/>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1428" s="3" t="inlineStr">
+        <is>
+          <t>03:29:46</t>
+        </is>
+      </c>
+      <c r="C1428" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1428" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1428" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1428" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1428" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261015032946287640.docx</t>
+        </is>
+      </c>
+      <c r="H1428" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1428" s="4" t="inlineStr"/>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1429" s="6" t="inlineStr">
+        <is>
+          <t>03:29:46</t>
+        </is>
+      </c>
+      <c r="C1429" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1429" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1429" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1429" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1429" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261015032946622599.pdf</t>
+        </is>
+      </c>
+      <c r="H1429" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1429" s="7" t="inlineStr"/>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1430" s="3" t="inlineStr">
+        <is>
+          <t>03:29:46</t>
+        </is>
+      </c>
+      <c r="C1430" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1430" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1430" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1430" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1430" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261015032946931053.jpeg</t>
+        </is>
+      </c>
+      <c r="H1430" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1430" s="4" t="inlineStr"/>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1431" s="6" t="inlineStr">
+        <is>
+          <t>03:29:47</t>
+        </is>
+      </c>
+      <c r="C1431" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1431" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1431" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1431" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1431" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261015032947264465.xlsx</t>
+        </is>
+      </c>
+      <c r="H1431" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1431" s="7" t="inlineStr"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1432" s="3" t="inlineStr">
+        <is>
+          <t>03:29:47</t>
+        </is>
+      </c>
+      <c r="C1432" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1432" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1432" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1432" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1432" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261015032947910697.txt</t>
+        </is>
+      </c>
+      <c r="H1432" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1432" s="4" t="inlineStr"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1433" s="6" t="inlineStr">
+        <is>
+          <t>03:29:48</t>
+        </is>
+      </c>
+      <c r="C1433" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1433" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1433" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1433" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1433" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261015032948221412.xlsx</t>
+        </is>
+      </c>
+      <c r="H1433" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1433" s="7" t="inlineStr"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1434" s="3" t="inlineStr">
+        <is>
+          <t>03:29:48</t>
+        </is>
+      </c>
+      <c r="C1434" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1434" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1434" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1434" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1434" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1434" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1434" s="4" t="inlineStr"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1435" s="6" t="inlineStr">
+        <is>
+          <t>03:29:49</t>
+        </is>
+      </c>
+      <c r="C1435" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1435" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1435" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1435" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1435" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261015032949091093.pdf</t>
+        </is>
+      </c>
+      <c r="H1435" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1435" s="7" t="inlineStr"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1436" s="3" t="inlineStr">
+        <is>
+          <t>03:29:49</t>
+        </is>
+      </c>
+      <c r="C1436" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1436" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1436" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1436" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1436" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261015032949428535.jpeg</t>
+        </is>
+      </c>
+      <c r="H1436" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1436" s="4" t="inlineStr"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1437" s="6" t="inlineStr">
+        <is>
+          <t>03:29:49</t>
+        </is>
+      </c>
+      <c r="C1437" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1437" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1437" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1437" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1437" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261015032949742127.pages</t>
+        </is>
+      </c>
+      <c r="H1437" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1437" s="7" t="inlineStr"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1438" s="3" t="inlineStr">
+        <is>
+          <t>03:29:50</t>
+        </is>
+      </c>
+      <c r="C1438" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1438" s="4" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1438" s="4" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1438" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1438" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261015032950488034.pdf</t>
+        </is>
+      </c>
+      <c r="H1438" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1438" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1438"/>
+  <dimension ref="A1:I1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -62333,6 +62333,995 @@
       </c>
       <c r="I1438" s="4" t="inlineStr"/>
     </row>
+    <row r="1439">
+      <c r="A1439" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1439" s="6" t="inlineStr">
+        <is>
+          <t>03:25:12</t>
+        </is>
+      </c>
+      <c r="C1439" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1439" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1439" s="7" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1439" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1439" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261016032512167794.gif</t>
+        </is>
+      </c>
+      <c r="H1439" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1439" s="7" t="inlineStr"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1440" s="3" t="inlineStr">
+        <is>
+          <t>03:25:12</t>
+        </is>
+      </c>
+      <c r="C1440" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1440" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1440" s="4" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1440" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1440" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261016032512451446.xlsx</t>
+        </is>
+      </c>
+      <c r="H1440" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1440" s="4" t="inlineStr"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1441" s="6" t="inlineStr">
+        <is>
+          <t>03:25:12</t>
+        </is>
+      </c>
+      <c r="C1441" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1441" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1441" s="7" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1441" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1441" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261016032512729085.csv</t>
+        </is>
+      </c>
+      <c r="H1441" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1441" s="7" t="inlineStr"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1442" s="3" t="inlineStr">
+        <is>
+          <t>03:25:13</t>
+        </is>
+      </c>
+      <c r="C1442" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1442" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1442" s="4" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1442" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1442" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261016032513022561.pdf</t>
+        </is>
+      </c>
+      <c r="H1442" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1442" s="4" t="inlineStr"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1443" s="6" t="inlineStr">
+        <is>
+          <t>03:25:13</t>
+        </is>
+      </c>
+      <c r="C1443" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1443" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1443" s="7" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1443" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1443" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261016032513314237.docx</t>
+        </is>
+      </c>
+      <c r="H1443" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1443" s="7" t="inlineStr"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1444" s="3" t="inlineStr">
+        <is>
+          <t>03:25:13</t>
+        </is>
+      </c>
+      <c r="C1444" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1444" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1444" s="4" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1444" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1444" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261016032513587688.pptx</t>
+        </is>
+      </c>
+      <c r="H1444" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1444" s="4" t="inlineStr"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1445" s="6" t="inlineStr">
+        <is>
+          <t>03:25:13</t>
+        </is>
+      </c>
+      <c r="C1445" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1445" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1445" s="7" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1445" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1445" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261016032513885367.jpg</t>
+        </is>
+      </c>
+      <c r="H1445" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1445" s="7" t="inlineStr"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1446" s="3" t="inlineStr">
+        <is>
+          <t>03:25:14</t>
+        </is>
+      </c>
+      <c r="C1446" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1446" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1446" s="4" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1446" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1446" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261016032514159454.doc</t>
+        </is>
+      </c>
+      <c r="H1446" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1446" s="4" t="inlineStr"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1447" s="6" t="inlineStr">
+        <is>
+          <t>03:25:14</t>
+        </is>
+      </c>
+      <c r="C1447" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1447" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1447" s="7" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1447" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1447" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261016032514456468.txt</t>
+        </is>
+      </c>
+      <c r="H1447" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1447" s="7" t="inlineStr"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1448" s="3" t="inlineStr">
+        <is>
+          <t>03:25:14</t>
+        </is>
+      </c>
+      <c r="C1448" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1448" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1448" s="4" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1448" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1448" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261016032514750411.xls</t>
+        </is>
+      </c>
+      <c r="H1448" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1448" s="4" t="inlineStr"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1449" s="6" t="inlineStr">
+        <is>
+          <t>03:25:15</t>
+        </is>
+      </c>
+      <c r="C1449" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1449" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1449" s="7" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1449" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1449" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261016032515024495.png</t>
+        </is>
+      </c>
+      <c r="H1449" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1449" s="7" t="inlineStr"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1450" s="3" t="inlineStr">
+        <is>
+          <t>03:25:15</t>
+        </is>
+      </c>
+      <c r="C1450" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1450" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1450" s="4" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1450" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1450" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261016032515326350.dat</t>
+        </is>
+      </c>
+      <c r="H1450" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1450" s="4" t="inlineStr"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1451" s="6" t="inlineStr">
+        <is>
+          <t>03:25:25</t>
+        </is>
+      </c>
+      <c r="C1451" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1451" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1451" s="7" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1451" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1451" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261016032525941691.docx</t>
+        </is>
+      </c>
+      <c r="H1451" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1451" s="7" t="inlineStr"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1452" s="3" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C1452" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1452" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1452" s="4" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1452" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1452" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261016032526247051.pdf</t>
+        </is>
+      </c>
+      <c r="H1452" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1452" s="4" t="inlineStr"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1453" s="6" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C1453" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1453" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1453" s="7" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1453" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1453" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261016032526526537.jpeg</t>
+        </is>
+      </c>
+      <c r="H1453" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1453" s="7" t="inlineStr"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1454" s="3" t="inlineStr">
+        <is>
+          <t>03:25:26</t>
+        </is>
+      </c>
+      <c r="C1454" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1454" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1454" s="4" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1454" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1454" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261016032526828643.xlsx</t>
+        </is>
+      </c>
+      <c r="H1454" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1454" s="4" t="inlineStr"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1455" s="6" t="inlineStr">
+        <is>
+          <t>03:25:27</t>
+        </is>
+      </c>
+      <c r="C1455" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1455" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1455" s="7" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1455" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1455" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261016032527929282.txt</t>
+        </is>
+      </c>
+      <c r="H1455" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1455" s="7" t="inlineStr"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1456" s="3" t="inlineStr">
+        <is>
+          <t>03:25:28</t>
+        </is>
+      </c>
+      <c r="C1456" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1456" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1456" s="4" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1456" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1456" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261016032528208273.xlsx</t>
+        </is>
+      </c>
+      <c r="H1456" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1456" s="4" t="inlineStr"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1457" s="6" t="inlineStr">
+        <is>
+          <t>03:25:28</t>
+        </is>
+      </c>
+      <c r="C1457" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1457" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1457" s="7" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1457" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1457" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1457" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1457" s="7" t="inlineStr"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1458" s="3" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C1458" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1458" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1458" s="4" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1458" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1458" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261016032529643612.pdf</t>
+        </is>
+      </c>
+      <c r="H1458" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1458" s="4" t="inlineStr"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1459" s="6" t="inlineStr">
+        <is>
+          <t>03:25:29</t>
+        </is>
+      </c>
+      <c r="C1459" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1459" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1459" s="7" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1459" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1459" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261016032529948782.jpeg</t>
+        </is>
+      </c>
+      <c r="H1459" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1459" s="7" t="inlineStr"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1460" s="3" t="inlineStr">
+        <is>
+          <t>03:25:30</t>
+        </is>
+      </c>
+      <c r="C1460" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1460" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1460" s="4" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1460" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1460" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261016032530247866.pages</t>
+        </is>
+      </c>
+      <c r="H1460" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1460" s="4" t="inlineStr"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1461" s="6" t="inlineStr">
+        <is>
+          <t>03:25:32</t>
+        </is>
+      </c>
+      <c r="C1461" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1461" s="7" t="inlineStr">
+        <is>
+          <t>0432 Patchanan Chuwecha &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1461" s="7" t="inlineStr">
+        <is>
+          <t>1.pdf</t>
+        </is>
+      </c>
+      <c r="F1461" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1461" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/1_20261016032532745049.pdf</t>
+        </is>
+      </c>
+      <c r="H1461" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1461" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1461"/>
+  <dimension ref="A1:I1483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -63322,6 +63322,952 @@
       </c>
       <c r="I1461" s="7" t="inlineStr"/>
     </row>
+    <row r="1462">
+      <c r="A1462" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1462" s="3" t="inlineStr">
+        <is>
+          <t>03:15:34</t>
+        </is>
+      </c>
+      <c r="C1462" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1462" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1462" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1462" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1462" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261017031534172897.gif</t>
+        </is>
+      </c>
+      <c r="H1462" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1462" s="4" t="inlineStr"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1463" s="6" t="inlineStr">
+        <is>
+          <t>03:15:34</t>
+        </is>
+      </c>
+      <c r="C1463" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1463" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1463" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1463" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1463" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261017031534504615.xlsx</t>
+        </is>
+      </c>
+      <c r="H1463" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1463" s="7" t="inlineStr"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1464" s="3" t="inlineStr">
+        <is>
+          <t>03:15:34</t>
+        </is>
+      </c>
+      <c r="C1464" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1464" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1464" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1464" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1464" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261017031534824383.csv</t>
+        </is>
+      </c>
+      <c r="H1464" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1464" s="4" t="inlineStr"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1465" s="6" t="inlineStr">
+        <is>
+          <t>03:15:35</t>
+        </is>
+      </c>
+      <c r="C1465" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1465" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1465" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1465" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1465" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261017031535164227.pdf</t>
+        </is>
+      </c>
+      <c r="H1465" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1465" s="7" t="inlineStr"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1466" s="3" t="inlineStr">
+        <is>
+          <t>03:15:35</t>
+        </is>
+      </c>
+      <c r="C1466" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1466" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1466" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1466" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1466" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261017031535503971.docx</t>
+        </is>
+      </c>
+      <c r="H1466" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1466" s="4" t="inlineStr"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1467" s="6" t="inlineStr">
+        <is>
+          <t>03:15:35</t>
+        </is>
+      </c>
+      <c r="C1467" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1467" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1467" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1467" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1467" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261017031535826249.pptx</t>
+        </is>
+      </c>
+      <c r="H1467" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1467" s="7" t="inlineStr"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1468" s="3" t="inlineStr">
+        <is>
+          <t>03:15:36</t>
+        </is>
+      </c>
+      <c r="C1468" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1468" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1468" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1468" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1468" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261017031536174315.jpg</t>
+        </is>
+      </c>
+      <c r="H1468" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1468" s="4" t="inlineStr"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1469" s="6" t="inlineStr">
+        <is>
+          <t>03:15:36</t>
+        </is>
+      </c>
+      <c r="C1469" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1469" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1469" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1469" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1469" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261017031536494133.doc</t>
+        </is>
+      </c>
+      <c r="H1469" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1469" s="7" t="inlineStr"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1470" s="3" t="inlineStr">
+        <is>
+          <t>03:15:36</t>
+        </is>
+      </c>
+      <c r="C1470" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1470" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1470" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1470" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1470" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261017031536843065.txt</t>
+        </is>
+      </c>
+      <c r="H1470" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1470" s="4" t="inlineStr"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1471" s="6" t="inlineStr">
+        <is>
+          <t>03:15:37</t>
+        </is>
+      </c>
+      <c r="C1471" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1471" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1471" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1471" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1471" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261017031537183016.xls</t>
+        </is>
+      </c>
+      <c r="H1471" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1471" s="7" t="inlineStr"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1472" s="3" t="inlineStr">
+        <is>
+          <t>03:15:37</t>
+        </is>
+      </c>
+      <c r="C1472" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1472" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1472" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1472" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1472" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261017031537503563.png</t>
+        </is>
+      </c>
+      <c r="H1472" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1472" s="4" t="inlineStr"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1473" s="6" t="inlineStr">
+        <is>
+          <t>03:15:37</t>
+        </is>
+      </c>
+      <c r="C1473" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1473" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1473" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1473" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1473" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261017031537851232.dat</t>
+        </is>
+      </c>
+      <c r="H1473" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1473" s="7" t="inlineStr"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1474" s="3" t="inlineStr">
+        <is>
+          <t>03:16:25</t>
+        </is>
+      </c>
+      <c r="C1474" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1474" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1474" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1474" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1474" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261017031625272136.docx</t>
+        </is>
+      </c>
+      <c r="H1474" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1474" s="4" t="inlineStr"/>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1475" s="6" t="inlineStr">
+        <is>
+          <t>03:16:25</t>
+        </is>
+      </c>
+      <c r="C1475" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1475" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1475" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1475" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1475" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261017031625618667.pdf</t>
+        </is>
+      </c>
+      <c r="H1475" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1475" s="7" t="inlineStr"/>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1476" s="3" t="inlineStr">
+        <is>
+          <t>03:16:25</t>
+        </is>
+      </c>
+      <c r="C1476" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1476" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1476" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1476" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1476" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261017031625962038.jpeg</t>
+        </is>
+      </c>
+      <c r="H1476" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1476" s="4" t="inlineStr"/>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1477" s="6" t="inlineStr">
+        <is>
+          <t>03:16:26</t>
+        </is>
+      </c>
+      <c r="C1477" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1477" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1477" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1477" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1477" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261017031626280519.xlsx</t>
+        </is>
+      </c>
+      <c r="H1477" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1477" s="7" t="inlineStr"/>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1478" s="3" t="inlineStr">
+        <is>
+          <t>03:16:34</t>
+        </is>
+      </c>
+      <c r="C1478" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1478" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1478" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1478" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1478" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261017031634528208.txt</t>
+        </is>
+      </c>
+      <c r="H1478" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1478" s="4" t="inlineStr"/>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1479" s="6" t="inlineStr">
+        <is>
+          <t>03:16:34</t>
+        </is>
+      </c>
+      <c r="C1479" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1479" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1479" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1479" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1479" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261017031634846669.xlsx</t>
+        </is>
+      </c>
+      <c r="H1479" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1479" s="7" t="inlineStr"/>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1480" s="3" t="inlineStr">
+        <is>
+          <t>03:16:35</t>
+        </is>
+      </c>
+      <c r="C1480" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1480" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1480" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1480" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1480" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1480" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1480" s="4" t="inlineStr"/>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1481" s="6" t="inlineStr">
+        <is>
+          <t>03:16:45</t>
+        </is>
+      </c>
+      <c r="C1481" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1481" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1481" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1481" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1481" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261017031645181181.pdf</t>
+        </is>
+      </c>
+      <c r="H1481" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1481" s="7" t="inlineStr"/>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1482" s="3" t="inlineStr">
+        <is>
+          <t>03:16:45</t>
+        </is>
+      </c>
+      <c r="C1482" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1482" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1482" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1482" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1482" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261017031645506825.jpeg</t>
+        </is>
+      </c>
+      <c r="H1482" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1482" s="4" t="inlineStr"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B1483" s="6" t="inlineStr">
+        <is>
+          <t>03:16:45</t>
+        </is>
+      </c>
+      <c r="C1483" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1483" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1483" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1483" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1483" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261017031645861905.pages</t>
+        </is>
+      </c>
+      <c r="H1483" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1483" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1483"/>
+  <dimension ref="A1:I1505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64268,6 +64268,952 @@
       </c>
       <c r="I1483" s="7" t="inlineStr"/>
     </row>
+    <row r="1484">
+      <c r="A1484" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1484" s="3" t="inlineStr">
+        <is>
+          <t>03:19:44</t>
+        </is>
+      </c>
+      <c r="C1484" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1484" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1484" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1484" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1484" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261018031944941100.gif</t>
+        </is>
+      </c>
+      <c r="H1484" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1484" s="4" t="inlineStr"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1485" s="6" t="inlineStr">
+        <is>
+          <t>03:19:45</t>
+        </is>
+      </c>
+      <c r="C1485" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1485" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1485" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1485" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1485" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261018031945281698.xlsx</t>
+        </is>
+      </c>
+      <c r="H1485" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1485" s="7" t="inlineStr"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1486" s="3" t="inlineStr">
+        <is>
+          <t>03:19:45</t>
+        </is>
+      </c>
+      <c r="C1486" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1486" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1486" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1486" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1486" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261018031945606423.csv</t>
+        </is>
+      </c>
+      <c r="H1486" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1486" s="4" t="inlineStr"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1487" s="6" t="inlineStr">
+        <is>
+          <t>03:19:45</t>
+        </is>
+      </c>
+      <c r="C1487" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1487" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1487" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1487" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1487" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261018031945961785.pdf</t>
+        </is>
+      </c>
+      <c r="H1487" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1487" s="7" t="inlineStr"/>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1488" s="3" t="inlineStr">
+        <is>
+          <t>03:19:46</t>
+        </is>
+      </c>
+      <c r="C1488" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1488" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1488" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1488" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1488" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261018031946300308.docx</t>
+        </is>
+      </c>
+      <c r="H1488" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1488" s="4" t="inlineStr"/>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1489" s="6" t="inlineStr">
+        <is>
+          <t>03:19:46</t>
+        </is>
+      </c>
+      <c r="C1489" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1489" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1489" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1489" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1489" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261018031946627413.pptx</t>
+        </is>
+      </c>
+      <c r="H1489" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1489" s="7" t="inlineStr"/>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1490" s="3" t="inlineStr">
+        <is>
+          <t>03:19:46</t>
+        </is>
+      </c>
+      <c r="C1490" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1490" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1490" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1490" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1490" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261018031946978605.jpg</t>
+        </is>
+      </c>
+      <c r="H1490" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1490" s="4" t="inlineStr"/>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1491" s="6" t="inlineStr">
+        <is>
+          <t>03:19:47</t>
+        </is>
+      </c>
+      <c r="C1491" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1491" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1491" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1491" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1491" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261018031947302044.doc</t>
+        </is>
+      </c>
+      <c r="H1491" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1491" s="7" t="inlineStr"/>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1492" s="3" t="inlineStr">
+        <is>
+          <t>03:19:47</t>
+        </is>
+      </c>
+      <c r="C1492" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1492" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1492" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1492" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1492" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261018031947648523.txt</t>
+        </is>
+      </c>
+      <c r="H1492" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1492" s="4" t="inlineStr"/>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1493" s="6" t="inlineStr">
+        <is>
+          <t>03:19:48</t>
+        </is>
+      </c>
+      <c r="C1493" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1493" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1493" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1493" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1493" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261018031948000827.xls</t>
+        </is>
+      </c>
+      <c r="H1493" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1493" s="7" t="inlineStr"/>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1494" s="3" t="inlineStr">
+        <is>
+          <t>03:19:48</t>
+        </is>
+      </c>
+      <c r="C1494" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1494" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1494" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1494" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1494" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261018031948331024.png</t>
+        </is>
+      </c>
+      <c r="H1494" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1494" s="4" t="inlineStr"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1495" s="6" t="inlineStr">
+        <is>
+          <t>03:19:48</t>
+        </is>
+      </c>
+      <c r="C1495" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1495" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1495" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1495" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1495" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261018031948687018.dat</t>
+        </is>
+      </c>
+      <c r="H1495" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1495" s="7" t="inlineStr"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1496" s="3" t="inlineStr">
+        <is>
+          <t>03:19:52</t>
+        </is>
+      </c>
+      <c r="C1496" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1496" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1496" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1496" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1496" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261018031952095296.docx</t>
+        </is>
+      </c>
+      <c r="H1496" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1496" s="4" t="inlineStr"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1497" s="6" t="inlineStr">
+        <is>
+          <t>03:19:52</t>
+        </is>
+      </c>
+      <c r="C1497" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1497" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1497" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1497" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1497" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261018031952447427.pdf</t>
+        </is>
+      </c>
+      <c r="H1497" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1497" s="7" t="inlineStr"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1498" s="3" t="inlineStr">
+        <is>
+          <t>03:19:52</t>
+        </is>
+      </c>
+      <c r="C1498" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1498" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1498" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1498" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1498" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261018031952796980.jpeg</t>
+        </is>
+      </c>
+      <c r="H1498" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1498" s="4" t="inlineStr"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1499" s="6" t="inlineStr">
+        <is>
+          <t>03:19:53</t>
+        </is>
+      </c>
+      <c r="C1499" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1499" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1499" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1499" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1499" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261018031953159474.xlsx</t>
+        </is>
+      </c>
+      <c r="H1499" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1499" s="7" t="inlineStr"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1500" s="3" t="inlineStr">
+        <is>
+          <t>03:19:53</t>
+        </is>
+      </c>
+      <c r="C1500" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1500" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1500" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1500" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1500" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261018031953894990.txt</t>
+        </is>
+      </c>
+      <c r="H1500" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1500" s="4" t="inlineStr"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1501" s="6" t="inlineStr">
+        <is>
+          <t>03:19:54</t>
+        </is>
+      </c>
+      <c r="C1501" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1501" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1501" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1501" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1501" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261018031954243071.xlsx</t>
+        </is>
+      </c>
+      <c r="H1501" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1501" s="7" t="inlineStr"/>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1502" s="3" t="inlineStr">
+        <is>
+          <t>03:19:54</t>
+        </is>
+      </c>
+      <c r="C1502" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1502" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1502" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1502" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1502" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1502" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1502" s="4" t="inlineStr"/>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1503" s="6" t="inlineStr">
+        <is>
+          <t>03:19:55</t>
+        </is>
+      </c>
+      <c r="C1503" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1503" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1503" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1503" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1503" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261018031955525889.pdf</t>
+        </is>
+      </c>
+      <c r="H1503" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1503" s="7" t="inlineStr"/>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1504" s="3" t="inlineStr">
+        <is>
+          <t>03:19:55</t>
+        </is>
+      </c>
+      <c r="C1504" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1504" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1504" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1504" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1504" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261018031955855448.jpeg</t>
+        </is>
+      </c>
+      <c r="H1504" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1504" s="4" t="inlineStr"/>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B1505" s="6" t="inlineStr">
+        <is>
+          <t>03:19:56</t>
+        </is>
+      </c>
+      <c r="C1505" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1505" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1505" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1505" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1505" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261018031956207745.pages</t>
+        </is>
+      </c>
+      <c r="H1505" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1505" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1505"/>
+  <dimension ref="A1:I1527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -65214,6 +65214,952 @@
       </c>
       <c r="I1505" s="7" t="inlineStr"/>
     </row>
+    <row r="1506">
+      <c r="A1506" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1506" s="3" t="inlineStr">
+        <is>
+          <t>03:32:13</t>
+        </is>
+      </c>
+      <c r="C1506" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1506" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1506" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1506" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1506" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261019033213500005.gif</t>
+        </is>
+      </c>
+      <c r="H1506" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1506" s="4" t="inlineStr"/>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1507" s="6" t="inlineStr">
+        <is>
+          <t>03:32:13</t>
+        </is>
+      </c>
+      <c r="C1507" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1507" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1507" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1507" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1507" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261019033213928692.xlsx</t>
+        </is>
+      </c>
+      <c r="H1507" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1507" s="7" t="inlineStr"/>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1508" s="3" t="inlineStr">
+        <is>
+          <t>03:32:14</t>
+        </is>
+      </c>
+      <c r="C1508" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1508" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1508" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1508" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1508" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261019033214255457.csv</t>
+        </is>
+      </c>
+      <c r="H1508" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1508" s="4" t="inlineStr"/>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1509" s="6" t="inlineStr">
+        <is>
+          <t>03:32:14</t>
+        </is>
+      </c>
+      <c r="C1509" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1509" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1509" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1509" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1509" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261019033214596079.pdf</t>
+        </is>
+      </c>
+      <c r="H1509" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1509" s="7" t="inlineStr"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1510" s="3" t="inlineStr">
+        <is>
+          <t>03:32:14</t>
+        </is>
+      </c>
+      <c r="C1510" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1510" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1510" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1510" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1510" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261019033214947132.docx</t>
+        </is>
+      </c>
+      <c r="H1510" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1510" s="4" t="inlineStr"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1511" s="6" t="inlineStr">
+        <is>
+          <t>03:32:15</t>
+        </is>
+      </c>
+      <c r="C1511" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1511" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1511" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1511" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1511" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261019033215270888.pptx</t>
+        </is>
+      </c>
+      <c r="H1511" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1511" s="7" t="inlineStr"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1512" s="3" t="inlineStr">
+        <is>
+          <t>03:32:15</t>
+        </is>
+      </c>
+      <c r="C1512" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1512" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1512" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1512" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1512" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261019033215618973.jpg</t>
+        </is>
+      </c>
+      <c r="H1512" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1512" s="4" t="inlineStr"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1513" s="6" t="inlineStr">
+        <is>
+          <t>03:32:15</t>
+        </is>
+      </c>
+      <c r="C1513" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1513" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1513" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1513" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1513" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261019033215967443.doc</t>
+        </is>
+      </c>
+      <c r="H1513" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1513" s="7" t="inlineStr"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1514" s="3" t="inlineStr">
+        <is>
+          <t>03:32:16</t>
+        </is>
+      </c>
+      <c r="C1514" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1514" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1514" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1514" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1514" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261019033216304147.txt</t>
+        </is>
+      </c>
+      <c r="H1514" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1514" s="4" t="inlineStr"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1515" s="6" t="inlineStr">
+        <is>
+          <t>03:32:16</t>
+        </is>
+      </c>
+      <c r="C1515" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1515" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1515" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1515" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1515" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261019033216661281.xls</t>
+        </is>
+      </c>
+      <c r="H1515" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1515" s="7" t="inlineStr"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1516" s="3" t="inlineStr">
+        <is>
+          <t>03:32:16</t>
+        </is>
+      </c>
+      <c r="C1516" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1516" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1516" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1516" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1516" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261019033216987337.png</t>
+        </is>
+      </c>
+      <c r="H1516" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1516" s="4" t="inlineStr"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1517" s="6" t="inlineStr">
+        <is>
+          <t>03:32:17</t>
+        </is>
+      </c>
+      <c r="C1517" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1517" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1517" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1517" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1517" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261019033217335472.dat</t>
+        </is>
+      </c>
+      <c r="H1517" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1517" s="7" t="inlineStr"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1518" s="3" t="inlineStr">
+        <is>
+          <t>03:32:25</t>
+        </is>
+      </c>
+      <c r="C1518" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1518" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1518" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1518" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1518" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261019033225829490.docx</t>
+        </is>
+      </c>
+      <c r="H1518" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1518" s="4" t="inlineStr"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1519" s="6" t="inlineStr">
+        <is>
+          <t>03:32:26</t>
+        </is>
+      </c>
+      <c r="C1519" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1519" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1519" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1519" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1519" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261019033226157829.pdf</t>
+        </is>
+      </c>
+      <c r="H1519" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1519" s="7" t="inlineStr"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1520" s="3" t="inlineStr">
+        <is>
+          <t>03:32:26</t>
+        </is>
+      </c>
+      <c r="C1520" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1520" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1520" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1520" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1520" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261019033226510562.jpeg</t>
+        </is>
+      </c>
+      <c r="H1520" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1520" s="4" t="inlineStr"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1521" s="6" t="inlineStr">
+        <is>
+          <t>03:32:26</t>
+        </is>
+      </c>
+      <c r="C1521" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1521" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1521" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1521" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1521" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261019033226840175.xlsx</t>
+        </is>
+      </c>
+      <c r="H1521" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1521" s="7" t="inlineStr"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1522" s="3" t="inlineStr">
+        <is>
+          <t>03:32:28</t>
+        </is>
+      </c>
+      <c r="C1522" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1522" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1522" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1522" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1522" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261019033228152447.txt</t>
+        </is>
+      </c>
+      <c r="H1522" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1522" s="4" t="inlineStr"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1523" s="6" t="inlineStr">
+        <is>
+          <t>03:32:28</t>
+        </is>
+      </c>
+      <c r="C1523" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1523" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1523" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1523" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1523" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261019033228502949.xlsx</t>
+        </is>
+      </c>
+      <c r="H1523" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1523" s="7" t="inlineStr"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1524" s="3" t="inlineStr">
+        <is>
+          <t>03:32:28</t>
+        </is>
+      </c>
+      <c r="C1524" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1524" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1524" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1524" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1524" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1524" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1524" s="4" t="inlineStr"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1525" s="6" t="inlineStr">
+        <is>
+          <t>03:32:30</t>
+        </is>
+      </c>
+      <c r="C1525" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1525" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1525" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1525" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1525" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261019033230973358.pdf</t>
+        </is>
+      </c>
+      <c r="H1525" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1525" s="7" t="inlineStr"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1526" s="3" t="inlineStr">
+        <is>
+          <t>03:32:31</t>
+        </is>
+      </c>
+      <c r="C1526" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1526" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1526" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1526" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1526" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261019033231317359.jpeg</t>
+        </is>
+      </c>
+      <c r="H1526" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1526" s="4" t="inlineStr"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1527" s="6" t="inlineStr">
+        <is>
+          <t>03:32:31</t>
+        </is>
+      </c>
+      <c r="C1527" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1527" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1527" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1527" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1527" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261019033231647248.pages</t>
+        </is>
+      </c>
+      <c r="H1527" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1527" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1527"/>
+  <dimension ref="A1:I1549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -66160,6 +66160,952 @@
       </c>
       <c r="I1527" s="7" t="inlineStr"/>
     </row>
+    <row r="1528">
+      <c r="A1528" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1528" s="3" t="inlineStr">
+        <is>
+          <t>03:42:13</t>
+        </is>
+      </c>
+      <c r="C1528" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1528" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1528" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1528" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1528" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261020034213645403.gif</t>
+        </is>
+      </c>
+      <c r="H1528" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1528" s="4" t="inlineStr"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1529" s="6" t="inlineStr">
+        <is>
+          <t>03:42:13</t>
+        </is>
+      </c>
+      <c r="C1529" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1529" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1529" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1529" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1529" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261020034213850251.xlsx</t>
+        </is>
+      </c>
+      <c r="H1529" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1529" s="7" t="inlineStr"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1530" s="3" t="inlineStr">
+        <is>
+          <t>03:42:14</t>
+        </is>
+      </c>
+      <c r="C1530" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1530" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1530" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1530" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1530" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261020034214044894.csv</t>
+        </is>
+      </c>
+      <c r="H1530" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1530" s="4" t="inlineStr"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1531" s="6" t="inlineStr">
+        <is>
+          <t>03:42:14</t>
+        </is>
+      </c>
+      <c r="C1531" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1531" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1531" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1531" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1531" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261020034214255383.pdf</t>
+        </is>
+      </c>
+      <c r="H1531" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1531" s="7" t="inlineStr"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1532" s="3" t="inlineStr">
+        <is>
+          <t>03:42:14</t>
+        </is>
+      </c>
+      <c r="C1532" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1532" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1532" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1532" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1532" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261020034214465416.docx</t>
+        </is>
+      </c>
+      <c r="H1532" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1532" s="4" t="inlineStr"/>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1533" s="6" t="inlineStr">
+        <is>
+          <t>03:42:14</t>
+        </is>
+      </c>
+      <c r="C1533" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1533" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1533" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1533" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1533" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261020034214659505.pptx</t>
+        </is>
+      </c>
+      <c r="H1533" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1533" s="7" t="inlineStr"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1534" s="3" t="inlineStr">
+        <is>
+          <t>03:42:14</t>
+        </is>
+      </c>
+      <c r="C1534" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1534" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1534" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1534" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1534" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261020034214869699.jpg</t>
+        </is>
+      </c>
+      <c r="H1534" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1534" s="4" t="inlineStr"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1535" s="6" t="inlineStr">
+        <is>
+          <t>03:42:15</t>
+        </is>
+      </c>
+      <c r="C1535" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1535" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1535" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1535" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1535" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261020034215079155.doc</t>
+        </is>
+      </c>
+      <c r="H1535" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1535" s="7" t="inlineStr"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1536" s="3" t="inlineStr">
+        <is>
+          <t>03:42:15</t>
+        </is>
+      </c>
+      <c r="C1536" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1536" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1536" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1536" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1536" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261020034215271698.txt</t>
+        </is>
+      </c>
+      <c r="H1536" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1536" s="4" t="inlineStr"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1537" s="6" t="inlineStr">
+        <is>
+          <t>03:42:15</t>
+        </is>
+      </c>
+      <c r="C1537" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1537" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1537" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1537" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1537" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261020034215486947.xls</t>
+        </is>
+      </c>
+      <c r="H1537" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1537" s="7" t="inlineStr"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1538" s="3" t="inlineStr">
+        <is>
+          <t>03:42:15</t>
+        </is>
+      </c>
+      <c r="C1538" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1538" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1538" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1538" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1538" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261020034215682101.png</t>
+        </is>
+      </c>
+      <c r="H1538" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1538" s="4" t="inlineStr"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1539" s="6" t="inlineStr">
+        <is>
+          <t>03:42:15</t>
+        </is>
+      </c>
+      <c r="C1539" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1539" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1539" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1539" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1539" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261020034215894851.dat</t>
+        </is>
+      </c>
+      <c r="H1539" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1539" s="7" t="inlineStr"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1540" s="3" t="inlineStr">
+        <is>
+          <t>03:42:20</t>
+        </is>
+      </c>
+      <c r="C1540" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1540" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1540" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1540" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1540" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261020034220514128.docx</t>
+        </is>
+      </c>
+      <c r="H1540" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1540" s="4" t="inlineStr"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1541" s="6" t="inlineStr">
+        <is>
+          <t>03:42:20</t>
+        </is>
+      </c>
+      <c r="C1541" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1541" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1541" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1541" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1541" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261020034220711391.pdf</t>
+        </is>
+      </c>
+      <c r="H1541" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1541" s="7" t="inlineStr"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1542" s="3" t="inlineStr">
+        <is>
+          <t>03:42:20</t>
+        </is>
+      </c>
+      <c r="C1542" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1542" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1542" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1542" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1542" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261020034220931613.jpeg</t>
+        </is>
+      </c>
+      <c r="H1542" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1542" s="4" t="inlineStr"/>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1543" s="6" t="inlineStr">
+        <is>
+          <t>03:42:21</t>
+        </is>
+      </c>
+      <c r="C1543" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1543" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1543" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1543" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1543" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261020034221142731.xlsx</t>
+        </is>
+      </c>
+      <c r="H1543" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1543" s="7" t="inlineStr"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1544" s="3" t="inlineStr">
+        <is>
+          <t>03:42:21</t>
+        </is>
+      </c>
+      <c r="C1544" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1544" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1544" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1544" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1544" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261020034221638871.txt</t>
+        </is>
+      </c>
+      <c r="H1544" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1544" s="4" t="inlineStr"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1545" s="6" t="inlineStr">
+        <is>
+          <t>03:42:21</t>
+        </is>
+      </c>
+      <c r="C1545" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1545" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1545" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1545" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1545" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261020034221858653.xlsx</t>
+        </is>
+      </c>
+      <c r="H1545" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1545" s="7" t="inlineStr"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1546" s="3" t="inlineStr">
+        <is>
+          <t>03:42:22</t>
+        </is>
+      </c>
+      <c r="C1546" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1546" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1546" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1546" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1546" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1546" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1546" s="4" t="inlineStr"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1547" s="6" t="inlineStr">
+        <is>
+          <t>03:42:22</t>
+        </is>
+      </c>
+      <c r="C1547" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1547" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1547" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1547" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1547" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261020034222600030.pdf</t>
+        </is>
+      </c>
+      <c r="H1547" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1547" s="7" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1548" s="3" t="inlineStr">
+        <is>
+          <t>03:42:22</t>
+        </is>
+      </c>
+      <c r="C1548" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1548" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1548" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1548" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1548" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261020034222811226.jpeg</t>
+        </is>
+      </c>
+      <c r="H1548" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1548" s="4" t="inlineStr"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1549" s="6" t="inlineStr">
+        <is>
+          <t>03:42:23</t>
+        </is>
+      </c>
+      <c r="C1549" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1549" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1549" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1549" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1549" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261020034223007453.pages</t>
+        </is>
+      </c>
+      <c r="H1549" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1549" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1549"/>
+  <dimension ref="A1:I1571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -67106,6 +67106,952 @@
       </c>
       <c r="I1549" s="7" t="inlineStr"/>
     </row>
+    <row r="1550">
+      <c r="A1550" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1550" s="3" t="inlineStr">
+        <is>
+          <t>03:34:01</t>
+        </is>
+      </c>
+      <c r="C1550" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1550" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1550" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1550" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1550" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261021033401778131.gif</t>
+        </is>
+      </c>
+      <c r="H1550" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1550" s="4" t="inlineStr"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1551" s="6" t="inlineStr">
+        <is>
+          <t>03:34:02</t>
+        </is>
+      </c>
+      <c r="C1551" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1551" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1551" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1551" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1551" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261021033402154713.xlsx</t>
+        </is>
+      </c>
+      <c r="H1551" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1551" s="7" t="inlineStr"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1552" s="3" t="inlineStr">
+        <is>
+          <t>03:34:02</t>
+        </is>
+      </c>
+      <c r="C1552" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1552" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1552" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1552" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1552" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261021033402503918.csv</t>
+        </is>
+      </c>
+      <c r="H1552" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1552" s="4" t="inlineStr"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1553" s="6" t="inlineStr">
+        <is>
+          <t>03:34:02</t>
+        </is>
+      </c>
+      <c r="C1553" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1553" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1553" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1553" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1553" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261021033402877257.pdf</t>
+        </is>
+      </c>
+      <c r="H1553" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1553" s="7" t="inlineStr"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1554" s="3" t="inlineStr">
+        <is>
+          <t>03:34:03</t>
+        </is>
+      </c>
+      <c r="C1554" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1554" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1554" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1554" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1554" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261021033403247417.docx</t>
+        </is>
+      </c>
+      <c r="H1554" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1554" s="4" t="inlineStr"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1555" s="6" t="inlineStr">
+        <is>
+          <t>03:34:03</t>
+        </is>
+      </c>
+      <c r="C1555" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1555" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1555" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1555" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1555" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261021033403591814.pptx</t>
+        </is>
+      </c>
+      <c r="H1555" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1555" s="7" t="inlineStr"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1556" s="3" t="inlineStr">
+        <is>
+          <t>03:34:03</t>
+        </is>
+      </c>
+      <c r="C1556" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1556" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1556" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1556" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1556" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261021033403970453.jpg</t>
+        </is>
+      </c>
+      <c r="H1556" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1556" s="4" t="inlineStr"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1557" s="6" t="inlineStr">
+        <is>
+          <t>03:34:04</t>
+        </is>
+      </c>
+      <c r="C1557" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1557" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1557" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1557" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1557" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261021033404351071.doc</t>
+        </is>
+      </c>
+      <c r="H1557" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1557" s="7" t="inlineStr"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1558" s="3" t="inlineStr">
+        <is>
+          <t>03:34:04</t>
+        </is>
+      </c>
+      <c r="C1558" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1558" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1558" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1558" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1558" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261021033404697477.txt</t>
+        </is>
+      </c>
+      <c r="H1558" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1558" s="4" t="inlineStr"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1559" s="6" t="inlineStr">
+        <is>
+          <t>03:34:05</t>
+        </is>
+      </c>
+      <c r="C1559" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1559" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1559" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1559" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1559" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261021033405073638.xls</t>
+        </is>
+      </c>
+      <c r="H1559" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1559" s="7" t="inlineStr"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1560" s="3" t="inlineStr">
+        <is>
+          <t>03:34:05</t>
+        </is>
+      </c>
+      <c r="C1560" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1560" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1560" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1560" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1560" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261021033405434838.png</t>
+        </is>
+      </c>
+      <c r="H1560" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1560" s="4" t="inlineStr"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1561" s="6" t="inlineStr">
+        <is>
+          <t>03:34:05</t>
+        </is>
+      </c>
+      <c r="C1561" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1561" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1561" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1561" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1561" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261021033405772199.dat</t>
+        </is>
+      </c>
+      <c r="H1561" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1561" s="7" t="inlineStr"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1562" s="3" t="inlineStr">
+        <is>
+          <t>03:34:08</t>
+        </is>
+      </c>
+      <c r="C1562" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1562" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1562" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1562" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1562" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261021033408135326.docx</t>
+        </is>
+      </c>
+      <c r="H1562" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1562" s="4" t="inlineStr"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1563" s="6" t="inlineStr">
+        <is>
+          <t>03:34:08</t>
+        </is>
+      </c>
+      <c r="C1563" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1563" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1563" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1563" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1563" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261021033408475352.pdf</t>
+        </is>
+      </c>
+      <c r="H1563" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1563" s="7" t="inlineStr"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1564" s="3" t="inlineStr">
+        <is>
+          <t>03:34:08</t>
+        </is>
+      </c>
+      <c r="C1564" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1564" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1564" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1564" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1564" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261021033408853178.jpeg</t>
+        </is>
+      </c>
+      <c r="H1564" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1564" s="4" t="inlineStr"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1565" s="6" t="inlineStr">
+        <is>
+          <t>03:34:09</t>
+        </is>
+      </c>
+      <c r="C1565" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1565" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1565" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1565" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1565" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261021033409219264.xlsx</t>
+        </is>
+      </c>
+      <c r="H1565" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1565" s="7" t="inlineStr"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1566" s="3" t="inlineStr">
+        <is>
+          <t>03:34:09</t>
+        </is>
+      </c>
+      <c r="C1566" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1566" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1566" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1566" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1566" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261021033409877267.txt</t>
+        </is>
+      </c>
+      <c r="H1566" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1566" s="4" t="inlineStr"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1567" s="6" t="inlineStr">
+        <is>
+          <t>03:34:10</t>
+        </is>
+      </c>
+      <c r="C1567" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1567" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1567" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1567" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1567" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261021033410245237.xlsx</t>
+        </is>
+      </c>
+      <c r="H1567" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1567" s="7" t="inlineStr"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1568" s="3" t="inlineStr">
+        <is>
+          <t>03:34:10</t>
+        </is>
+      </c>
+      <c r="C1568" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1568" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1568" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1568" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1568" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1568" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1568" s="4" t="inlineStr"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1569" s="6" t="inlineStr">
+        <is>
+          <t>03:34:11</t>
+        </is>
+      </c>
+      <c r="C1569" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1569" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1569" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1569" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1569" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261021033411311441.pdf</t>
+        </is>
+      </c>
+      <c r="H1569" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1569" s="7" t="inlineStr"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1570" s="3" t="inlineStr">
+        <is>
+          <t>03:34:11</t>
+        </is>
+      </c>
+      <c r="C1570" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1570" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1570" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1570" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1570" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261021033411692459.jpeg</t>
+        </is>
+      </c>
+      <c r="H1570" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1570" s="4" t="inlineStr"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1571" s="6" t="inlineStr">
+        <is>
+          <t>03:34:12</t>
+        </is>
+      </c>
+      <c r="C1571" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1571" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1571" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1571" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1571" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261021033412096089.pages</t>
+        </is>
+      </c>
+      <c r="H1571" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1571" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1571"/>
+  <dimension ref="A1:I1593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -68052,6 +68052,952 @@
       </c>
       <c r="I1571" s="7" t="inlineStr"/>
     </row>
+    <row r="1572">
+      <c r="A1572" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1572" s="3" t="inlineStr">
+        <is>
+          <t>03:33:55</t>
+        </is>
+      </c>
+      <c r="C1572" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1572" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1572" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1572" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1572" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261022033355239010.gif</t>
+        </is>
+      </c>
+      <c r="H1572" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1572" s="4" t="inlineStr"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1573" s="6" t="inlineStr">
+        <is>
+          <t>03:33:55</t>
+        </is>
+      </c>
+      <c r="C1573" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1573" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1573" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1573" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1573" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261022033355609060.xlsx</t>
+        </is>
+      </c>
+      <c r="H1573" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1573" s="7" t="inlineStr"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1574" s="3" t="inlineStr">
+        <is>
+          <t>03:33:56</t>
+        </is>
+      </c>
+      <c r="C1574" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1574" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1574" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1574" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1574" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261022033356022933.csv</t>
+        </is>
+      </c>
+      <c r="H1574" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1574" s="4" t="inlineStr"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1575" s="6" t="inlineStr">
+        <is>
+          <t>03:33:56</t>
+        </is>
+      </c>
+      <c r="C1575" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1575" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1575" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1575" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1575" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261022033356367228.pdf</t>
+        </is>
+      </c>
+      <c r="H1575" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1575" s="7" t="inlineStr"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1576" s="3" t="inlineStr">
+        <is>
+          <t>03:33:56</t>
+        </is>
+      </c>
+      <c r="C1576" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1576" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1576" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1576" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1576" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261022033356735011.docx</t>
+        </is>
+      </c>
+      <c r="H1576" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1576" s="4" t="inlineStr"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1577" s="6" t="inlineStr">
+        <is>
+          <t>03:33:57</t>
+        </is>
+      </c>
+      <c r="C1577" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1577" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1577" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1577" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1577" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261022033357076628.pptx</t>
+        </is>
+      </c>
+      <c r="H1577" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1577" s="7" t="inlineStr"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1578" s="3" t="inlineStr">
+        <is>
+          <t>03:33:57</t>
+        </is>
+      </c>
+      <c r="C1578" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1578" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1578" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1578" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1578" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261022033357450196.jpg</t>
+        </is>
+      </c>
+      <c r="H1578" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1578" s="4" t="inlineStr"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1579" s="6" t="inlineStr">
+        <is>
+          <t>03:33:57</t>
+        </is>
+      </c>
+      <c r="C1579" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1579" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1579" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1579" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1579" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261022033357813438.doc</t>
+        </is>
+      </c>
+      <c r="H1579" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1579" s="7" t="inlineStr"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1580" s="3" t="inlineStr">
+        <is>
+          <t>03:33:58</t>
+        </is>
+      </c>
+      <c r="C1580" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1580" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1580" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1580" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1580" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261022033358158785.txt</t>
+        </is>
+      </c>
+      <c r="H1580" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1580" s="4" t="inlineStr"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1581" s="6" t="inlineStr">
+        <is>
+          <t>03:33:58</t>
+        </is>
+      </c>
+      <c r="C1581" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1581" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1581" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1581" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1581" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261022033358522248.xls</t>
+        </is>
+      </c>
+      <c r="H1581" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1581" s="7" t="inlineStr"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1582" s="3" t="inlineStr">
+        <is>
+          <t>03:33:58</t>
+        </is>
+      </c>
+      <c r="C1582" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1582" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1582" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1582" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1582" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261022033358887795.png</t>
+        </is>
+      </c>
+      <c r="H1582" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1582" s="4" t="inlineStr"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1583" s="6" t="inlineStr">
+        <is>
+          <t>03:33:59</t>
+        </is>
+      </c>
+      <c r="C1583" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1583" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1583" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1583" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1583" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261022033359234459.dat</t>
+        </is>
+      </c>
+      <c r="H1583" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1583" s="7" t="inlineStr"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1584" s="3" t="inlineStr">
+        <is>
+          <t>03:34:01</t>
+        </is>
+      </c>
+      <c r="C1584" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1584" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1584" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1584" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1584" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261022033401711068.docx</t>
+        </is>
+      </c>
+      <c r="H1584" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1584" s="4" t="inlineStr"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1585" s="6" t="inlineStr">
+        <is>
+          <t>03:34:02</t>
+        </is>
+      </c>
+      <c r="C1585" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1585" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1585" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1585" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1585" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261022033402074217.pdf</t>
+        </is>
+      </c>
+      <c r="H1585" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1585" s="7" t="inlineStr"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1586" s="3" t="inlineStr">
+        <is>
+          <t>03:34:02</t>
+        </is>
+      </c>
+      <c r="C1586" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1586" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1586" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1586" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1586" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261022033402422803.jpeg</t>
+        </is>
+      </c>
+      <c r="H1586" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1586" s="4" t="inlineStr"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1587" s="6" t="inlineStr">
+        <is>
+          <t>03:34:02</t>
+        </is>
+      </c>
+      <c r="C1587" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1587" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1587" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1587" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1587" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261022033402789343.xlsx</t>
+        </is>
+      </c>
+      <c r="H1587" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1587" s="7" t="inlineStr"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1588" s="3" t="inlineStr">
+        <is>
+          <t>03:34:03</t>
+        </is>
+      </c>
+      <c r="C1588" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1588" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1588" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1588" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1588" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261022033403552939.txt</t>
+        </is>
+      </c>
+      <c r="H1588" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1588" s="4" t="inlineStr"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1589" s="6" t="inlineStr">
+        <is>
+          <t>03:34:03</t>
+        </is>
+      </c>
+      <c r="C1589" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1589" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1589" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1589" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1589" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261022033403897279.xlsx</t>
+        </is>
+      </c>
+      <c r="H1589" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1589" s="7" t="inlineStr"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1590" s="3" t="inlineStr">
+        <is>
+          <t>03:34:04</t>
+        </is>
+      </c>
+      <c r="C1590" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1590" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1590" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1590" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1590" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1590" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1590" s="4" t="inlineStr"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1591" s="6" t="inlineStr">
+        <is>
+          <t>03:34:05</t>
+        </is>
+      </c>
+      <c r="C1591" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1591" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1591" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1591" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1591" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261022033405238051.pdf</t>
+        </is>
+      </c>
+      <c r="H1591" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1591" s="7" t="inlineStr"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1592" s="3" t="inlineStr">
+        <is>
+          <t>03:34:05</t>
+        </is>
+      </c>
+      <c r="C1592" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1592" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1592" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1592" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1592" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261022033405585176.jpeg</t>
+        </is>
+      </c>
+      <c r="H1592" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1592" s="4" t="inlineStr"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1593" s="6" t="inlineStr">
+        <is>
+          <t>03:34:05</t>
+        </is>
+      </c>
+      <c r="C1593" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1593" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1593" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1593" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1593" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261022033405962149.pages</t>
+        </is>
+      </c>
+      <c r="H1593" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1593" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1593"/>
+  <dimension ref="A1:I1615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -68998,6 +68998,952 @@
       </c>
       <c r="I1593" s="7" t="inlineStr"/>
     </row>
+    <row r="1594">
+      <c r="A1594" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1594" s="3" t="inlineStr">
+        <is>
+          <t>03:38:52</t>
+        </is>
+      </c>
+      <c r="C1594" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1594" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1594" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1594" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1594" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261023033852885294.gif</t>
+        </is>
+      </c>
+      <c r="H1594" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1594" s="4" t="inlineStr"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1595" s="6" t="inlineStr">
+        <is>
+          <t>03:38:53</t>
+        </is>
+      </c>
+      <c r="C1595" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1595" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1595" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1595" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1595" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261023033853262944.xlsx</t>
+        </is>
+      </c>
+      <c r="H1595" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1595" s="7" t="inlineStr"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1596" s="3" t="inlineStr">
+        <is>
+          <t>03:38:53</t>
+        </is>
+      </c>
+      <c r="C1596" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1596" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1596" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1596" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1596" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261023033853650942.csv</t>
+        </is>
+      </c>
+      <c r="H1596" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1596" s="4" t="inlineStr"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1597" s="6" t="inlineStr">
+        <is>
+          <t>03:38:54</t>
+        </is>
+      </c>
+      <c r="C1597" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1597" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1597" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1597" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1597" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261023033854008926.pdf</t>
+        </is>
+      </c>
+      <c r="H1597" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1597" s="7" t="inlineStr"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1598" s="3" t="inlineStr">
+        <is>
+          <t>03:38:54</t>
+        </is>
+      </c>
+      <c r="C1598" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1598" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1598" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1598" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1598" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261023033854409270.docx</t>
+        </is>
+      </c>
+      <c r="H1598" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1598" s="4" t="inlineStr"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1599" s="6" t="inlineStr">
+        <is>
+          <t>03:38:54</t>
+        </is>
+      </c>
+      <c r="C1599" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1599" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1599" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1599" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1599" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261023033854770291.pptx</t>
+        </is>
+      </c>
+      <c r="H1599" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1599" s="7" t="inlineStr"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1600" s="3" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C1600" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1600" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1600" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1600" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1600" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261023033855166931.jpg</t>
+        </is>
+      </c>
+      <c r="H1600" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1600" s="4" t="inlineStr"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1601" s="6" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C1601" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1601" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1601" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1601" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1601" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261023033855551150.doc</t>
+        </is>
+      </c>
+      <c r="H1601" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1601" s="7" t="inlineStr"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1602" s="3" t="inlineStr">
+        <is>
+          <t>03:38:55</t>
+        </is>
+      </c>
+      <c r="C1602" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1602" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1602" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1602" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1602" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261023033855911657.txt</t>
+        </is>
+      </c>
+      <c r="H1602" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1602" s="4" t="inlineStr"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1603" s="6" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C1603" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1603" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1603" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1603" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1603" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261023033856299894.xls</t>
+        </is>
+      </c>
+      <c r="H1603" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1603" s="7" t="inlineStr"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1604" s="3" t="inlineStr">
+        <is>
+          <t>03:38:56</t>
+        </is>
+      </c>
+      <c r="C1604" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1604" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1604" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1604" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1604" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261023033856697877.png</t>
+        </is>
+      </c>
+      <c r="H1604" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1604" s="4" t="inlineStr"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1605" s="6" t="inlineStr">
+        <is>
+          <t>03:38:57</t>
+        </is>
+      </c>
+      <c r="C1605" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1605" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1605" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1605" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1605" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261023033857054329.dat</t>
+        </is>
+      </c>
+      <c r="H1605" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1605" s="7" t="inlineStr"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1606" s="3" t="inlineStr">
+        <is>
+          <t>03:39:17</t>
+        </is>
+      </c>
+      <c r="C1606" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1606" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1606" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1606" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1606" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261023033917640492.docx</t>
+        </is>
+      </c>
+      <c r="H1606" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1606" s="4" t="inlineStr"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1607" s="6" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C1607" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1607" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1607" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1607" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1607" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261023033918037370.pdf</t>
+        </is>
+      </c>
+      <c r="H1607" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1607" s="7" t="inlineStr"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1608" s="3" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C1608" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1608" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1608" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1608" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1608" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261023033918403543.jpeg</t>
+        </is>
+      </c>
+      <c r="H1608" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1608" s="4" t="inlineStr"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1609" s="6" t="inlineStr">
+        <is>
+          <t>03:39:18</t>
+        </is>
+      </c>
+      <c r="C1609" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1609" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1609" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1609" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1609" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261023033918818144.xlsx</t>
+        </is>
+      </c>
+      <c r="H1609" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1609" s="7" t="inlineStr"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1610" s="3" t="inlineStr">
+        <is>
+          <t>03:39:20</t>
+        </is>
+      </c>
+      <c r="C1610" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1610" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1610" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1610" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1610" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261023033920552777.txt</t>
+        </is>
+      </c>
+      <c r="H1610" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1610" s="4" t="inlineStr"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1611" s="6" t="inlineStr">
+        <is>
+          <t>03:39:20</t>
+        </is>
+      </c>
+      <c r="C1611" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1611" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1611" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1611" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1611" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261023033920920894.xlsx</t>
+        </is>
+      </c>
+      <c r="H1611" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1611" s="7" t="inlineStr"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1612" s="3" t="inlineStr">
+        <is>
+          <t>03:39:21</t>
+        </is>
+      </c>
+      <c r="C1612" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1612" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1612" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1612" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1612" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1612" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1612" s="4" t="inlineStr"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1613" s="6" t="inlineStr">
+        <is>
+          <t>03:39:24</t>
+        </is>
+      </c>
+      <c r="C1613" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1613" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1613" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1613" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1613" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261023033924422570.pdf</t>
+        </is>
+      </c>
+      <c r="H1613" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1613" s="7" t="inlineStr"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1614" s="3" t="inlineStr">
+        <is>
+          <t>03:39:24</t>
+        </is>
+      </c>
+      <c r="C1614" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1614" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1614" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1614" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1614" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261023033924780852.jpeg</t>
+        </is>
+      </c>
+      <c r="H1614" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1614" s="4" t="inlineStr"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1615" s="6" t="inlineStr">
+        <is>
+          <t>03:39:25</t>
+        </is>
+      </c>
+      <c r="C1615" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1615" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1615" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1615" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1615" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261023033925183730.pages</t>
+        </is>
+      </c>
+      <c r="H1615" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1615" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1615"/>
+  <dimension ref="A1:I1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -69944,6 +69944,952 @@
       </c>
       <c r="I1615" s="7" t="inlineStr"/>
     </row>
+    <row r="1616">
+      <c r="A1616" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1616" s="3" t="inlineStr">
+        <is>
+          <t>03:32:50</t>
+        </is>
+      </c>
+      <c r="C1616" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1616" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1616" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1616" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1616" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261024033250430900.gif</t>
+        </is>
+      </c>
+      <c r="H1616" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1616" s="4" t="inlineStr"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1617" s="6" t="inlineStr">
+        <is>
+          <t>03:32:50</t>
+        </is>
+      </c>
+      <c r="C1617" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1617" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1617" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1617" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1617" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261024033250700493.xlsx</t>
+        </is>
+      </c>
+      <c r="H1617" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1617" s="7" t="inlineStr"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1618" s="3" t="inlineStr">
+        <is>
+          <t>03:32:50</t>
+        </is>
+      </c>
+      <c r="C1618" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1618" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1618" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1618" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1618" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261024033250990135.csv</t>
+        </is>
+      </c>
+      <c r="H1618" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1618" s="4" t="inlineStr"/>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1619" s="6" t="inlineStr">
+        <is>
+          <t>03:32:51</t>
+        </is>
+      </c>
+      <c r="C1619" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1619" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1619" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1619" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1619" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261024033251431152.pdf</t>
+        </is>
+      </c>
+      <c r="H1619" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1619" s="7" t="inlineStr"/>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1620" s="3" t="inlineStr">
+        <is>
+          <t>03:32:51</t>
+        </is>
+      </c>
+      <c r="C1620" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1620" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1620" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1620" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1620" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261024033251872609.docx</t>
+        </is>
+      </c>
+      <c r="H1620" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1620" s="4" t="inlineStr"/>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1621" s="6" t="inlineStr">
+        <is>
+          <t>03:32:52</t>
+        </is>
+      </c>
+      <c r="C1621" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1621" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1621" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1621" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1621" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261024033252281914.pptx</t>
+        </is>
+      </c>
+      <c r="H1621" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1621" s="7" t="inlineStr"/>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1622" s="3" t="inlineStr">
+        <is>
+          <t>03:32:52</t>
+        </is>
+      </c>
+      <c r="C1622" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1622" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1622" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1622" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1622" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261024033252586398.jpg</t>
+        </is>
+      </c>
+      <c r="H1622" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1622" s="4" t="inlineStr"/>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1623" s="6" t="inlineStr">
+        <is>
+          <t>03:32:52</t>
+        </is>
+      </c>
+      <c r="C1623" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1623" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1623" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1623" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1623" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261024033252884285.doc</t>
+        </is>
+      </c>
+      <c r="H1623" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1623" s="7" t="inlineStr"/>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1624" s="3" t="inlineStr">
+        <is>
+          <t>03:32:53</t>
+        </is>
+      </c>
+      <c r="C1624" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1624" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1624" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1624" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1624" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261024033253147309.txt</t>
+        </is>
+      </c>
+      <c r="H1624" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1624" s="4" t="inlineStr"/>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1625" s="6" t="inlineStr">
+        <is>
+          <t>03:32:53</t>
+        </is>
+      </c>
+      <c r="C1625" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1625" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1625" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1625" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1625" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261024033253437574.xls</t>
+        </is>
+      </c>
+      <c r="H1625" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1625" s="7" t="inlineStr"/>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1626" s="3" t="inlineStr">
+        <is>
+          <t>03:32:53</t>
+        </is>
+      </c>
+      <c r="C1626" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1626" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1626" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1626" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1626" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261024033253727295.png</t>
+        </is>
+      </c>
+      <c r="H1626" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1626" s="4" t="inlineStr"/>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1627" s="6" t="inlineStr">
+        <is>
+          <t>03:32:53</t>
+        </is>
+      </c>
+      <c r="C1627" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1627" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1627" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1627" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1627" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261024033253995595.dat</t>
+        </is>
+      </c>
+      <c r="H1627" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1627" s="7" t="inlineStr"/>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1628" s="3" t="inlineStr">
+        <is>
+          <t>03:32:57</t>
+        </is>
+      </c>
+      <c r="C1628" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1628" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1628" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1628" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1628" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261024033257255261.docx</t>
+        </is>
+      </c>
+      <c r="H1628" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1628" s="4" t="inlineStr"/>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1629" s="6" t="inlineStr">
+        <is>
+          <t>03:32:57</t>
+        </is>
+      </c>
+      <c r="C1629" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1629" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1629" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1629" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1629" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261024033257553050.pdf</t>
+        </is>
+      </c>
+      <c r="H1629" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1629" s="7" t="inlineStr"/>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1630" s="3" t="inlineStr">
+        <is>
+          <t>03:32:57</t>
+        </is>
+      </c>
+      <c r="C1630" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1630" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1630" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1630" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1630" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261024033257812059.jpeg</t>
+        </is>
+      </c>
+      <c r="H1630" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1630" s="4" t="inlineStr"/>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1631" s="6" t="inlineStr">
+        <is>
+          <t>03:32:58</t>
+        </is>
+      </c>
+      <c r="C1631" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1631" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1631" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1631" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1631" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261024033258090639.xlsx</t>
+        </is>
+      </c>
+      <c r="H1631" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1631" s="7" t="inlineStr"/>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1632" s="3" t="inlineStr">
+        <is>
+          <t>03:32:59</t>
+        </is>
+      </c>
+      <c r="C1632" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1632" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1632" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1632" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1632" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261024033259247159.txt</t>
+        </is>
+      </c>
+      <c r="H1632" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1632" s="4" t="inlineStr"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1633" s="6" t="inlineStr">
+        <is>
+          <t>03:32:59</t>
+        </is>
+      </c>
+      <c r="C1633" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1633" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1633" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1633" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1633" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261024033259502588.xlsx</t>
+        </is>
+      </c>
+      <c r="H1633" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1633" s="7" t="inlineStr"/>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1634" s="3" t="inlineStr">
+        <is>
+          <t>03:32:59</t>
+        </is>
+      </c>
+      <c r="C1634" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1634" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1634" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1634" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1634" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1634" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1634" s="4" t="inlineStr"/>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1635" s="6" t="inlineStr">
+        <is>
+          <t>03:33:01</t>
+        </is>
+      </c>
+      <c r="C1635" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1635" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1635" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1635" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1635" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261024033301520491.pdf</t>
+        </is>
+      </c>
+      <c r="H1635" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1635" s="7" t="inlineStr"/>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1636" s="3" t="inlineStr">
+        <is>
+          <t>03:33:01</t>
+        </is>
+      </c>
+      <c r="C1636" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1636" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1636" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1636" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1636" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261024033301805017.jpeg</t>
+        </is>
+      </c>
+      <c r="H1636" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1636" s="4" t="inlineStr"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B1637" s="6" t="inlineStr">
+        <is>
+          <t>03:33:02</t>
+        </is>
+      </c>
+      <c r="C1637" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1637" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1637" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1637" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1637" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261024033302070293.pages</t>
+        </is>
+      </c>
+      <c r="H1637" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1637" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1637"/>
+  <dimension ref="A1:I1659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -70890,6 +70890,952 @@
       </c>
       <c r="I1637" s="7" t="inlineStr"/>
     </row>
+    <row r="1638">
+      <c r="A1638" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1638" s="3" t="inlineStr">
+        <is>
+          <t>03:29:17</t>
+        </is>
+      </c>
+      <c r="C1638" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1638" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1638" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1638" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1638" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261025032917079858.gif</t>
+        </is>
+      </c>
+      <c r="H1638" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1638" s="4" t="inlineStr"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1639" s="6" t="inlineStr">
+        <is>
+          <t>03:29:17</t>
+        </is>
+      </c>
+      <c r="C1639" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1639" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1639" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1639" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1639" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261025032917259820.xlsx</t>
+        </is>
+      </c>
+      <c r="H1639" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1639" s="7" t="inlineStr"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1640" s="3" t="inlineStr">
+        <is>
+          <t>03:29:17</t>
+        </is>
+      </c>
+      <c r="C1640" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1640" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1640" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1640" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1640" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261025032917446615.csv</t>
+        </is>
+      </c>
+      <c r="H1640" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1640" s="4" t="inlineStr"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1641" s="6" t="inlineStr">
+        <is>
+          <t>03:29:17</t>
+        </is>
+      </c>
+      <c r="C1641" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1641" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1641" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1641" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1641" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261025032917616717.pdf</t>
+        </is>
+      </c>
+      <c r="H1641" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1641" s="7" t="inlineStr"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1642" s="3" t="inlineStr">
+        <is>
+          <t>03:29:17</t>
+        </is>
+      </c>
+      <c r="C1642" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1642" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1642" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1642" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1642" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261025032917803872.docx</t>
+        </is>
+      </c>
+      <c r="H1642" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1642" s="4" t="inlineStr"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1643" s="6" t="inlineStr">
+        <is>
+          <t>03:29:17</t>
+        </is>
+      </c>
+      <c r="C1643" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1643" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1643" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1643" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1643" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261025032917988261.pptx</t>
+        </is>
+      </c>
+      <c r="H1643" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1643" s="7" t="inlineStr"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1644" s="3" t="inlineStr">
+        <is>
+          <t>03:29:18</t>
+        </is>
+      </c>
+      <c r="C1644" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1644" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1644" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1644" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1644" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261025032918160896.jpg</t>
+        </is>
+      </c>
+      <c r="H1644" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1644" s="4" t="inlineStr"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1645" s="6" t="inlineStr">
+        <is>
+          <t>03:29:18</t>
+        </is>
+      </c>
+      <c r="C1645" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1645" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1645" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1645" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1645" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261025032918348359.doc</t>
+        </is>
+      </c>
+      <c r="H1645" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1645" s="7" t="inlineStr"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1646" s="3" t="inlineStr">
+        <is>
+          <t>03:29:18</t>
+        </is>
+      </c>
+      <c r="C1646" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1646" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1646" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1646" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1646" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261025032918528930.txt</t>
+        </is>
+      </c>
+      <c r="H1646" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1646" s="4" t="inlineStr"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1647" s="6" t="inlineStr">
+        <is>
+          <t>03:29:18</t>
+        </is>
+      </c>
+      <c r="C1647" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1647" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1647" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1647" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1647" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261025032918708817.xls</t>
+        </is>
+      </c>
+      <c r="H1647" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1647" s="7" t="inlineStr"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1648" s="3" t="inlineStr">
+        <is>
+          <t>03:29:18</t>
+        </is>
+      </c>
+      <c r="C1648" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1648" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1648" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1648" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1648" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261025032918897889.png</t>
+        </is>
+      </c>
+      <c r="H1648" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1648" s="4" t="inlineStr"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1649" s="6" t="inlineStr">
+        <is>
+          <t>03:29:19</t>
+        </is>
+      </c>
+      <c r="C1649" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1649" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1649" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1649" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1649" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261025032919077721.dat</t>
+        </is>
+      </c>
+      <c r="H1649" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1649" s="7" t="inlineStr"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1650" s="3" t="inlineStr">
+        <is>
+          <t>03:29:26</t>
+        </is>
+      </c>
+      <c r="C1650" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1650" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1650" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1650" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1650" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261025032926035609.docx</t>
+        </is>
+      </c>
+      <c r="H1650" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1650" s="4" t="inlineStr"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1651" s="6" t="inlineStr">
+        <is>
+          <t>03:29:26</t>
+        </is>
+      </c>
+      <c r="C1651" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1651" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1651" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1651" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1651" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261025032926227775.pdf</t>
+        </is>
+      </c>
+      <c r="H1651" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1651" s="7" t="inlineStr"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1652" s="3" t="inlineStr">
+        <is>
+          <t>03:29:26</t>
+        </is>
+      </c>
+      <c r="C1652" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1652" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1652" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1652" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1652" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261025032926416806.jpeg</t>
+        </is>
+      </c>
+      <c r="H1652" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1652" s="4" t="inlineStr"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1653" s="6" t="inlineStr">
+        <is>
+          <t>03:29:26</t>
+        </is>
+      </c>
+      <c r="C1653" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1653" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1653" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1653" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1653" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261025032926586274.xlsx</t>
+        </is>
+      </c>
+      <c r="H1653" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1653" s="7" t="inlineStr"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1654" s="3" t="inlineStr">
+        <is>
+          <t>03:29:28</t>
+        </is>
+      </c>
+      <c r="C1654" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1654" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1654" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1654" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1654" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261025032928495659.txt</t>
+        </is>
+      </c>
+      <c r="H1654" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1654" s="4" t="inlineStr"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1655" s="6" t="inlineStr">
+        <is>
+          <t>03:29:28</t>
+        </is>
+      </c>
+      <c r="C1655" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1655" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1655" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1655" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1655" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261025032928687226.xlsx</t>
+        </is>
+      </c>
+      <c r="H1655" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1655" s="7" t="inlineStr"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1656" s="3" t="inlineStr">
+        <is>
+          <t>03:29:28</t>
+        </is>
+      </c>
+      <c r="C1656" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1656" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1656" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1656" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1656" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1656" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1656" s="4" t="inlineStr"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1657" s="6" t="inlineStr">
+        <is>
+          <t>03:29:30</t>
+        </is>
+      </c>
+      <c r="C1657" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1657" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1657" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1657" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1657" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261025032930302700.pdf</t>
+        </is>
+      </c>
+      <c r="H1657" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1657" s="7" t="inlineStr"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1658" s="3" t="inlineStr">
+        <is>
+          <t>03:29:30</t>
+        </is>
+      </c>
+      <c r="C1658" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1658" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1658" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1658" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1658" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261025032930490104.jpeg</t>
+        </is>
+      </c>
+      <c r="H1658" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1658" s="4" t="inlineStr"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B1659" s="6" t="inlineStr">
+        <is>
+          <t>03:29:30</t>
+        </is>
+      </c>
+      <c r="C1659" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1659" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1659" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1659" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1659" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261025032930659733.pages</t>
+        </is>
+      </c>
+      <c r="H1659" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1659" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1659"/>
+  <dimension ref="A1:I1681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71836,6 +71836,952 @@
       </c>
       <c r="I1659" s="7" t="inlineStr"/>
     </row>
+    <row r="1660">
+      <c r="A1660" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1660" s="3" t="inlineStr">
+        <is>
+          <t>03:31:40</t>
+        </is>
+      </c>
+      <c r="C1660" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1660" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1660" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1660" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1660" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261026033140686818.gif</t>
+        </is>
+      </c>
+      <c r="H1660" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1660" s="4" t="inlineStr"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1661" s="6" t="inlineStr">
+        <is>
+          <t>03:31:40</t>
+        </is>
+      </c>
+      <c r="C1661" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1661" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1661" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1661" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1661" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261026033140951908.xlsx</t>
+        </is>
+      </c>
+      <c r="H1661" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1661" s="7" t="inlineStr"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1662" s="3" t="inlineStr">
+        <is>
+          <t>03:31:41</t>
+        </is>
+      </c>
+      <c r="C1662" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1662" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1662" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1662" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1662" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261026033141224535.csv</t>
+        </is>
+      </c>
+      <c r="H1662" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1662" s="4" t="inlineStr"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1663" s="6" t="inlineStr">
+        <is>
+          <t>03:31:41</t>
+        </is>
+      </c>
+      <c r="C1663" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1663" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1663" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1663" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1663" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261026033141477425.pdf</t>
+        </is>
+      </c>
+      <c r="H1663" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1663" s="7" t="inlineStr"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1664" s="3" t="inlineStr">
+        <is>
+          <t>03:31:41</t>
+        </is>
+      </c>
+      <c r="C1664" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1664" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1664" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1664" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1664" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261026033141757938.docx</t>
+        </is>
+      </c>
+      <c r="H1664" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1664" s="4" t="inlineStr"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1665" s="6" t="inlineStr">
+        <is>
+          <t>03:31:42</t>
+        </is>
+      </c>
+      <c r="C1665" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1665" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1665" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1665" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1665" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261026033142038406.pptx</t>
+        </is>
+      </c>
+      <c r="H1665" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1665" s="7" t="inlineStr"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1666" s="3" t="inlineStr">
+        <is>
+          <t>03:31:42</t>
+        </is>
+      </c>
+      <c r="C1666" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1666" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1666" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1666" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1666" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261026033142293206.jpg</t>
+        </is>
+      </c>
+      <c r="H1666" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1666" s="4" t="inlineStr"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1667" s="6" t="inlineStr">
+        <is>
+          <t>03:31:42</t>
+        </is>
+      </c>
+      <c r="C1667" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1667" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1667" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1667" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1667" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261026033142571412.doc</t>
+        </is>
+      </c>
+      <c r="H1667" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1667" s="7" t="inlineStr"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1668" s="3" t="inlineStr">
+        <is>
+          <t>03:31:42</t>
+        </is>
+      </c>
+      <c r="C1668" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1668" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1668" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1668" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1668" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261026033142845297.txt</t>
+        </is>
+      </c>
+      <c r="H1668" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1668" s="4" t="inlineStr"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1669" s="6" t="inlineStr">
+        <is>
+          <t>03:31:43</t>
+        </is>
+      </c>
+      <c r="C1669" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1669" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1669" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1669" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1669" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261026033143099525.xls</t>
+        </is>
+      </c>
+      <c r="H1669" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1669" s="7" t="inlineStr"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1670" s="3" t="inlineStr">
+        <is>
+          <t>03:31:43</t>
+        </is>
+      </c>
+      <c r="C1670" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1670" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1670" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1670" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1670" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261026033143379808.png</t>
+        </is>
+      </c>
+      <c r="H1670" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1670" s="4" t="inlineStr"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1671" s="6" t="inlineStr">
+        <is>
+          <t>03:31:43</t>
+        </is>
+      </c>
+      <c r="C1671" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1671" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1671" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1671" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1671" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261026033143657128.dat</t>
+        </is>
+      </c>
+      <c r="H1671" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1671" s="7" t="inlineStr"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1672" s="3" t="inlineStr">
+        <is>
+          <t>03:31:45</t>
+        </is>
+      </c>
+      <c r="C1672" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1672" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1672" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1672" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1672" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261026033145385326.docx</t>
+        </is>
+      </c>
+      <c r="H1672" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1672" s="4" t="inlineStr"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1673" s="6" t="inlineStr">
+        <is>
+          <t>03:31:45</t>
+        </is>
+      </c>
+      <c r="C1673" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1673" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1673" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1673" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1673" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261026033145666340.pdf</t>
+        </is>
+      </c>
+      <c r="H1673" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1673" s="7" t="inlineStr"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1674" s="3" t="inlineStr">
+        <is>
+          <t>03:31:45</t>
+        </is>
+      </c>
+      <c r="C1674" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1674" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1674" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1674" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1674" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261026033145945095.jpeg</t>
+        </is>
+      </c>
+      <c r="H1674" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1674" s="4" t="inlineStr"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1675" s="6" t="inlineStr">
+        <is>
+          <t>03:31:46</t>
+        </is>
+      </c>
+      <c r="C1675" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1675" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1675" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1675" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1675" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261026033146203864.xlsx</t>
+        </is>
+      </c>
+      <c r="H1675" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1675" s="7" t="inlineStr"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1676" s="3" t="inlineStr">
+        <is>
+          <t>03:31:46</t>
+        </is>
+      </c>
+      <c r="C1676" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1676" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1676" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1676" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1676" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261026033146769840.txt</t>
+        </is>
+      </c>
+      <c r="H1676" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1676" s="4" t="inlineStr"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1677" s="6" t="inlineStr">
+        <is>
+          <t>03:31:47</t>
+        </is>
+      </c>
+      <c r="C1677" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1677" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1677" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1677" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1677" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261026033147047031.xlsx</t>
+        </is>
+      </c>
+      <c r="H1677" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1677" s="7" t="inlineStr"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1678" s="3" t="inlineStr">
+        <is>
+          <t>03:31:47</t>
+        </is>
+      </c>
+      <c r="C1678" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1678" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1678" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1678" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1678" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1678" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1678" s="4" t="inlineStr"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1679" s="6" t="inlineStr">
+        <is>
+          <t>03:31:47</t>
+        </is>
+      </c>
+      <c r="C1679" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1679" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1679" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1679" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1679" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261026033147774267.pdf</t>
+        </is>
+      </c>
+      <c r="H1679" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1679" s="7" t="inlineStr"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1680" s="3" t="inlineStr">
+        <is>
+          <t>03:31:48</t>
+        </is>
+      </c>
+      <c r="C1680" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1680" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1680" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1680" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1680" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261026033148057495.jpeg</t>
+        </is>
+      </c>
+      <c r="H1680" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1680" s="4" t="inlineStr"/>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1681" s="6" t="inlineStr">
+        <is>
+          <t>03:31:48</t>
+        </is>
+      </c>
+      <c r="C1681" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1681" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1681" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1681" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1681" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261026033148345023.pages</t>
+        </is>
+      </c>
+      <c r="H1681" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1681" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1681"/>
+  <dimension ref="A1:I1703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72782,6 +72782,952 @@
       </c>
       <c r="I1681" s="7" t="inlineStr"/>
     </row>
+    <row r="1682">
+      <c r="A1682" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1682" s="3" t="inlineStr">
+        <is>
+          <t>03:57:42</t>
+        </is>
+      </c>
+      <c r="C1682" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1682" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1682" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1682" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1682" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261027035742549745.gif</t>
+        </is>
+      </c>
+      <c r="H1682" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1682" s="4" t="inlineStr"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1683" s="6" t="inlineStr">
+        <is>
+          <t>03:57:42</t>
+        </is>
+      </c>
+      <c r="C1683" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1683" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1683" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1683" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1683" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261027035742938762.xlsx</t>
+        </is>
+      </c>
+      <c r="H1683" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1683" s="7" t="inlineStr"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1684" s="3" t="inlineStr">
+        <is>
+          <t>03:57:43</t>
+        </is>
+      </c>
+      <c r="C1684" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1684" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1684" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1684" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1684" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261027035743345619.csv</t>
+        </is>
+      </c>
+      <c r="H1684" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1684" s="4" t="inlineStr"/>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1685" s="6" t="inlineStr">
+        <is>
+          <t>03:57:43</t>
+        </is>
+      </c>
+      <c r="C1685" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1685" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1685" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1685" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1685" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261027035743719639.pdf</t>
+        </is>
+      </c>
+      <c r="H1685" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1685" s="7" t="inlineStr"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1686" s="3" t="inlineStr">
+        <is>
+          <t>03:57:44</t>
+        </is>
+      </c>
+      <c r="C1686" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1686" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1686" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1686" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1686" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261027035744129204.docx</t>
+        </is>
+      </c>
+      <c r="H1686" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1686" s="4" t="inlineStr"/>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1687" s="6" t="inlineStr">
+        <is>
+          <t>03:57:44</t>
+        </is>
+      </c>
+      <c r="C1687" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1687" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1687" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1687" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1687" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261027035744527864.pptx</t>
+        </is>
+      </c>
+      <c r="H1687" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1687" s="7" t="inlineStr"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1688" s="3" t="inlineStr">
+        <is>
+          <t>03:57:44</t>
+        </is>
+      </c>
+      <c r="C1688" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1688" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1688" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1688" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1688" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261027035744906062.jpg</t>
+        </is>
+      </c>
+      <c r="H1688" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1688" s="4" t="inlineStr"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1689" s="6" t="inlineStr">
+        <is>
+          <t>03:57:45</t>
+        </is>
+      </c>
+      <c r="C1689" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1689" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1689" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1689" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1689" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261027035745319514.doc</t>
+        </is>
+      </c>
+      <c r="H1689" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1689" s="7" t="inlineStr"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1690" s="3" t="inlineStr">
+        <is>
+          <t>03:57:45</t>
+        </is>
+      </c>
+      <c r="C1690" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1690" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1690" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1690" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1690" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261027035745725655.txt</t>
+        </is>
+      </c>
+      <c r="H1690" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1690" s="4" t="inlineStr"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1691" s="6" t="inlineStr">
+        <is>
+          <t>03:57:46</t>
+        </is>
+      </c>
+      <c r="C1691" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1691" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1691" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1691" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1691" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261027035746108836.xls</t>
+        </is>
+      </c>
+      <c r="H1691" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1691" s="7" t="inlineStr"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1692" s="3" t="inlineStr">
+        <is>
+          <t>03:57:46</t>
+        </is>
+      </c>
+      <c r="C1692" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1692" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1692" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1692" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1692" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261027035746521355.png</t>
+        </is>
+      </c>
+      <c r="H1692" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1692" s="4" t="inlineStr"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1693" s="6" t="inlineStr">
+        <is>
+          <t>03:57:46</t>
+        </is>
+      </c>
+      <c r="C1693" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1693" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1693" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1693" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1693" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261027035746923407.dat</t>
+        </is>
+      </c>
+      <c r="H1693" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1693" s="7" t="inlineStr"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1694" s="3" t="inlineStr">
+        <is>
+          <t>03:58:06</t>
+        </is>
+      </c>
+      <c r="C1694" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1694" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1694" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1694" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1694" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261027035806479019.docx</t>
+        </is>
+      </c>
+      <c r="H1694" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1694" s="4" t="inlineStr"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1695" s="6" t="inlineStr">
+        <is>
+          <t>03:58:06</t>
+        </is>
+      </c>
+      <c r="C1695" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1695" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1695" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1695" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1695" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261027035806883854.pdf</t>
+        </is>
+      </c>
+      <c r="H1695" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1695" s="7" t="inlineStr"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1696" s="3" t="inlineStr">
+        <is>
+          <t>03:58:07</t>
+        </is>
+      </c>
+      <c r="C1696" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1696" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1696" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1696" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1696" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261027035807301626.jpeg</t>
+        </is>
+      </c>
+      <c r="H1696" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1696" s="4" t="inlineStr"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1697" s="6" t="inlineStr">
+        <is>
+          <t>03:58:07</t>
+        </is>
+      </c>
+      <c r="C1697" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1697" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1697" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1697" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1697" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261027035807723833.xlsx</t>
+        </is>
+      </c>
+      <c r="H1697" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1697" s="7" t="inlineStr"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1698" s="3" t="inlineStr">
+        <is>
+          <t>03:58:12</t>
+        </is>
+      </c>
+      <c r="C1698" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1698" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1698" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1698" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1698" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261027035812460852.txt</t>
+        </is>
+      </c>
+      <c r="H1698" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1698" s="4" t="inlineStr"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1699" s="6" t="inlineStr">
+        <is>
+          <t>03:58:12</t>
+        </is>
+      </c>
+      <c r="C1699" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1699" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1699" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1699" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1699" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261027035812886932.xlsx</t>
+        </is>
+      </c>
+      <c r="H1699" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1699" s="7" t="inlineStr"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1700" s="3" t="inlineStr">
+        <is>
+          <t>03:58:13</t>
+        </is>
+      </c>
+      <c r="C1700" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1700" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1700" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1700" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1700" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1700" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1700" s="4" t="inlineStr"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1701" s="6" t="inlineStr">
+        <is>
+          <t>03:58:17</t>
+        </is>
+      </c>
+      <c r="C1701" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1701" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1701" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1701" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1701" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261027035817519730.pdf</t>
+        </is>
+      </c>
+      <c r="H1701" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1701" s="7" t="inlineStr"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1702" s="3" t="inlineStr">
+        <is>
+          <t>03:58:17</t>
+        </is>
+      </c>
+      <c r="C1702" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1702" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1702" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1702" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1702" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261027035817935216.jpeg</t>
+        </is>
+      </c>
+      <c r="H1702" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1702" s="4" t="inlineStr"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1703" s="6" t="inlineStr">
+        <is>
+          <t>03:58:18</t>
+        </is>
+      </c>
+      <c r="C1703" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1703" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1703" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1703" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1703" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261027035818347230.pages</t>
+        </is>
+      </c>
+      <c r="H1703" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1703" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1703"/>
+  <dimension ref="A1:I1725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73728,6 +73728,952 @@
       </c>
       <c r="I1703" s="7" t="inlineStr"/>
     </row>
+    <row r="1704">
+      <c r="A1704" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1704" s="3" t="inlineStr">
+        <is>
+          <t>04:20:36</t>
+        </is>
+      </c>
+      <c r="C1704" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1704" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1704" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1704" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1704" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261028042036219997.gif</t>
+        </is>
+      </c>
+      <c r="H1704" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1704" s="4" t="inlineStr"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1705" s="6" t="inlineStr">
+        <is>
+          <t>04:20:36</t>
+        </is>
+      </c>
+      <c r="C1705" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1705" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1705" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1705" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1705" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261028042036600033.xlsx</t>
+        </is>
+      </c>
+      <c r="H1705" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1705" s="7" t="inlineStr"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1706" s="3" t="inlineStr">
+        <is>
+          <t>04:20:36</t>
+        </is>
+      </c>
+      <c r="C1706" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1706" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1706" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1706" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1706" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261028042036990560.csv</t>
+        </is>
+      </c>
+      <c r="H1706" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1706" s="4" t="inlineStr"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1707" s="6" t="inlineStr">
+        <is>
+          <t>04:20:37</t>
+        </is>
+      </c>
+      <c r="C1707" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1707" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1707" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1707" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1707" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261028042037354405.pdf</t>
+        </is>
+      </c>
+      <c r="H1707" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1707" s="7" t="inlineStr"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1708" s="3" t="inlineStr">
+        <is>
+          <t>04:20:37</t>
+        </is>
+      </c>
+      <c r="C1708" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1708" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1708" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1708" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1708" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261028042037742599.docx</t>
+        </is>
+      </c>
+      <c r="H1708" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1708" s="4" t="inlineStr"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1709" s="6" t="inlineStr">
+        <is>
+          <t>04:20:38</t>
+        </is>
+      </c>
+      <c r="C1709" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1709" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1709" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1709" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1709" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261028042038127886.pptx</t>
+        </is>
+      </c>
+      <c r="H1709" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1709" s="7" t="inlineStr"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1710" s="3" t="inlineStr">
+        <is>
+          <t>04:20:38</t>
+        </is>
+      </c>
+      <c r="C1710" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1710" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1710" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1710" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1710" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261028042038493769.jpg</t>
+        </is>
+      </c>
+      <c r="H1710" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1710" s="4" t="inlineStr"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1711" s="6" t="inlineStr">
+        <is>
+          <t>04:20:38</t>
+        </is>
+      </c>
+      <c r="C1711" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1711" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1711" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1711" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1711" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261028042038892052.doc</t>
+        </is>
+      </c>
+      <c r="H1711" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1711" s="7" t="inlineStr"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1712" s="3" t="inlineStr">
+        <is>
+          <t>04:20:39</t>
+        </is>
+      </c>
+      <c r="C1712" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1712" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1712" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1712" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1712" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261028042039277229.txt</t>
+        </is>
+      </c>
+      <c r="H1712" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1712" s="4" t="inlineStr"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1713" s="6" t="inlineStr">
+        <is>
+          <t>04:20:39</t>
+        </is>
+      </c>
+      <c r="C1713" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1713" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1713" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1713" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1713" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261028042039662310.xls</t>
+        </is>
+      </c>
+      <c r="H1713" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1713" s="7" t="inlineStr"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1714" s="3" t="inlineStr">
+        <is>
+          <t>04:20:40</t>
+        </is>
+      </c>
+      <c r="C1714" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1714" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1714" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1714" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1714" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261028042040025948.png</t>
+        </is>
+      </c>
+      <c r="H1714" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1714" s="4" t="inlineStr"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1715" s="6" t="inlineStr">
+        <is>
+          <t>04:20:40</t>
+        </is>
+      </c>
+      <c r="C1715" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1715" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1715" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1715" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1715" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261028042040424248.dat</t>
+        </is>
+      </c>
+      <c r="H1715" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1715" s="7" t="inlineStr"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1716" s="3" t="inlineStr">
+        <is>
+          <t>04:21:20</t>
+        </is>
+      </c>
+      <c r="C1716" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1716" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1716" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1716" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1716" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261028042120627316.docx</t>
+        </is>
+      </c>
+      <c r="H1716" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1716" s="4" t="inlineStr"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1717" s="6" t="inlineStr">
+        <is>
+          <t>04:21:20</t>
+        </is>
+      </c>
+      <c r="C1717" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1717" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1717" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1717" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1717" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261028042120993821.pdf</t>
+        </is>
+      </c>
+      <c r="H1717" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1717" s="7" t="inlineStr"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1718" s="3" t="inlineStr">
+        <is>
+          <t>04:21:21</t>
+        </is>
+      </c>
+      <c r="C1718" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1718" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1718" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1718" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1718" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261028042121393261.jpeg</t>
+        </is>
+      </c>
+      <c r="H1718" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1718" s="4" t="inlineStr"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1719" s="6" t="inlineStr">
+        <is>
+          <t>04:21:21</t>
+        </is>
+      </c>
+      <c r="C1719" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1719" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1719" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1719" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1719" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261028042121784846.xlsx</t>
+        </is>
+      </c>
+      <c r="H1719" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1719" s="7" t="inlineStr"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1720" s="3" t="inlineStr">
+        <is>
+          <t>04:21:24</t>
+        </is>
+      </c>
+      <c r="C1720" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1720" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1720" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1720" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1720" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261028042124891053.txt</t>
+        </is>
+      </c>
+      <c r="H1720" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1720" s="4" t="inlineStr"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1721" s="6" t="inlineStr">
+        <is>
+          <t>04:21:25</t>
+        </is>
+      </c>
+      <c r="C1721" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1721" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1721" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1721" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1721" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261028042125283455.xlsx</t>
+        </is>
+      </c>
+      <c r="H1721" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1721" s="7" t="inlineStr"/>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1722" s="3" t="inlineStr">
+        <is>
+          <t>04:21:25</t>
+        </is>
+      </c>
+      <c r="C1722" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1722" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1722" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1722" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1722" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1722" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1722" s="4" t="inlineStr"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1723" s="6" t="inlineStr">
+        <is>
+          <t>04:21:28</t>
+        </is>
+      </c>
+      <c r="C1723" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1723" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1723" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1723" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1723" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261028042128311808.pdf</t>
+        </is>
+      </c>
+      <c r="H1723" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1723" s="7" t="inlineStr"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1724" s="3" t="inlineStr">
+        <is>
+          <t>04:21:28</t>
+        </is>
+      </c>
+      <c r="C1724" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1724" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1724" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1724" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1724" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261028042128679989.jpeg</t>
+        </is>
+      </c>
+      <c r="H1724" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1724" s="4" t="inlineStr"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1725" s="6" t="inlineStr">
+        <is>
+          <t>04:21:29</t>
+        </is>
+      </c>
+      <c r="C1725" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1725" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1725" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1725" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1725" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261028042129077649.pages</t>
+        </is>
+      </c>
+      <c r="H1725" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1725" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1725"/>
+  <dimension ref="A1:I1747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74674,6 +74674,952 @@
       </c>
       <c r="I1725" s="7" t="inlineStr"/>
     </row>
+    <row r="1726">
+      <c r="A1726" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1726" s="3" t="inlineStr">
+        <is>
+          <t>04:40:25</t>
+        </is>
+      </c>
+      <c r="C1726" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1726" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1726" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1726" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1726" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261029044025028894.gif</t>
+        </is>
+      </c>
+      <c r="H1726" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1726" s="4" t="inlineStr"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1727" s="6" t="inlineStr">
+        <is>
+          <t>04:40:25</t>
+        </is>
+      </c>
+      <c r="C1727" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1727" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1727" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1727" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1727" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261029044025421839.xlsx</t>
+        </is>
+      </c>
+      <c r="H1727" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1727" s="7" t="inlineStr"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1728" s="3" t="inlineStr">
+        <is>
+          <t>04:40:25</t>
+        </is>
+      </c>
+      <c r="C1728" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1728" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1728" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1728" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1728" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261029044025830820.csv</t>
+        </is>
+      </c>
+      <c r="H1728" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1728" s="4" t="inlineStr"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1729" s="6" t="inlineStr">
+        <is>
+          <t>04:40:26</t>
+        </is>
+      </c>
+      <c r="C1729" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1729" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1729" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1729" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1729" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261029044026223545.pdf</t>
+        </is>
+      </c>
+      <c r="H1729" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1729" s="7" t="inlineStr"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1730" s="3" t="inlineStr">
+        <is>
+          <t>04:40:26</t>
+        </is>
+      </c>
+      <c r="C1730" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1730" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1730" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1730" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1730" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261029044026631793.docx</t>
+        </is>
+      </c>
+      <c r="H1730" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1730" s="4" t="inlineStr"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1731" s="6" t="inlineStr">
+        <is>
+          <t>04:40:27</t>
+        </is>
+      </c>
+      <c r="C1731" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1731" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1731" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1731" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1731" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261029044027035100.pptx</t>
+        </is>
+      </c>
+      <c r="H1731" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1731" s="7" t="inlineStr"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1732" s="3" t="inlineStr">
+        <is>
+          <t>04:40:27</t>
+        </is>
+      </c>
+      <c r="C1732" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1732" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1732" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1732" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1732" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261029044027413497.jpg</t>
+        </is>
+      </c>
+      <c r="H1732" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1732" s="4" t="inlineStr"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1733" s="6" t="inlineStr">
+        <is>
+          <t>04:40:27</t>
+        </is>
+      </c>
+      <c r="C1733" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1733" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1733" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1733" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1733" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261029044027816349.doc</t>
+        </is>
+      </c>
+      <c r="H1733" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1733" s="7" t="inlineStr"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1734" s="3" t="inlineStr">
+        <is>
+          <t>04:40:28</t>
+        </is>
+      </c>
+      <c r="C1734" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1734" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1734" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1734" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1734" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261029044028220398.txt</t>
+        </is>
+      </c>
+      <c r="H1734" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1734" s="4" t="inlineStr"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1735" s="6" t="inlineStr">
+        <is>
+          <t>04:40:28</t>
+        </is>
+      </c>
+      <c r="C1735" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1735" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1735" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1735" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1735" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261029044028635485.xls</t>
+        </is>
+      </c>
+      <c r="H1735" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1735" s="7" t="inlineStr"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1736" s="3" t="inlineStr">
+        <is>
+          <t>04:40:29</t>
+        </is>
+      </c>
+      <c r="C1736" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1736" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1736" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1736" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1736" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261029044029011728.png</t>
+        </is>
+      </c>
+      <c r="H1736" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1736" s="4" t="inlineStr"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1737" s="6" t="inlineStr">
+        <is>
+          <t>04:40:29</t>
+        </is>
+      </c>
+      <c r="C1737" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1737" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1737" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1737" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1737" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261029044029415708.dat</t>
+        </is>
+      </c>
+      <c r="H1737" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1737" s="7" t="inlineStr"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1738" s="3" t="inlineStr">
+        <is>
+          <t>04:40:31</t>
+        </is>
+      </c>
+      <c r="C1738" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1738" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1738" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1738" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1738" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261029044031827379.docx</t>
+        </is>
+      </c>
+      <c r="H1738" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1738" s="4" t="inlineStr"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1739" s="6" t="inlineStr">
+        <is>
+          <t>04:40:32</t>
+        </is>
+      </c>
+      <c r="C1739" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1739" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1739" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1739" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1739" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261029044032206198.pdf</t>
+        </is>
+      </c>
+      <c r="H1739" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1739" s="7" t="inlineStr"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1740" s="3" t="inlineStr">
+        <is>
+          <t>04:40:32</t>
+        </is>
+      </c>
+      <c r="C1740" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1740" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1740" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1740" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1740" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261029044032616208.jpeg</t>
+        </is>
+      </c>
+      <c r="H1740" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1740" s="4" t="inlineStr"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1741" s="6" t="inlineStr">
+        <is>
+          <t>04:40:33</t>
+        </is>
+      </c>
+      <c r="C1741" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1741" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1741" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1741" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1741" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261029044033027715.xlsx</t>
+        </is>
+      </c>
+      <c r="H1741" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1741" s="7" t="inlineStr"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1742" s="3" t="inlineStr">
+        <is>
+          <t>04:40:33</t>
+        </is>
+      </c>
+      <c r="C1742" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1742" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1742" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1742" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1742" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261029044033779934.txt</t>
+        </is>
+      </c>
+      <c r="H1742" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1742" s="4" t="inlineStr"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1743" s="6" t="inlineStr">
+        <is>
+          <t>04:40:34</t>
+        </is>
+      </c>
+      <c r="C1743" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1743" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1743" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1743" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1743" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261029044034162911.xlsx</t>
+        </is>
+      </c>
+      <c r="H1743" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1743" s="7" t="inlineStr"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1744" s="3" t="inlineStr">
+        <is>
+          <t>04:40:34</t>
+        </is>
+      </c>
+      <c r="C1744" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1744" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1744" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1744" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1744" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1744" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1744" s="4" t="inlineStr"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1745" s="6" t="inlineStr">
+        <is>
+          <t>04:40:35</t>
+        </is>
+      </c>
+      <c r="C1745" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1745" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1745" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1745" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1745" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261029044035556732.pdf</t>
+        </is>
+      </c>
+      <c r="H1745" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1745" s="7" t="inlineStr"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1746" s="3" t="inlineStr">
+        <is>
+          <t>04:40:35</t>
+        </is>
+      </c>
+      <c r="C1746" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1746" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1746" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1746" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1746" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261029044035936700.jpeg</t>
+        </is>
+      </c>
+      <c r="H1746" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1746" s="4" t="inlineStr"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1747" s="6" t="inlineStr">
+        <is>
+          <t>04:40:36</t>
+        </is>
+      </c>
+      <c r="C1747" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1747" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1747" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1747" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1747" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261029044036348089.pages</t>
+        </is>
+      </c>
+      <c r="H1747" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1747" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1747"/>
+  <dimension ref="A1:I1769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75620,6 +75620,952 @@
       </c>
       <c r="I1747" s="7" t="inlineStr"/>
     </row>
+    <row r="1748">
+      <c r="A1748" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1748" s="3" t="inlineStr">
+        <is>
+          <t>04:40:15</t>
+        </is>
+      </c>
+      <c r="C1748" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1748" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1748" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1748" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1748" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261030044015790891.gif</t>
+        </is>
+      </c>
+      <c r="H1748" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1748" s="4" t="inlineStr"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1749" s="6" t="inlineStr">
+        <is>
+          <t>04:40:16</t>
+        </is>
+      </c>
+      <c r="C1749" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1749" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1749" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1749" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1749" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261030044016104054.xlsx</t>
+        </is>
+      </c>
+      <c r="H1749" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1749" s="7" t="inlineStr"/>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1750" s="3" t="inlineStr">
+        <is>
+          <t>04:40:16</t>
+        </is>
+      </c>
+      <c r="C1750" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1750" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1750" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1750" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1750" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261030044016432972.csv</t>
+        </is>
+      </c>
+      <c r="H1750" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1750" s="4" t="inlineStr"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1751" s="6" t="inlineStr">
+        <is>
+          <t>04:40:16</t>
+        </is>
+      </c>
+      <c r="C1751" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1751" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1751" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1751" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1751" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261030044016735446.pdf</t>
+        </is>
+      </c>
+      <c r="H1751" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1751" s="7" t="inlineStr"/>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1752" s="3" t="inlineStr">
+        <is>
+          <t>04:40:17</t>
+        </is>
+      </c>
+      <c r="C1752" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1752" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1752" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1752" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1752" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261030044017062893.docx</t>
+        </is>
+      </c>
+      <c r="H1752" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1752" s="4" t="inlineStr"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1753" s="6" t="inlineStr">
+        <is>
+          <t>04:40:17</t>
+        </is>
+      </c>
+      <c r="C1753" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1753" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1753" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1753" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1753" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261030044017386196.pptx</t>
+        </is>
+      </c>
+      <c r="H1753" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1753" s="7" t="inlineStr"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1754" s="3" t="inlineStr">
+        <is>
+          <t>04:40:17</t>
+        </is>
+      </c>
+      <c r="C1754" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1754" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1754" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1754" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1754" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261030044017710885.jpg</t>
+        </is>
+      </c>
+      <c r="H1754" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1754" s="4" t="inlineStr"/>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1755" s="6" t="inlineStr">
+        <is>
+          <t>04:40:18</t>
+        </is>
+      </c>
+      <c r="C1755" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1755" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1755" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1755" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1755" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261030044018011433.doc</t>
+        </is>
+      </c>
+      <c r="H1755" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1755" s="7" t="inlineStr"/>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1756" s="3" t="inlineStr">
+        <is>
+          <t>04:40:18</t>
+        </is>
+      </c>
+      <c r="C1756" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1756" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1756" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1756" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1756" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261030044018352955.txt</t>
+        </is>
+      </c>
+      <c r="H1756" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1756" s="4" t="inlineStr"/>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1757" s="6" t="inlineStr">
+        <is>
+          <t>04:40:18</t>
+        </is>
+      </c>
+      <c r="C1757" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1757" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1757" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1757" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1757" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261030044018669455.xls</t>
+        </is>
+      </c>
+      <c r="H1757" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1757" s="7" t="inlineStr"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1758" s="3" t="inlineStr">
+        <is>
+          <t>04:40:18</t>
+        </is>
+      </c>
+      <c r="C1758" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1758" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1758" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1758" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1758" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261030044018962252.png</t>
+        </is>
+      </c>
+      <c r="H1758" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1758" s="4" t="inlineStr"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1759" s="6" t="inlineStr">
+        <is>
+          <t>04:40:19</t>
+        </is>
+      </c>
+      <c r="C1759" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1759" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1759" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1759" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1759" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261030044019294272.dat</t>
+        </is>
+      </c>
+      <c r="H1759" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1759" s="7" t="inlineStr"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1760" s="3" t="inlineStr">
+        <is>
+          <t>04:40:21</t>
+        </is>
+      </c>
+      <c r="C1760" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1760" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1760" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1760" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1760" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261030044021528298.docx</t>
+        </is>
+      </c>
+      <c r="H1760" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1760" s="4" t="inlineStr"/>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1761" s="6" t="inlineStr">
+        <is>
+          <t>04:40:21</t>
+        </is>
+      </c>
+      <c r="C1761" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1761" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1761" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1761" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1761" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261030044021847750.pdf</t>
+        </is>
+      </c>
+      <c r="H1761" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1761" s="7" t="inlineStr"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1762" s="3" t="inlineStr">
+        <is>
+          <t>04:40:22</t>
+        </is>
+      </c>
+      <c r="C1762" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1762" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1762" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1762" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1762" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261030044022140104.jpeg</t>
+        </is>
+      </c>
+      <c r="H1762" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1762" s="4" t="inlineStr"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1763" s="6" t="inlineStr">
+        <is>
+          <t>04:40:22</t>
+        </is>
+      </c>
+      <c r="C1763" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1763" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1763" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1763" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1763" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261030044022466529.xlsx</t>
+        </is>
+      </c>
+      <c r="H1763" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1763" s="7" t="inlineStr"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1764" s="3" t="inlineStr">
+        <is>
+          <t>04:40:23</t>
+        </is>
+      </c>
+      <c r="C1764" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1764" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1764" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1764" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1764" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261030044023267617.txt</t>
+        </is>
+      </c>
+      <c r="H1764" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1764" s="4" t="inlineStr"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1765" s="6" t="inlineStr">
+        <is>
+          <t>04:40:23</t>
+        </is>
+      </c>
+      <c r="C1765" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1765" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1765" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1765" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1765" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261030044023563216.xlsx</t>
+        </is>
+      </c>
+      <c r="H1765" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1765" s="7" t="inlineStr"/>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1766" s="3" t="inlineStr">
+        <is>
+          <t>04:40:23</t>
+        </is>
+      </c>
+      <c r="C1766" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1766" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1766" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1766" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1766" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1766" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1766" s="4" t="inlineStr"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1767" s="6" t="inlineStr">
+        <is>
+          <t>04:40:24</t>
+        </is>
+      </c>
+      <c r="C1767" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1767" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1767" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1767" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1767" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261030044024662205.pdf</t>
+        </is>
+      </c>
+      <c r="H1767" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1767" s="7" t="inlineStr"/>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1768" s="3" t="inlineStr">
+        <is>
+          <t>04:40:24</t>
+        </is>
+      </c>
+      <c r="C1768" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1768" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1768" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1768" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1768" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261030044024988162.jpeg</t>
+        </is>
+      </c>
+      <c r="H1768" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1768" s="4" t="inlineStr"/>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1769" s="6" t="inlineStr">
+        <is>
+          <t>04:40:25</t>
+        </is>
+      </c>
+      <c r="C1769" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1769" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1769" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1769" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1769" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261030044025292462.pages</t>
+        </is>
+      </c>
+      <c r="H1769" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1769" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1769"/>
+  <dimension ref="A1:I1791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76566,6 +76566,952 @@
       </c>
       <c r="I1769" s="7" t="inlineStr"/>
     </row>
+    <row r="1770">
+      <c r="A1770" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1770" s="3" t="inlineStr">
+        <is>
+          <t>04:24:06</t>
+        </is>
+      </c>
+      <c r="C1770" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1770" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1770" s="4" t="inlineStr">
+        <is>
+          <t>architecture_diagram.gif</t>
+        </is>
+      </c>
+      <c r="F1770" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1770" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/architecture_diagram_20261031042406371264.gif</t>
+        </is>
+      </c>
+      <c r="H1770" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1770" s="4" t="inlineStr"/>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1771" s="6" t="inlineStr">
+        <is>
+          <t>04:24:06</t>
+        </is>
+      </c>
+      <c r="C1771" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1771" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1771" s="7" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="F1771" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1771" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/budget_2024_20261031042406730311.xlsx</t>
+        </is>
+      </c>
+      <c r="H1771" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1771" s="7" t="inlineStr"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1772" s="3" t="inlineStr">
+        <is>
+          <t>04:24:07</t>
+        </is>
+      </c>
+      <c r="C1772" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1772" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1772" s="4" t="inlineStr">
+        <is>
+          <t>data_export.csv</t>
+        </is>
+      </c>
+      <c r="F1772" s="3" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1772" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/data_export_20261031042407097918.csv</t>
+        </is>
+      </c>
+      <c r="H1772" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1772" s="4" t="inlineStr"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1773" s="6" t="inlineStr">
+        <is>
+          <t>04:24:07</t>
+        </is>
+      </c>
+      <c r="C1773" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1773" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1773" s="7" t="inlineStr">
+        <is>
+          <t>invoice_april_2024.pdf</t>
+        </is>
+      </c>
+      <c r="F1773" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1773" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/invoice_april_2024_20261031042407445232.pdf</t>
+        </is>
+      </c>
+      <c r="H1773" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1773" s="7" t="inlineStr"/>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1774" s="3" t="inlineStr">
+        <is>
+          <t>04:24:07</t>
+        </is>
+      </c>
+      <c r="C1774" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1774" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1774" s="4" t="inlineStr">
+        <is>
+          <t>meeting_notes.docx</t>
+        </is>
+      </c>
+      <c r="F1774" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1774" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/meeting_notes_20261031042407819007.docx</t>
+        </is>
+      </c>
+      <c r="H1774" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1774" s="4" t="inlineStr"/>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1775" s="6" t="inlineStr">
+        <is>
+          <t>04:24:08</t>
+        </is>
+      </c>
+      <c r="C1775" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1775" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1775" s="7" t="inlineStr">
+        <is>
+          <t>presentation.pptx</t>
+        </is>
+      </c>
+      <c r="F1775" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1775" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/presentation_20261031042408193787.pptx</t>
+        </is>
+      </c>
+      <c r="H1775" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1775" s="7" t="inlineStr"/>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1776" s="3" t="inlineStr">
+        <is>
+          <t>04:24:08</t>
+        </is>
+      </c>
+      <c r="C1776" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1776" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1776" s="4" t="inlineStr">
+        <is>
+          <t>product_screenshot.jpg</t>
+        </is>
+      </c>
+      <c r="F1776" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1776" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/product_screenshot_20261031042408568651.jpg</t>
+        </is>
+      </c>
+      <c r="H1776" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1776" s="4" t="inlineStr"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1777" s="6" t="inlineStr">
+        <is>
+          <t>04:24:08</t>
+        </is>
+      </c>
+      <c r="C1777" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1777" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1777" s="7" t="inlineStr">
+        <is>
+          <t>project_plan.doc</t>
+        </is>
+      </c>
+      <c r="F1777" s="6" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1777" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/project_plan_20261031042408917335.doc</t>
+        </is>
+      </c>
+      <c r="H1777" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1777" s="7" t="inlineStr"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1778" s="3" t="inlineStr">
+        <is>
+          <t>04:24:09</t>
+        </is>
+      </c>
+      <c r="C1778" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1778" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1778" s="4" t="inlineStr">
+        <is>
+          <t>readme_notes.txt</t>
+        </is>
+      </c>
+      <c r="F1778" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1778" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/readme_notes_20261031042409296558.txt</t>
+        </is>
+      </c>
+      <c r="H1778" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1778" s="4" t="inlineStr"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1779" s="6" t="inlineStr">
+        <is>
+          <t>04:24:09</t>
+        </is>
+      </c>
+      <c r="C1779" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1779" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1779" s="7" t="inlineStr">
+        <is>
+          <t>salary_sheet.xls</t>
+        </is>
+      </c>
+      <c r="F1779" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1779" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/salary_sheet_20261031042409670547.xls</t>
+        </is>
+      </c>
+      <c r="H1779" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1779" s="7" t="inlineStr"/>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1780" s="3" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1780" s="4" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1780" s="4" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1780" s="4" t="inlineStr">
+        <is>
+          <t>team_photo.png</t>
+        </is>
+      </c>
+      <c r="F1780" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1780" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/team_photo_20261031042410020189.png</t>
+        </is>
+      </c>
+      <c r="H1780" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1780" s="4" t="inlineStr"/>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1781" s="6" t="inlineStr">
+        <is>
+          <t>04:24:10</t>
+        </is>
+      </c>
+      <c r="C1781" s="7" t="inlineStr">
+        <is>
+          <t>Test Run</t>
+        </is>
+      </c>
+      <c r="D1781" s="7" t="inlineStr">
+        <is>
+          <t>local@test</t>
+        </is>
+      </c>
+      <c r="E1781" s="7" t="inlineStr">
+        <is>
+          <t>unknown_format.dat</t>
+        </is>
+      </c>
+      <c r="F1781" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1781" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/unknown_format_20261031042410401495.dat</t>
+        </is>
+      </c>
+      <c r="H1781" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1781" s="7" t="inlineStr"/>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1782" s="3" t="inlineStr">
+        <is>
+          <t>04:24:13</t>
+        </is>
+      </c>
+      <c r="C1782" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1782" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1782" s="4" t="inlineStr">
+        <is>
+          <t>Forge_Review1_EasyLearningyu.docx</t>
+        </is>
+      </c>
+      <c r="F1782" s="3" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="G1782" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/word/Forge_Review1_EasyLearningyu_20261031042413402798.docx</t>
+        </is>
+      </c>
+      <c r="H1782" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1782" s="4" t="inlineStr"/>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1783" s="6" t="inlineStr">
+        <is>
+          <t>04:24:13</t>
+        </is>
+      </c>
+      <c r="C1783" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1783" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1783" s="7" t="inlineStr">
+        <is>
+          <t>csc472 Week 14 GA.pdf</t>
+        </is>
+      </c>
+      <c r="F1783" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1783" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/csc472 Week 14 GA_20261031042413788115.pdf</t>
+        </is>
+      </c>
+      <c r="H1783" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1783" s="7" t="inlineStr"/>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1784" s="3" t="inlineStr">
+        <is>
+          <t>04:24:14</t>
+        </is>
+      </c>
+      <c r="C1784" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1784" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1784" s="4" t="inlineStr">
+        <is>
+          <t>_ 1.jpeg</t>
+        </is>
+      </c>
+      <c r="F1784" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1784" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/_ 1_20261031042414138081.jpeg</t>
+        </is>
+      </c>
+      <c r="H1784" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1784" s="4" t="inlineStr"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1785" s="6" t="inlineStr">
+        <is>
+          <t>04:24:14</t>
+        </is>
+      </c>
+      <c r="C1785" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1785" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1785" s="7" t="inlineStr">
+        <is>
+          <t>python_jobs_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1785" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1785" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/python_jobs_report_20261031042414515576.xlsx</t>
+        </is>
+      </c>
+      <c r="H1785" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1785" s="7" t="inlineStr"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1786" s="3" t="inlineStr">
+        <is>
+          <t>04:24:15</t>
+        </is>
+      </c>
+      <c r="C1786" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1786" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1786" s="4" t="inlineStr">
+        <is>
+          <t>03.txt</t>
+        </is>
+      </c>
+      <c r="F1786" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1786" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/03_20261031042415514175.txt</t>
+        </is>
+      </c>
+      <c r="H1786" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1786" s="4" t="inlineStr"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1787" s="6" t="inlineStr">
+        <is>
+          <t>04:24:15</t>
+        </is>
+      </c>
+      <c r="C1787" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1787" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1787" s="7" t="inlineStr">
+        <is>
+          <t>sales_report.xlsx</t>
+        </is>
+      </c>
+      <c r="F1787" s="6" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="G1787" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/excel/sales_report_20261031042415888599.xlsx</t>
+        </is>
+      </c>
+      <c r="H1787" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1787" s="7" t="inlineStr"/>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1788" s="3" t="inlineStr">
+        <is>
+          <t>04:24:16</t>
+        </is>
+      </c>
+      <c r="C1788" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1788" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1788" s="4" t="inlineStr">
+        <is>
+          <t>token.json</t>
+        </is>
+      </c>
+      <c r="F1788" s="3" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1788" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/token.json</t>
+        </is>
+      </c>
+      <c r="H1788" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1788" s="4" t="inlineStr"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1789" s="6" t="inlineStr">
+        <is>
+          <t>04:24:16</t>
+        </is>
+      </c>
+      <c r="C1789" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1789" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1789" s="7" t="inlineStr">
+        <is>
+          <t>watermark.pdf</t>
+        </is>
+      </c>
+      <c r="F1789" s="6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="G1789" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/pdf/watermark_20261031042416976285.pdf</t>
+        </is>
+      </c>
+      <c r="H1789" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1789" s="7" t="inlineStr"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1790" s="3" t="inlineStr">
+        <is>
+          <t>04:24:17</t>
+        </is>
+      </c>
+      <c r="C1790" s="4" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1790" s="4" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1790" s="4" t="inlineStr">
+        <is>
+          <t>_.jpeg</t>
+        </is>
+      </c>
+      <c r="F1790" s="3" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1790" s="4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/image/__20261031042417352251.jpeg</t>
+        </is>
+      </c>
+      <c r="H1790" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1790" s="4" t="inlineStr"/>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B1791" s="6" t="inlineStr">
+        <is>
+          <t>04:24:17</t>
+        </is>
+      </c>
+      <c r="C1791" s="7" t="inlineStr">
+        <is>
+          <t>RPA_TEST</t>
+        </is>
+      </c>
+      <c r="D1791" s="7" t="inlineStr">
+        <is>
+          <t>Patkbung &lt;patchanansnt@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="E1791" s="7" t="inlineStr">
+        <is>
+          <t>detail table.pages</t>
+        </is>
+      </c>
+      <c r="F1791" s="6" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="G1791" s="7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/rpa_email_dashboard/rpa_email_dashboard/downloads/others/detail table_20261031042417726140.pages</t>
+        </is>
+      </c>
+      <c r="H1791" s="8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I1791" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
